--- a/gstdatabase/GSTR-1-2023-2024.xlsx
+++ b/gstdatabase/GSTR-1-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1FF8005-4A7A-4130-80DF-C2C1E3262DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744966EB-8BDD-4459-9953-AFC501B81962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
 CD</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -362,18 +362,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -385,6 +373,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -684,13 +684,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -702,10 +702,10 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="19"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -722,107 +722,107 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="8" spans="1:62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="18">
         <v>45017</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="15">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="18">
         <v>45047</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="15">
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="18">
         <v>45078</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="15">
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="18">
         <v>45108</v>
       </c>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="15">
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="18">
         <v>45139</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="15">
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="18">
         <v>45170</v>
       </c>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="15">
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="18">
         <v>45200</v>
       </c>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="16"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="15">
+      <c r="AH8" s="19"/>
+      <c r="AI8" s="19"/>
+      <c r="AJ8" s="19"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="18">
         <v>45231</v>
       </c>
-      <c r="AM8" s="16"/>
-      <c r="AN8" s="16"/>
-      <c r="AO8" s="16"/>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="15">
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="20"/>
+      <c r="AQ8" s="18">
         <v>45261</v>
       </c>
-      <c r="AR8" s="16"/>
-      <c r="AS8" s="16"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="17"/>
-      <c r="AV8" s="15">
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
+      <c r="AT8" s="19"/>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="18">
         <v>45292</v>
       </c>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="16"/>
-      <c r="AY8" s="16"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="15">
+      <c r="AW8" s="19"/>
+      <c r="AX8" s="19"/>
+      <c r="AY8" s="19"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="18">
         <v>45323</v>
       </c>
-      <c r="BB8" s="16"/>
-      <c r="BC8" s="16"/>
-      <c r="BD8" s="16"/>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="15">
+      <c r="BB8" s="19"/>
+      <c r="BC8" s="19"/>
+      <c r="BD8" s="19"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="18">
         <v>45352</v>
       </c>
-      <c r="BG8" s="16"/>
-      <c r="BH8" s="16"/>
-      <c r="BI8" s="16"/>
-      <c r="BJ8" s="17"/>
+      <c r="BG8" s="19"/>
+      <c r="BH8" s="19"/>
+      <c r="BI8" s="19"/>
+      <c r="BJ8" s="20"/>
     </row>
     <row r="9" spans="1:62" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>41877</v>
+        <v>41879</v>
       </c>
       <c r="F10" s="5">
-        <v>70566</v>
+        <v>70568</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>1.0045125197511708</v>
+        <v>1.0045409899073297</v>
       </c>
       <c r="H10" s="5">
         <v>72254</v>
@@ -1036,14 +1036,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>43020</v>
+        <v>43023</v>
       </c>
       <c r="K10" s="5">
-        <v>72185</v>
+        <v>72188</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.99904503556896507</v>
+        <v>0.99908655576161876</v>
       </c>
       <c r="M10" s="5">
         <v>120466</v>
@@ -1053,14 +1053,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>74866</v>
+        <v>74871</v>
       </c>
       <c r="P10" s="5">
-        <v>120489</v>
+        <v>120494</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>1.0001909252403167</v>
+        <v>1.0002324307273422</v>
       </c>
       <c r="R10" s="5">
         <v>70979</v>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>41691</v>
+        <v>41695</v>
       </c>
       <c r="U10" s="5">
-        <v>71185</v>
+        <v>71189</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>1.002902266867665</v>
+        <v>1.0029586215641246</v>
       </c>
       <c r="W10" s="5">
         <v>73348</v>
@@ -1087,14 +1087,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>42542</v>
+        <v>42547</v>
       </c>
       <c r="Z10" s="5">
-        <v>72932</v>
+        <v>72937</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.99432840704586356</v>
+        <v>0.99439657523040847</v>
       </c>
       <c r="AB10" s="5">
         <v>123554</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>77011</v>
+        <v>77024</v>
       </c>
       <c r="AE10" s="5">
-        <v>123611</v>
+        <v>123624</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>1.0004613367434483</v>
+        <v>1.0005665538954627</v>
       </c>
       <c r="AG10" s="5">
         <v>71950</v>
@@ -1121,14 +1121,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41853</v>
+        <v>41863</v>
       </c>
       <c r="AJ10" s="5">
-        <v>71904</v>
+        <v>71914</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99936066712995131</v>
+        <v>0.99949965253648365</v>
       </c>
       <c r="AL10" s="5">
         <v>73532</v>
@@ -1138,14 +1138,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>43038</v>
+        <v>43047</v>
       </c>
       <c r="AO10" s="5">
-        <v>72968</v>
+        <v>72977</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99232986998857642</v>
+        <v>0.99245226568024802</v>
       </c>
       <c r="AQ10" s="5">
         <v>125499</v>
@@ -1155,14 +1155,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79239</v>
+        <v>79253</v>
       </c>
       <c r="AT10" s="5">
-        <v>125954</v>
+        <v>125968</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0036255268966288</v>
+        <v>1.003737081570371</v>
       </c>
       <c r="AV10" s="5">
         <v>72481</v>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>42355</v>
+        <v>42363</v>
       </c>
       <c r="AY10" s="5">
-        <v>72219</v>
+        <v>72227</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99638525958527058</v>
+        <v>0.99649563333839208</v>
       </c>
       <c r="BA10" s="5">
         <v>73790</v>
@@ -1189,14 +1189,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>43024</v>
+        <v>43034</v>
       </c>
       <c r="BD10" s="5">
-        <v>73219</v>
+        <v>73229</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.99226182409540586</v>
+        <v>0.99239734381352485</v>
       </c>
       <c r="BF10" s="5">
         <v>128129</v>
@@ -1206,14 +1206,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>85623</v>
+        <v>85642</v>
       </c>
       <c r="BI10" s="5">
-        <v>128146</v>
+        <v>128165</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>1.0001326787846623</v>
+        <v>1.0002809668381085</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>17631</v>
+        <v>17633</v>
       </c>
       <c r="F11" s="5">
-        <v>44786</v>
+        <v>44788</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G47" si="1">F11/C11</f>
-        <v>1.0061104371658354</v>
+        <v>1.0061553668508785</v>
       </c>
       <c r="H11" s="5">
         <v>46110</v>
@@ -1248,14 +1248,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>18774</v>
+        <v>18775</v>
       </c>
       <c r="K11" s="5">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.99752765126870524</v>
+        <v>0.99754933853827799</v>
       </c>
       <c r="M11" s="5">
         <v>102242</v>
@@ -1265,14 +1265,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>52505</v>
+        <v>52507</v>
       </c>
       <c r="P11" s="5">
-        <v>102568</v>
+        <v>102570</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.0031885135267307</v>
+        <v>1.0032080749594101</v>
       </c>
       <c r="R11" s="5">
         <v>44890</v>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>16798</v>
+        <v>16799</v>
       </c>
       <c r="U11" s="5">
-        <v>44823</v>
+        <v>44824</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.9985074626865672</v>
+        <v>0.99852973936288703</v>
       </c>
       <c r="W11" s="5">
         <v>46425</v>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>17302</v>
+        <v>17307</v>
       </c>
       <c r="Z11" s="5">
-        <v>45899</v>
+        <v>45904</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.98866989768443725</v>
+        <v>0.98877759827679057</v>
       </c>
       <c r="AB11" s="5">
         <v>103964</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>44407</v>
+        <v>44415</v>
       </c>
       <c r="AE11" s="5">
-        <v>104329</v>
+        <v>104337</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.0035108306721559</v>
+        <v>1.003587780385518</v>
       </c>
       <c r="AG11" s="5">
         <v>45569</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15632</v>
+        <v>15640</v>
       </c>
       <c r="AJ11" s="5">
-        <v>45341</v>
+        <v>45349</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99499659856481382</v>
+        <v>0.99517215650990809</v>
       </c>
       <c r="AL11" s="5">
         <v>46951</v>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN25" si="14">AO11-AM11</f>
-        <v>16002</v>
+        <v>16009</v>
       </c>
       <c r="AO11" s="5">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP26" si="15">AO11/AL11</f>
-        <v>0.98513343698749756</v>
+        <v>0.98528252859364018</v>
       </c>
       <c r="AQ11" s="5">
         <v>105644</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS25" si="16">AT11-AR11</f>
-        <v>42423</v>
+        <v>42437</v>
       </c>
       <c r="AT11" s="5">
-        <v>106029</v>
+        <v>106043</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU26" si="17">AT11/AQ11</f>
-        <v>1.0036443148688046</v>
+        <v>1.0037768354094885</v>
       </c>
       <c r="AV11" s="5">
         <v>46072</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX25" si="18">AY11-AW11</f>
-        <v>15094</v>
+        <v>15102</v>
       </c>
       <c r="AY11" s="5">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ26" si="19">AY11/AV11</f>
-        <v>0.99711321409967013</v>
+        <v>0.99728685535683281</v>
       </c>
       <c r="BA11" s="5">
         <v>47252</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC25" si="20">BD11-BB11</f>
-        <v>15556</v>
+        <v>15567</v>
       </c>
       <c r="BD11" s="5">
-        <v>46902</v>
+        <v>46913</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE26" si="21">BD11/BA11</f>
-        <v>0.99259290612037587</v>
+        <v>0.99282570049944974</v>
       </c>
       <c r="BF11" s="5">
         <v>107665</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>46545</v>
+        <v>46572</v>
       </c>
       <c r="BI11" s="5">
-        <v>107741</v>
+        <v>107768</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>1.0007058932800816</v>
+        <v>1.0009566711559001</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>35169</v>
+        <v>35173</v>
       </c>
       <c r="F12" s="5">
-        <v>165070</v>
+        <v>165074</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.99457733325299758</v>
+        <v>0.99460143399409529</v>
       </c>
       <c r="H12" s="5">
         <v>170538</v>
@@ -1460,14 +1460,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>37612</v>
+        <v>37617</v>
       </c>
       <c r="K12" s="5">
-        <v>168152</v>
+        <v>168157</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98600898333509246</v>
+        <v>0.98603830231385381</v>
       </c>
       <c r="M12" s="5">
         <v>344875</v>
@@ -1477,14 +1477,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>96107</v>
+        <v>96118</v>
       </c>
       <c r="P12" s="5">
-        <v>343868</v>
+        <v>343879</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99708010148604564</v>
+        <v>0.99711199710039866</v>
       </c>
       <c r="R12" s="5">
         <v>167705</v>
@@ -1494,14 +1494,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>37666</v>
+        <v>37672</v>
       </c>
       <c r="U12" s="5">
-        <v>166804</v>
+        <v>166810</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99462747085656356</v>
+        <v>0.99466324796517691</v>
       </c>
       <c r="W12" s="5">
         <v>171864</v>
@@ -1511,14 +1511,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>38692</v>
+        <v>38700</v>
       </c>
       <c r="Z12" s="5">
-        <v>169932</v>
+        <v>169940</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.98875855327468232</v>
+        <v>0.98880510170832747</v>
       </c>
       <c r="AB12" s="5">
         <v>349048</v>
@@ -1528,14 +1528,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>93171</v>
+        <v>93190</v>
       </c>
       <c r="AE12" s="5">
-        <v>348625</v>
+        <v>348644</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99878813229126084</v>
+        <v>0.99884256606541222</v>
       </c>
       <c r="AG12" s="5">
         <v>170526</v>
@@ -1545,14 +1545,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>38068</v>
+        <v>38081</v>
       </c>
       <c r="AJ12" s="5">
-        <v>169844</v>
+        <v>169857</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.99600060987767258</v>
+        <v>0.99607684458674928</v>
       </c>
       <c r="AL12" s="5">
         <v>174892</v>
@@ -1562,14 +1562,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>38309</v>
+        <v>38323</v>
       </c>
       <c r="AO12" s="5">
-        <v>172257</v>
+        <v>172271</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98493355899640922</v>
+        <v>0.98501360839832586</v>
       </c>
       <c r="AQ12" s="5">
         <v>353589</v>
@@ -1579,14 +1579,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94304</v>
+        <v>94333</v>
       </c>
       <c r="AT12" s="5">
-        <v>353323</v>
+        <v>353352</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99924771415400371</v>
+        <v>0.99932973028007088</v>
       </c>
       <c r="AV12" s="5">
         <v>172980</v>
@@ -1596,14 +1596,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36186</v>
+        <v>36200</v>
       </c>
       <c r="AY12" s="5">
-        <v>171862</v>
+        <v>171876</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99353682506648167</v>
+        <v>0.99361775927852936</v>
       </c>
       <c r="BA12" s="5">
         <v>177212</v>
@@ -1613,14 +1613,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>36691</v>
+        <v>36708</v>
       </c>
       <c r="BD12" s="5">
-        <v>174585</v>
+        <v>174602</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98517594745276849</v>
+        <v>0.98527187775094238</v>
       </c>
       <c r="BF12" s="5">
         <v>359260</v>
@@ -1630,14 +1630,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>100711</v>
+        <v>100751</v>
       </c>
       <c r="BI12" s="5">
-        <v>357951</v>
+        <v>357991</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99635639926515618</v>
+        <v>0.99646773924177479</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1655,14 +1655,14 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>3341</v>
+        <v>3342</v>
       </c>
       <c r="F13" s="5">
-        <v>16556</v>
+        <v>16557</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>1.0029076811243034</v>
+        <v>1.002968257814393</v>
       </c>
       <c r="H13" s="5">
         <v>16836</v>
@@ -1672,14 +1672,14 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="K13" s="5">
-        <v>16752</v>
+        <v>16753</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="3"/>
-        <v>0.9950106913756237</v>
+        <v>0.99507008790686624</v>
       </c>
       <c r="M13" s="5">
         <v>27790</v>
@@ -1689,14 +1689,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>7551</v>
+        <v>7552</v>
       </c>
       <c r="P13" s="5">
-        <v>27867</v>
+        <v>27868</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>1.0027707808564232</v>
+        <v>1.0028067650233896</v>
       </c>
       <c r="R13" s="5">
         <v>16731</v>
@@ -1867,14 +1867,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>36546</v>
+        <v>36552</v>
       </c>
       <c r="F14" s="5">
-        <v>84990</v>
+        <v>84996</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99539721021749061</v>
+        <v>0.99546748181722355</v>
       </c>
       <c r="H14" s="5">
         <v>88261</v>
@@ -1884,14 +1884,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>37971</v>
+        <v>37981</v>
       </c>
       <c r="K14" s="5">
-        <v>86796</v>
+        <v>86806</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.98340150236231183</v>
+        <v>0.9835148026874837</v>
       </c>
       <c r="M14" s="5">
         <v>157146</v>
@@ -1901,14 +1901,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>76965</v>
+        <v>76986</v>
       </c>
       <c r="P14" s="5">
-        <v>155866</v>
+        <v>155887</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99185470836037826</v>
+        <v>0.99198834205134079</v>
       </c>
       <c r="R14" s="5">
         <v>86469</v>
@@ -1918,14 +1918,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>36744</v>
+        <v>36755</v>
       </c>
       <c r="U14" s="5">
-        <v>85076</v>
+        <v>85087</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.98389018029582853</v>
+        <v>0.98401739351675166</v>
       </c>
       <c r="W14" s="5">
         <v>88169</v>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>37724</v>
+        <v>37737</v>
       </c>
       <c r="Z14" s="5">
-        <v>86289</v>
+        <v>86302</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97867731288774962</v>
+        <v>0.97882475700075988</v>
       </c>
       <c r="AB14" s="5">
         <v>157930</v>
@@ -1952,14 +1952,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>76113</v>
+        <v>76138</v>
       </c>
       <c r="AE14" s="5">
-        <v>157529</v>
+        <v>157554</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99746090039891089</v>
+        <v>0.99761919837902868</v>
       </c>
       <c r="AG14" s="5">
         <v>87312</v>
@@ -1969,14 +1969,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>37750</v>
+        <v>37763</v>
       </c>
       <c r="AJ14" s="5">
-        <v>86606</v>
+        <v>86619</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99191405534176291</v>
+        <v>0.99206294667399675</v>
       </c>
       <c r="AL14" s="5">
         <v>89337</v>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>37678</v>
+        <v>37694</v>
       </c>
       <c r="AO14" s="5">
-        <v>87796</v>
+        <v>87812</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.98275070799332864</v>
+        <v>0.9829298051199391</v>
       </c>
       <c r="AQ14" s="5">
         <v>160173</v>
@@ -2003,14 +2003,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>77609</v>
+        <v>77640</v>
       </c>
       <c r="AT14" s="5">
-        <v>160619</v>
+        <v>160650</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>1.0027844892709759</v>
+        <v>1.002978030005057</v>
       </c>
       <c r="AV14" s="5">
         <v>88523</v>
@@ -2020,14 +2020,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>37606</v>
+        <v>37626</v>
       </c>
       <c r="AY14" s="5">
-        <v>88143</v>
+        <v>88163</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99570733029834058</v>
+        <v>0.9959332602826384</v>
       </c>
       <c r="BA14" s="5">
         <v>90782</v>
@@ -2037,14 +2037,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>37715</v>
+        <v>37733</v>
       </c>
       <c r="BD14" s="5">
-        <v>89629</v>
+        <v>89647</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.9872992443435924</v>
+        <v>0.98749752153510606</v>
       </c>
       <c r="BF14" s="5">
         <v>163900</v>
@@ -2054,14 +2054,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>82104</v>
+        <v>82149</v>
       </c>
       <c r="BI14" s="5">
-        <v>163258</v>
+        <v>163303</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99608297742525931</v>
+        <v>0.99635753508236735</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2079,14 +2079,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>72333</v>
+        <v>72334</v>
       </c>
       <c r="F15" s="5">
-        <v>282211</v>
+        <v>282212</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.99278482526683132</v>
+        <v>0.9927883431482224</v>
       </c>
       <c r="H15" s="5">
         <v>290906</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>76324</v>
+        <v>76325</v>
       </c>
       <c r="K15" s="5">
-        <v>286774</v>
+        <v>286775</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.98579609908355281</v>
+        <v>0.98579953662007658</v>
       </c>
       <c r="M15" s="5">
         <v>490131</v>
@@ -2113,14 +2113,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>147280</v>
+        <v>147284</v>
       </c>
       <c r="P15" s="5">
-        <v>486596</v>
+        <v>486600</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99278764248741658</v>
+        <v>0.99279580357088204</v>
       </c>
       <c r="R15" s="5">
         <v>287010</v>
@@ -2130,14 +2130,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>74982</v>
+        <v>74984</v>
       </c>
       <c r="U15" s="5">
-        <v>283572</v>
+        <v>283574</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.98802132329883974</v>
+        <v>0.98802829169715345</v>
       </c>
       <c r="W15" s="5">
         <v>292338</v>
@@ -2147,14 +2147,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>74391</v>
+        <v>74392</v>
       </c>
       <c r="Z15" s="5">
-        <v>287484</v>
+        <v>287485</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98339593210598686</v>
+        <v>0.98339935280394608</v>
       </c>
       <c r="AB15" s="5">
         <v>495688</v>
@@ -2164,14 +2164,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>142476</v>
+        <v>142479</v>
       </c>
       <c r="AE15" s="5">
-        <v>492164</v>
+        <v>492167</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99289068930456259</v>
+        <v>0.99289674149868468</v>
       </c>
       <c r="AG15" s="5">
         <v>292071</v>
@@ -2181,14 +2181,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>78354</v>
+        <v>78358</v>
       </c>
       <c r="AJ15" s="5">
-        <v>289363</v>
+        <v>289367</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99072828182188577</v>
+        <v>0.99074197712200118</v>
       </c>
       <c r="AL15" s="5">
         <v>298411</v>
@@ -2198,14 +2198,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75039</v>
+        <v>75045</v>
       </c>
       <c r="AO15" s="5">
-        <v>293260</v>
+        <v>293266</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98273857196953196</v>
+        <v>0.98275867846694664</v>
       </c>
       <c r="AQ15" s="5">
         <v>502913</v>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137724</v>
+        <v>137738</v>
       </c>
       <c r="AT15" s="5">
-        <v>499812</v>
+        <v>499826</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99383392356133171</v>
+        <v>0.99386176137821058</v>
       </c>
       <c r="AV15" s="5">
         <v>298012</v>
@@ -2232,14 +2232,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>71726</v>
+        <v>71733</v>
       </c>
       <c r="AY15" s="5">
-        <v>294429</v>
+        <v>294436</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.98797699421499807</v>
+        <v>0.98800048320201872</v>
       </c>
       <c r="BA15" s="5">
         <v>303376</v>
@@ -2249,14 +2249,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>71588</v>
+        <v>71595</v>
       </c>
       <c r="BD15" s="5">
-        <v>298816</v>
+        <v>298823</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98496914719687778</v>
+        <v>0.98499222087442651</v>
       </c>
       <c r="BF15" s="5">
         <v>511329</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>149671</v>
+        <v>149692</v>
       </c>
       <c r="BI15" s="5">
-        <v>507677</v>
+        <v>507698</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99285782734795014</v>
+        <v>0.99289889679638743</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>107201</v>
+        <v>107217</v>
       </c>
       <c r="F16" s="5">
-        <v>426835</v>
+        <v>426851</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99117582175159935</v>
+        <v>0.99121297618632953</v>
       </c>
       <c r="H16" s="5">
         <v>441093</v>
@@ -2308,14 +2308,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>113310</v>
+        <v>113334</v>
       </c>
       <c r="K16" s="5">
-        <v>431236</v>
+        <v>431260</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.977653238659421</v>
+        <v>0.97770764895384876</v>
       </c>
       <c r="M16" s="5">
         <v>754668</v>
@@ -2325,14 +2325,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>199802</v>
+        <v>199861</v>
       </c>
       <c r="P16" s="5">
-        <v>751654</v>
+        <v>751713</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99600619080178299</v>
+        <v>0.99608437087566981</v>
       </c>
       <c r="R16" s="5">
         <v>429537</v>
@@ -2342,14 +2342,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>111528</v>
+        <v>111560</v>
       </c>
       <c r="U16" s="5">
-        <v>423830</v>
+        <v>423862</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.98671360092378535</v>
+        <v>0.98678809974460868</v>
       </c>
       <c r="W16" s="5">
         <v>433887</v>
@@ -2359,14 +2359,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>112598</v>
+        <v>112634</v>
       </c>
       <c r="Z16" s="5">
-        <v>426841</v>
+        <v>426877</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98376074876638386</v>
+        <v>0.98384371967816509</v>
       </c>
       <c r="AB16" s="5">
         <v>753330</v>
@@ -2376,14 +2376,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>199957</v>
+        <v>200030</v>
       </c>
       <c r="AE16" s="5">
-        <v>752035</v>
+        <v>752108</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.9982809658449816</v>
+        <v>0.99837786892862357</v>
       </c>
       <c r="AG16" s="5">
         <v>431686</v>
@@ -2393,14 +2393,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>113749</v>
+        <v>113789</v>
       </c>
       <c r="AJ16" s="5">
-        <v>426090</v>
+        <v>426130</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98703687402417495</v>
+        <v>0.98712953396681846</v>
       </c>
       <c r="AL16" s="5">
         <v>438911</v>
@@ -2410,14 +2410,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>114001</v>
+        <v>114049</v>
       </c>
       <c r="AO16" s="5">
-        <v>430493</v>
+        <v>430541</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.9808207130830624</v>
+        <v>0.98093007466206128</v>
       </c>
       <c r="AQ16" s="5">
         <v>759875</v>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>195534</v>
+        <v>195643</v>
       </c>
       <c r="AT16" s="5">
-        <v>758533</v>
+        <v>758642</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99823392005264022</v>
+        <v>0.99837736469814109</v>
       </c>
       <c r="AV16" s="5">
         <v>437477</v>
@@ -2444,14 +2444,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108288</v>
+        <v>108349</v>
       </c>
       <c r="AY16" s="5">
-        <v>431029</v>
+        <v>431090</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.98526093943224446</v>
+        <v>0.98540037533401759</v>
       </c>
       <c r="BA16" s="5">
         <v>445887</v>
@@ -2461,14 +2461,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>109698</v>
+        <v>109767</v>
       </c>
       <c r="BD16" s="5">
-        <v>436866</v>
+        <v>436935</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.97976841666162051</v>
+        <v>0.97992316438918381</v>
       </c>
       <c r="BF16" s="5">
         <v>770088</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>207215</v>
+        <v>207378</v>
       </c>
       <c r="BI16" s="5">
-        <v>764797</v>
+        <v>764960</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99312935664495483</v>
+        <v>0.99334102076645781</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>89294</v>
+        <v>89306</v>
       </c>
       <c r="F17" s="5">
-        <v>301140</v>
+        <v>301152</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99526066350710896</v>
+        <v>0.9953003232267148</v>
       </c>
       <c r="H17" s="5">
         <v>314962</v>
@@ -2520,14 +2520,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>92335</v>
+        <v>92347</v>
       </c>
       <c r="K17" s="5">
-        <v>309386</v>
+        <v>309398</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98229627701119504</v>
+        <v>0.98233437684546077</v>
       </c>
       <c r="M17" s="5">
         <v>695415</v>
@@ -2537,14 +2537,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>249422</v>
+        <v>249466</v>
       </c>
       <c r="P17" s="5">
-        <v>691701</v>
+        <v>691745</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99465930415651083</v>
+        <v>0.99472257572816236</v>
       </c>
       <c r="R17" s="5">
         <v>305324</v>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>90685</v>
+        <v>90703</v>
       </c>
       <c r="U17" s="5">
-        <v>302671</v>
+        <v>302689</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99131086976457794</v>
+        <v>0.99136982353172365</v>
       </c>
       <c r="W17" s="5">
         <v>316716</v>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>93425</v>
+        <v>93447</v>
       </c>
       <c r="Z17" s="5">
-        <v>309778</v>
+        <v>309800</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97809393904949549</v>
+        <v>0.97816340191212314</v>
       </c>
       <c r="AB17" s="5">
         <v>703511</v>
@@ -2588,14 +2588,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>254003</v>
+        <v>254073</v>
       </c>
       <c r="AE17" s="5">
-        <v>699678</v>
+        <v>699748</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99455161326546426</v>
+        <v>0.99465111419721941</v>
       </c>
       <c r="AG17" s="5">
         <v>311084</v>
@@ -2605,14 +2605,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>90853</v>
+        <v>90878</v>
       </c>
       <c r="AJ17" s="5">
-        <v>308947</v>
+        <v>308972</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99313047279834388</v>
+        <v>0.9932108369443623</v>
       </c>
       <c r="AL17" s="5">
         <v>323550</v>
@@ -2622,14 +2622,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93502</v>
+        <v>93528</v>
       </c>
       <c r="AO17" s="5">
-        <v>316247</v>
+        <v>316273</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97742852727553697</v>
+        <v>0.97750888579817652</v>
       </c>
       <c r="AQ17" s="5">
         <v>714257</v>
@@ -2639,14 +2639,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>244151</v>
+        <v>244243</v>
       </c>
       <c r="AT17" s="5">
-        <v>714075</v>
+        <v>714167</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99974518975662818</v>
+        <v>0.99987399493459639</v>
       </c>
       <c r="AV17" s="5">
         <v>316308</v>
@@ -2656,14 +2656,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>87021</v>
+        <v>87059</v>
       </c>
       <c r="AY17" s="5">
-        <v>314677</v>
+        <v>314715</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99484363342059001</v>
+        <v>0.99496376949049659</v>
       </c>
       <c r="BA17" s="5">
         <v>328067</v>
@@ -2673,14 +2673,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>88440</v>
+        <v>88484</v>
       </c>
       <c r="BD17" s="5">
-        <v>321610</v>
+        <v>321654</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.98031804478963136</v>
+        <v>0.98045216373484689</v>
       </c>
       <c r="BF17" s="5">
         <v>726752</v>
@@ -2690,14 +2690,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>272976</v>
+        <v>273093</v>
       </c>
       <c r="BI17" s="5">
-        <v>725446</v>
+        <v>725563</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99820296332173841</v>
+        <v>0.99836395359077101</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>454309</v>
+        <v>454337</v>
       </c>
       <c r="F18" s="5">
-        <v>917842</v>
+        <v>917870</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99631581918205536</v>
+        <v>0.99634621313105431</v>
       </c>
       <c r="H18" s="5">
         <v>943261</v>
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>449470</v>
+        <v>449505</v>
       </c>
       <c r="K18" s="5">
-        <v>932500</v>
+        <v>932535</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98859170473495672</v>
+        <v>0.98862881005363312</v>
       </c>
       <c r="M18" s="5">
         <v>1440086</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>736474</v>
+        <v>736537</v>
       </c>
       <c r="P18" s="5">
-        <v>1430564</v>
+        <v>1430627</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99338789488961077</v>
+        <v>0.9934316422769196</v>
       </c>
       <c r="R18" s="5">
         <v>938677</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>455634</v>
+        <v>455678</v>
       </c>
       <c r="U18" s="5">
-        <v>928201</v>
+        <v>928245</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98883961149575417</v>
+        <v>0.98888648597973527</v>
       </c>
       <c r="W18" s="5">
         <v>958009</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>462107</v>
+        <v>462163</v>
       </c>
       <c r="Z18" s="5">
-        <v>943287</v>
+        <v>943343</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.98463271221877868</v>
+        <v>0.98469116678444568</v>
       </c>
       <c r="AB18" s="5">
         <v>1463397</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>751015</v>
+        <v>751121</v>
       </c>
       <c r="AE18" s="5">
-        <v>1454773</v>
+        <v>1454879</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.9941068623210243</v>
+        <v>0.99417929652718984</v>
       </c>
       <c r="AG18" s="5">
         <v>959088</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>468992</v>
+        <v>469070</v>
       </c>
       <c r="AJ18" s="5">
-        <v>950963</v>
+        <v>951041</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99152841032314032</v>
+        <v>0.99160973758403814</v>
       </c>
       <c r="AL18" s="5">
         <v>980581</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>469975</v>
+        <v>470061</v>
       </c>
       <c r="AO18" s="5">
-        <v>963996</v>
+        <v>964082</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98308655786722365</v>
+        <v>0.98317426097385119</v>
       </c>
       <c r="AQ18" s="5">
         <v>1490329</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>752796</v>
+        <v>752954</v>
       </c>
       <c r="AT18" s="5">
-        <v>1485779</v>
+        <v>1485937</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99694698284741157</v>
+        <v>0.99705299970677619</v>
       </c>
       <c r="AV18" s="5">
         <v>983291</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>464748</v>
+        <v>464853</v>
       </c>
       <c r="AY18" s="5">
-        <v>974046</v>
+        <v>974151</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.9905979003163865</v>
+        <v>0.99070468457455629</v>
       </c>
       <c r="BA18" s="5">
         <v>1002255</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>472998</v>
+        <v>473118</v>
       </c>
       <c r="BD18" s="5">
-        <v>987511</v>
+        <v>987631</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98528917291507645</v>
+        <v>0.98540890292390659</v>
       </c>
       <c r="BF18" s="5">
         <v>1522890</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>808897</v>
+        <v>809130</v>
       </c>
       <c r="BI18" s="5">
-        <v>1512516</v>
+        <v>1512749</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99318795185469733</v>
+        <v>0.99334095042977499</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>185640</v>
+        <v>185660</v>
       </c>
       <c r="F19" s="5">
-        <v>271104</v>
+        <v>271124</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.98513417758316835</v>
+        <v>0.98520685332218971</v>
       </c>
       <c r="H19" s="5">
         <v>285702</v>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>189588</v>
+        <v>189612</v>
       </c>
       <c r="K19" s="5">
-        <v>277196</v>
+        <v>277220</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.9702277197919511</v>
+        <v>0.97031172340410643</v>
       </c>
       <c r="M19" s="5">
         <v>479092</v>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>327870</v>
+        <v>327921</v>
       </c>
       <c r="P19" s="5">
-        <v>470268</v>
+        <v>470319</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98158182562013141</v>
+        <v>0.98168827699064065</v>
       </c>
       <c r="R19" s="5">
         <v>279649</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>185503</v>
+        <v>185540</v>
       </c>
       <c r="U19" s="5">
-        <v>272320</v>
+        <v>272357</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97379214658375324</v>
+        <v>0.9739244552993217</v>
       </c>
       <c r="W19" s="5">
         <v>287758</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>188389</v>
+        <v>188428</v>
       </c>
       <c r="Z19" s="5">
-        <v>276619</v>
+        <v>276658</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96129038984146398</v>
+        <v>0.96142592039144004</v>
       </c>
       <c r="AB19" s="5">
         <v>485015</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>331798</v>
+        <v>331877</v>
       </c>
       <c r="AE19" s="5">
-        <v>476356</v>
+        <v>476435</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.9821469439089513</v>
+        <v>0.98230982546931533</v>
       </c>
       <c r="AG19" s="5">
         <v>283525</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>183997</v>
+        <v>184047</v>
       </c>
       <c r="AJ19" s="5">
-        <v>276389</v>
+        <v>276439</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97483114363812717</v>
+        <v>0.97500749492990035</v>
       </c>
       <c r="AL19" s="5">
         <v>295027</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>188045</v>
+        <v>188095</v>
       </c>
       <c r="AO19" s="5">
-        <v>281991</v>
+        <v>282041</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.95581421361434715</v>
+        <v>0.95598368962840685</v>
       </c>
       <c r="AQ19" s="5">
         <v>494059</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>335655</v>
+        <v>335748</v>
       </c>
       <c r="AT19" s="5">
-        <v>487794</v>
+        <v>487887</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.98731932825836588</v>
+        <v>0.98750756488597513</v>
       </c>
       <c r="AV19" s="5">
         <v>287237</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>185949</v>
+        <v>186005</v>
       </c>
       <c r="AY19" s="5">
-        <v>282939</v>
+        <v>282995</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98503674665868257</v>
+        <v>0.9852317076142697</v>
       </c>
       <c r="BA19" s="5">
         <v>298081</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>191176</v>
+        <v>191238</v>
       </c>
       <c r="BD19" s="5">
-        <v>287368</v>
+        <v>287430</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.96406010446824852</v>
+        <v>0.96426810162338428</v>
       </c>
       <c r="BF19" s="5">
         <v>503654</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>355306</v>
+        <v>355454</v>
       </c>
       <c r="BI19" s="5">
-        <v>493890</v>
+        <v>494038</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.98061367526119125</v>
+        <v>0.98090752778693313</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3532</v>
+        <v>3536</v>
       </c>
       <c r="F20" s="5">
-        <v>5788</v>
+        <v>5792</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>1.0255138199858256</v>
+        <v>1.0262225372076541</v>
       </c>
       <c r="H20" s="5">
         <v>5914</v>
@@ -3156,14 +3156,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3639</v>
+        <v>3643</v>
       </c>
       <c r="K20" s="5">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>1.0064254311802503</v>
+        <v>1.0071017923571186</v>
       </c>
       <c r="M20" s="5">
         <v>9037</v>
@@ -3173,14 +3173,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5715</v>
+        <v>5723</v>
       </c>
       <c r="P20" s="5">
-        <v>9282</v>
+        <v>9290</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>1.0271107668474051</v>
+        <v>1.0279960163771162</v>
       </c>
       <c r="R20" s="5">
         <v>5910</v>
@@ -3190,14 +3190,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3634</v>
+        <v>3640</v>
       </c>
       <c r="U20" s="5">
-        <v>6021</v>
+        <v>6027</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>1.0187817258883249</v>
+        <v>1.0197969543147207</v>
       </c>
       <c r="W20" s="5">
         <v>6115</v>
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>3717</v>
+        <v>3723</v>
       </c>
       <c r="Z20" s="5">
-        <v>6122</v>
+        <v>6128</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>1.0011447260834014</v>
+        <v>1.0021259198691741</v>
       </c>
       <c r="AB20" s="5">
         <v>9431</v>
@@ -3224,14 +3224,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>5777</v>
+        <v>5787</v>
       </c>
       <c r="AE20" s="5">
-        <v>9550</v>
+        <v>9560</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>1.0126179620400806</v>
+        <v>1.0136782949846252</v>
       </c>
       <c r="AG20" s="5">
         <v>6099</v>
@@ -3241,14 +3241,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3553</v>
+        <v>3560</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6143</v>
+        <v>6150</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>1.0072142974258076</v>
+        <v>1.0083620265617315</v>
       </c>
       <c r="AL20" s="5">
         <v>6250</v>
@@ -3258,14 +3258,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3429</v>
+        <v>3434</v>
       </c>
       <c r="AO20" s="5">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.99631999999999998</v>
+        <v>0.99712000000000001</v>
       </c>
       <c r="AQ20" s="5">
         <v>9632</v>
@@ -3275,14 +3275,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5960</v>
+        <v>5968</v>
       </c>
       <c r="AT20" s="5">
-        <v>9735</v>
+        <v>9743</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.0106935215946844</v>
+        <v>1.0115240863787376</v>
       </c>
       <c r="AV20" s="5">
         <v>6297</v>
@@ -3292,14 +3292,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>3616</v>
+        <v>3622</v>
       </c>
       <c r="AY20" s="5">
-        <v>6243</v>
+        <v>6249</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.99142448785135784</v>
+        <v>0.99237732253454025</v>
       </c>
       <c r="BA20" s="5">
         <v>6366</v>
@@ -3309,14 +3309,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3720</v>
+        <v>3727</v>
       </c>
       <c r="BD20" s="5">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.98711907005969213</v>
+        <v>0.9882186616399623</v>
       </c>
       <c r="BF20" s="5">
         <v>9853</v>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6349</v>
+        <v>6359</v>
       </c>
       <c r="BI20" s="5">
-        <v>9886</v>
+        <v>9896</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>1.003349233735918</v>
+        <v>1.0043641530498326</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3351,14 +3351,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>7617</v>
+        <v>7619</v>
       </c>
       <c r="F21" s="5">
-        <v>9834</v>
+        <v>9836</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.027478842336224</v>
+        <v>1.0276878069167277</v>
       </c>
       <c r="H21" s="5">
         <v>10057</v>
@@ -3368,14 +3368,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7258</v>
+        <v>7260</v>
       </c>
       <c r="K21" s="5">
-        <v>9975</v>
+        <v>9977</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99184647509197577</v>
+        <v>0.99204534155314705</v>
       </c>
       <c r="M21" s="5">
         <v>12982</v>
@@ -3385,14 +3385,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>9799</v>
+        <v>9806</v>
       </c>
       <c r="P21" s="5">
-        <v>13243</v>
+        <v>13250</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0201047604375288</v>
+        <v>1.0206439685718687</v>
       </c>
       <c r="R21" s="5">
         <v>9811</v>
@@ -3402,14 +3402,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>7321</v>
+        <v>7324</v>
       </c>
       <c r="U21" s="5">
-        <v>10035</v>
+        <v>10038</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0228315156457037</v>
+        <v>1.0231372948731017</v>
       </c>
       <c r="W21" s="5">
         <v>10152</v>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>7377</v>
+        <v>7383</v>
       </c>
       <c r="Z21" s="5">
-        <v>10168</v>
+        <v>10174</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0015760441292356</v>
+        <v>1.0021670606776989</v>
       </c>
       <c r="AB21" s="5">
         <v>13231</v>
@@ -3436,14 +3436,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>9716</v>
+        <v>9729</v>
       </c>
       <c r="AE21" s="5">
-        <v>13560</v>
+        <v>13573</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0248658453631623</v>
+        <v>1.025848386365354</v>
       </c>
       <c r="AG21" s="5">
         <v>10040</v>
@@ -3453,14 +3453,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>7386</v>
+        <v>7392</v>
       </c>
       <c r="AJ21" s="5">
-        <v>10240</v>
+        <v>10246</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0199203187250996</v>
+        <v>1.0205179282868526</v>
       </c>
       <c r="AL21" s="5">
         <v>10211</v>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7519</v>
       </c>
       <c r="AO21" s="5">
-        <v>10392</v>
+        <v>10398</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0177259817843503</v>
+        <v>1.0183135833904613</v>
       </c>
       <c r="AQ21" s="5">
         <v>13473</v>
@@ -3487,14 +3487,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10074</v>
+        <v>10087</v>
       </c>
       <c r="AT21" s="5">
-        <v>13888</v>
+        <v>13901</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.030802345431604</v>
+        <v>1.0317672381800638</v>
       </c>
       <c r="AV21" s="5">
         <v>10213</v>
@@ -3504,14 +3504,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>7689</v>
+        <v>7702</v>
       </c>
       <c r="AY21" s="5">
-        <v>10493</v>
+        <v>10506</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0274160383824538</v>
+        <v>1.0286889258787819</v>
       </c>
       <c r="BA21" s="5">
         <v>10449</v>
@@ -3521,14 +3521,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>7793</v>
+        <v>7808</v>
       </c>
       <c r="BD21" s="5">
-        <v>10631</v>
+        <v>10646</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0174179347305963</v>
+        <v>1.0188534788017991</v>
       </c>
       <c r="BF21" s="5">
         <v>13925</v>
@@ -3538,14 +3538,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>10868</v>
+        <v>10893</v>
       </c>
       <c r="BI21" s="5">
-        <v>14316</v>
+        <v>14341</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0280789946140036</v>
+        <v>1.0298743267504489</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4196</v>
+        <v>4200</v>
       </c>
       <c r="F22" s="5">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>1.0105536613086541</v>
+        <v>1.0112031173891864</v>
       </c>
       <c r="H22" s="5">
         <v>6265</v>
@@ -3580,14 +3580,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4366</v>
+        <v>4371</v>
       </c>
       <c r="K22" s="5">
-        <v>6309</v>
+        <v>6314</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.007023144453312</v>
+        <v>1.0078212290502793</v>
       </c>
       <c r="M22" s="5">
         <v>7537</v>
@@ -3597,14 +3597,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5098</v>
+        <v>5104</v>
       </c>
       <c r="P22" s="5">
-        <v>7606</v>
+        <v>7612</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0091548361417009</v>
+        <v>1.009950908849675</v>
       </c>
       <c r="R22" s="5">
         <v>6306</v>
@@ -3614,14 +3614,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4400</v>
+        <v>4407</v>
       </c>
       <c r="U22" s="5">
-        <v>6358</v>
+        <v>6365</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0082461148112909</v>
+        <v>1.0093561687281953</v>
       </c>
       <c r="W22" s="5">
         <v>6435</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4391</v>
+        <v>4398</v>
       </c>
       <c r="Z22" s="5">
-        <v>6433</v>
+        <v>6440</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99968919968919967</v>
+        <v>1.0007770007770007</v>
       </c>
       <c r="AB22" s="5">
         <v>7668</v>
@@ -3648,14 +3648,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5285</v>
+        <v>5295</v>
       </c>
       <c r="AE22" s="5">
-        <v>7712</v>
+        <v>7722</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0057381324986958</v>
+        <v>1.0070422535211268</v>
       </c>
       <c r="AG22" s="5">
         <v>6422</v>
@@ -3665,14 +3665,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4396</v>
+        <v>4406</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6448</v>
+        <v>6458</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0040485829959513</v>
+        <v>1.0056057303020867</v>
       </c>
       <c r="AL22" s="5">
         <v>6508</v>
@@ -3682,14 +3682,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4418</v>
+        <v>4428</v>
       </c>
       <c r="AO22" s="5">
-        <v>6498</v>
+        <v>6508</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>0.99846342962507684</v>
+        <v>1</v>
       </c>
       <c r="AQ22" s="5">
         <v>7781</v>
@@ -3699,14 +3699,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5388</v>
+        <v>5399</v>
       </c>
       <c r="AT22" s="5">
-        <v>7804</v>
+        <v>7815</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0029559182624341</v>
+        <v>1.0043696183009896</v>
       </c>
       <c r="AV22" s="5">
         <v>6603</v>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4465</v>
+        <v>4478</v>
       </c>
       <c r="AY22" s="5">
-        <v>6509</v>
+        <v>6522</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.98576404664546413</v>
+        <v>0.987732848705134</v>
       </c>
       <c r="BA22" s="5">
         <v>6608</v>
@@ -3733,14 +3733,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4405</v>
+        <v>4417</v>
       </c>
       <c r="BD22" s="5">
-        <v>6550</v>
+        <v>6562</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.99122276029055689</v>
+        <v>0.99303874092009681</v>
       </c>
       <c r="BF22" s="5">
         <v>7906</v>
@@ -3750,14 +3750,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5594</v>
+        <v>5607</v>
       </c>
       <c r="BI22" s="5">
-        <v>7942</v>
+        <v>7955</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>1.0045535036681001</v>
+        <v>1.0061978244371363</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>7368</v>
+        <v>7373</v>
       </c>
       <c r="F23" s="5">
-        <v>8487</v>
+        <v>8492</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.96443181818181822</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="H23" s="5">
         <v>8763</v>
@@ -3792,14 +3792,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7000</v>
+        <v>7007</v>
       </c>
       <c r="K23" s="5">
-        <v>8518</v>
+        <v>8525</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.97204153828597517</v>
+        <v>0.97284035147780445</v>
       </c>
       <c r="M23" s="5">
         <v>10654</v>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8119</v>
+        <v>8128</v>
       </c>
       <c r="P23" s="5">
-        <v>10504</v>
+        <v>10513</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98592078092735125</v>
+        <v>0.98676553407171019</v>
       </c>
       <c r="R23" s="5">
         <v>8621</v>
@@ -3826,14 +3826,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6396</v>
+        <v>6404</v>
       </c>
       <c r="U23" s="5">
-        <v>8385</v>
+        <v>8393</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.97262498550052201</v>
+        <v>0.97355295209372461</v>
       </c>
       <c r="W23" s="5">
         <v>8774</v>
@@ -3843,14 +3843,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6283</v>
+        <v>6294</v>
       </c>
       <c r="Z23" s="5">
-        <v>8439</v>
+        <v>8450</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.96181901071347164</v>
+        <v>0.96307271483929791</v>
       </c>
       <c r="AB23" s="5">
         <v>10734</v>
@@ -3860,14 +3860,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>7666</v>
+        <v>7676</v>
       </c>
       <c r="AE23" s="5">
-        <v>10571</v>
+        <v>10581</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98481460778833618</v>
+        <v>0.98574622694242597</v>
       </c>
       <c r="AG23" s="5">
         <v>8589</v>
@@ -3877,14 +3877,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6115</v>
+        <v>6124</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8438</v>
+        <v>8447</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.9824193736174176</v>
+        <v>0.98346722552101529</v>
       </c>
       <c r="AL23" s="5">
         <v>8660</v>
@@ -3894,14 +3894,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>5936</v>
+        <v>5946</v>
       </c>
       <c r="AO23" s="5">
-        <v>8510</v>
+        <v>8520</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.98267898383371821</v>
+        <v>0.9838337182448037</v>
       </c>
       <c r="AQ23" s="5">
         <v>10698</v>
@@ -3911,14 +3911,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>7634</v>
+        <v>7645</v>
       </c>
       <c r="AT23" s="5">
-        <v>10741</v>
+        <v>10752</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>1.0040194428865208</v>
+        <v>1.0050476724621424</v>
       </c>
       <c r="AV23" s="5">
         <v>8445</v>
@@ -3928,14 +3928,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6071</v>
+        <v>6083</v>
       </c>
       <c r="AY23" s="5">
-        <v>8491</v>
+        <v>8503</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>1.0054470100651274</v>
+        <v>1.0068679692125517</v>
       </c>
       <c r="BA23" s="5">
         <v>8623</v>
@@ -3945,14 +3945,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>5989</v>
+        <v>6001</v>
       </c>
       <c r="BD23" s="5">
-        <v>8538</v>
+        <v>8550</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.99014264177200506</v>
+        <v>0.9915342688159573</v>
       </c>
       <c r="BF23" s="5">
         <v>11023</v>
@@ -3962,14 +3962,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>7945</v>
+        <v>7960</v>
       </c>
       <c r="BI23" s="5">
-        <v>10923</v>
+        <v>10938</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.99092805951192964</v>
+        <v>0.99228885058514016</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4004,14 +4004,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>4250</v>
+        <v>4251</v>
       </c>
       <c r="K24" s="5">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.97088215024121294</v>
+        <v>0.9710544452101999</v>
       </c>
       <c r="M24" s="5">
         <v>6771</v>
@@ -4055,14 +4055,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4399</v>
+        <v>4401</v>
       </c>
       <c r="Z24" s="5">
-        <v>5806</v>
+        <v>5808</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.97991561181434594</v>
+        <v>0.98025316455696199</v>
       </c>
       <c r="AB24" s="5">
         <v>6940</v>
@@ -4072,14 +4072,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5236</v>
+        <v>5239</v>
       </c>
       <c r="AE24" s="5">
-        <v>6813</v>
+        <v>6816</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.981700288184438</v>
+        <v>0.98213256484149858</v>
       </c>
       <c r="AG24" s="5">
         <v>6076</v>
@@ -4089,14 +4089,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4619</v>
+        <v>4621</v>
       </c>
       <c r="AJ24" s="5">
-        <v>5951</v>
+        <v>5953</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.97942725477287684</v>
+        <v>0.97975641869651087</v>
       </c>
       <c r="AL24" s="5">
         <v>6181</v>
@@ -4106,14 +4106,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4435</v>
+        <v>4438</v>
       </c>
       <c r="AO24" s="5">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.97298171816858114</v>
+        <v>0.97346707652483422</v>
       </c>
       <c r="AQ24" s="5">
         <v>6974</v>
@@ -4123,14 +4123,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5465</v>
+        <v>5468</v>
       </c>
       <c r="AT24" s="5">
-        <v>6905</v>
+        <v>6908</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.99010610840263835</v>
+        <v>0.99053627760252361</v>
       </c>
       <c r="AV24" s="5">
         <v>6124</v>
@@ -4140,14 +4140,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>4694</v>
+        <v>4698</v>
       </c>
       <c r="AY24" s="5">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.98644676681907251</v>
+        <v>0.98709993468321355</v>
       </c>
       <c r="BA24" s="5">
         <v>6202</v>
@@ -4157,14 +4157,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>4723</v>
+        <v>4728</v>
       </c>
       <c r="BD24" s="5">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.98871331828442433</v>
+        <v>0.98951950983553694</v>
       </c>
       <c r="BF24" s="5">
         <v>7084</v>
@@ -4174,14 +4174,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>5548</v>
+        <v>5553</v>
       </c>
       <c r="BI24" s="5">
-        <v>7034</v>
+        <v>7039</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.99294184076792769</v>
+        <v>0.99364765669113497</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4199,14 +4199,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>10068</v>
+        <v>10072</v>
       </c>
       <c r="F25" s="5">
-        <v>18490</v>
+        <v>18494</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>1.0112666812513673</v>
+        <v>1.0114854517611025</v>
       </c>
       <c r="H25" s="5">
         <v>18682</v>
@@ -4216,14 +4216,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>10332</v>
+        <v>10337</v>
       </c>
       <c r="K25" s="5">
-        <v>18843</v>
+        <v>18848</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>1.0086179209934696</v>
+        <v>1.0088855582914036</v>
       </c>
       <c r="M25" s="5">
         <v>25970</v>
@@ -4233,14 +4233,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>14485</v>
+        <v>14496</v>
       </c>
       <c r="P25" s="5">
-        <v>26269</v>
+        <v>26280</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>1.0115132845591066</v>
+        <v>1.0119368502117829</v>
       </c>
       <c r="R25" s="5">
         <v>18895</v>
@@ -4250,14 +4250,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>10397</v>
+        <v>10405</v>
       </c>
       <c r="U25" s="5">
-        <v>19039</v>
+        <v>19047</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>1.007621063773485</v>
+        <v>1.0080444562053454</v>
       </c>
       <c r="W25" s="5">
         <v>19436</v>
@@ -4267,14 +4267,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>10758</v>
+        <v>10767</v>
       </c>
       <c r="Z25" s="5">
-        <v>19328</v>
+        <v>19337</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.9944433010907594</v>
+        <v>0.99490635933319616</v>
       </c>
       <c r="AB25" s="5">
         <v>26661</v>
@@ -4284,14 +4284,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>14610</v>
+        <v>14623</v>
       </c>
       <c r="AE25" s="5">
-        <v>26867</v>
+        <v>26880</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>1.0077266419114062</v>
+        <v>1.0082142455271745</v>
       </c>
       <c r="AG25" s="5">
         <v>19440</v>
@@ -4301,14 +4301,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>10475</v>
+        <v>10484</v>
       </c>
       <c r="AJ25" s="5">
-        <v>19505</v>
+        <v>19514</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>1.0033436213991769</v>
+        <v>1.00380658436214</v>
       </c>
       <c r="AL25" s="5">
         <v>19709</v>
@@ -4318,14 +4318,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>10522</v>
+        <v>10531</v>
       </c>
       <c r="AO25" s="5">
-        <v>19681</v>
+        <v>19690</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99857932924044857</v>
+        <v>0.99903597341316153</v>
       </c>
       <c r="AQ25" s="5">
         <v>27081</v>
@@ -4335,14 +4335,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>15486</v>
+        <v>15499</v>
       </c>
       <c r="AT25" s="5">
-        <v>27300</v>
+        <v>27313</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>1.0080868505594329</v>
+        <v>1.008566891916842</v>
       </c>
       <c r="AV25" s="5">
         <v>19795</v>
@@ -4352,14 +4352,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>10828</v>
+        <v>10837</v>
       </c>
       <c r="AY25" s="5">
-        <v>19913</v>
+        <v>19922</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>1.0059611012882042</v>
+        <v>1.0064157615559484</v>
       </c>
       <c r="BA25" s="5">
         <v>20139</v>
@@ -4369,14 +4369,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>11086</v>
+        <v>11096</v>
       </c>
       <c r="BD25" s="5">
-        <v>20137</v>
+        <v>20147</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.99990069020308858</v>
+        <v>1.0003972391876459</v>
       </c>
       <c r="BF25" s="5">
         <v>27639</v>
@@ -4386,14 +4386,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>16917</v>
+        <v>16936</v>
       </c>
       <c r="BI25" s="5">
-        <v>27787</v>
+        <v>27806</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>1.0053547523427042</v>
+        <v>1.0060421867650784</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4411,14 +4411,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>8939</v>
+        <v>8941</v>
       </c>
       <c r="F26" s="5">
-        <v>13317</v>
+        <v>13319</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.98389360916143331</v>
+        <v>0.98404137421499815</v>
       </c>
       <c r="H26" s="5">
         <v>13884</v>
@@ -4428,14 +4428,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9406</v>
+        <v>9408</v>
       </c>
       <c r="K26" s="5">
-        <v>13912</v>
+        <v>13914</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>1.0020167098818784</v>
+        <v>1.002160760587727</v>
       </c>
       <c r="M26" s="5">
         <v>25920</v>
@@ -4445,14 +4445,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>17754</v>
+        <v>17762</v>
       </c>
       <c r="P26" s="5">
-        <v>26333</v>
+        <v>26341</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>1.0159336419753087</v>
+        <v>1.0162422839506173</v>
       </c>
       <c r="R26" s="5">
         <v>13869</v>
@@ -4462,14 +4462,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9520</v>
+        <v>9527</v>
       </c>
       <c r="U26" s="5">
-        <v>14110</v>
+        <v>14117</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>1.0173768836974548</v>
+        <v>1.0178816064604514</v>
       </c>
       <c r="W26" s="5">
         <v>14474</v>
@@ -4479,14 +4479,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9558</v>
+        <v>9566</v>
       </c>
       <c r="Z26" s="5">
-        <v>14416</v>
+        <v>14424</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.99599281470222467</v>
+        <v>0.99654552991571088</v>
       </c>
       <c r="AB26" s="5">
         <v>27035</v>
@@ -4496,14 +4496,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>18132</v>
+        <v>18146</v>
       </c>
       <c r="AE26" s="5">
-        <v>27000</v>
+        <v>27014</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.99870538191233582</v>
+        <v>0.99922322914740147</v>
       </c>
       <c r="AG26" s="5">
         <v>14053</v>
@@ -4513,14 +4513,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9380</v>
+        <v>9388</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14048</v>
+        <v>14056</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.99964420408453714</v>
+        <v>1.0002134775492777</v>
       </c>
       <c r="AL26" s="5">
         <v>14372</v>
@@ -4530,14 +4530,14 @@
       </c>
       <c r="AN26" s="3">
         <f>AO26-AM26</f>
-        <v>9101</v>
+        <v>9109</v>
       </c>
       <c r="AO26" s="5">
-        <v>14209</v>
+        <v>14217</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.9886585026440301</v>
+        <v>0.98921514055107151</v>
       </c>
       <c r="AQ26" s="5">
         <v>27267</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="AS26" s="3">
         <f>AT26-AR26</f>
-        <v>19103</v>
+        <v>19120</v>
       </c>
       <c r="AT26" s="5">
-        <v>27102</v>
+        <v>27119</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99394872923313893</v>
+        <v>0.99457219349396708</v>
       </c>
       <c r="AV26" s="5">
         <v>14007</v>
@@ -4564,14 +4564,14 @@
       </c>
       <c r="AX26" s="3">
         <f>AY26-AW26</f>
-        <v>9369</v>
+        <v>9378</v>
       </c>
       <c r="AY26" s="5">
-        <v>13975</v>
+        <v>13984</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99771542800028556</v>
+        <v>0.99835796387520526</v>
       </c>
       <c r="BA26" s="5">
         <v>14398</v>
@@ -4581,14 +4581,14 @@
       </c>
       <c r="BC26" s="3">
         <f>BD26-BB26</f>
-        <v>9276</v>
+        <v>9285</v>
       </c>
       <c r="BD26" s="5">
-        <v>14070</v>
+        <v>14079</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97721905820252808</v>
+        <v>0.97784414502014172</v>
       </c>
       <c r="BF26" s="5">
         <v>27339</v>
@@ -4598,14 +4598,14 @@
       </c>
       <c r="BH26" s="3">
         <f>BI26-BG26</f>
-        <v>19164</v>
+        <v>19185</v>
       </c>
       <c r="BI26" s="5">
-        <v>27117</v>
+        <v>27138</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99187973225063097</v>
+        <v>0.99264786568638208</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>74091</v>
+        <v>74114</v>
       </c>
       <c r="F27" s="5">
-        <v>120682</v>
+        <v>120705</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>1.0016599990040005</v>
+        <v>1.0018508988894608</v>
       </c>
       <c r="H27" s="5">
         <v>123649</v>
@@ -4640,14 +4640,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>75115</v>
+        <v>75146</v>
       </c>
       <c r="K27" s="5">
-        <v>122537</v>
+        <v>122568</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.99100680151072795</v>
+        <v>0.9912575111808426</v>
       </c>
       <c r="M27" s="5">
         <v>182121</v>
@@ -4657,14 +4657,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>115152</v>
+        <v>115197</v>
       </c>
       <c r="P27" s="5">
-        <v>181362</v>
+        <v>181407</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99583244106939894</v>
+        <v>0.99607952954354517</v>
       </c>
       <c r="R27" s="5">
         <v>122848</v>
@@ -4674,14 +4674,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>73615</v>
+        <v>73647</v>
       </c>
       <c r="U27" s="5">
-        <v>121940</v>
+        <v>121972</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99260875227923939</v>
+        <v>0.99286923678041161</v>
       </c>
       <c r="W27" s="5">
         <v>125846</v>
@@ -4691,14 +4691,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>74910</v>
+        <v>74942</v>
       </c>
       <c r="Z27" s="5">
-        <v>123293</v>
+        <v>123325</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97971330038300786</v>
+        <v>0.9799675794224687</v>
       </c>
       <c r="AB27" s="5">
         <v>184102</v>
@@ -4708,14 +4708,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>113284</v>
+        <v>113341</v>
       </c>
       <c r="AE27" s="5">
-        <v>183094</v>
+        <v>183151</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99452477430989339</v>
+        <v>0.99483438528641732</v>
       </c>
       <c r="AG27" s="5">
         <v>124176</v>
@@ -4725,14 +4725,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>72843</v>
+        <v>72885</v>
       </c>
       <c r="AJ27" s="5">
-        <v>123106</v>
+        <v>123148</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99138319804148944</v>
+        <v>0.99172142765107585</v>
       </c>
       <c r="AL27" s="5">
         <v>126536</v>
@@ -4742,14 +4742,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" ref="AN27:AN33" si="24">AO27-AM27</f>
-        <v>73975</v>
+        <v>74019</v>
       </c>
       <c r="AO27" s="5">
-        <v>124039</v>
+        <v>124083</v>
       </c>
       <c r="AP27" s="4">
         <f>AO27/AL27</f>
-        <v>0.98026648542707218</v>
+        <v>0.98061421255611048</v>
       </c>
       <c r="AQ27" s="5">
         <v>184835</v>
@@ -4759,14 +4759,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" ref="AS27:AS33" si="25">AT27-AR27</f>
-        <v>115132</v>
+        <v>115215</v>
       </c>
       <c r="AT27" s="5">
-        <v>184585</v>
+        <v>184668</v>
       </c>
       <c r="AU27" s="4">
         <f>AT27/AQ27</f>
-        <v>0.99864744231341462</v>
+        <v>0.99909649146536095</v>
       </c>
       <c r="AV27" s="5">
         <v>124975</v>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" ref="AX27:AX33" si="26">AY27-AW27</f>
-        <v>73548</v>
+        <v>73612</v>
       </c>
       <c r="AY27" s="5">
-        <v>124133</v>
+        <v>124197</v>
       </c>
       <c r="AZ27" s="4">
         <f>AY27/AV27</f>
-        <v>0.99326265253050605</v>
+        <v>0.99377475495099021</v>
       </c>
       <c r="BA27" s="5">
         <v>127493</v>
@@ -4793,14 +4793,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" ref="BC27:BC33" si="27">BD27-BB27</f>
-        <v>74160</v>
+        <v>74233</v>
       </c>
       <c r="BD27" s="5">
-        <v>125254</v>
+        <v>125327</v>
       </c>
       <c r="BE27" s="4">
         <f>BD27/BA27</f>
-        <v>0.98243825151184772</v>
+        <v>0.98301083196724526</v>
       </c>
       <c r="BF27" s="5">
         <v>187636</v>
@@ -4810,14 +4810,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>121434</v>
+        <v>121561</v>
       </c>
       <c r="BI27" s="5">
-        <v>185982</v>
+        <v>186109</v>
       </c>
       <c r="BJ27" s="4">
         <f>BI27/BF27</f>
-        <v>0.99118506043616361</v>
+        <v>0.99186190283314501</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4835,14 +4835,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>164947</v>
+        <v>164960</v>
       </c>
       <c r="F28" s="5">
-        <v>379820</v>
+        <v>379833</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99375209310113866</v>
+        <v>0.99378610599464168</v>
       </c>
       <c r="H28" s="5">
         <v>389922</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>167341</v>
+        <v>167360</v>
       </c>
       <c r="K28" s="5">
-        <v>384950</v>
+        <v>384969</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.98724873179764161</v>
+        <v>0.9872974594918984</v>
       </c>
       <c r="M28" s="5">
         <v>650891</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>302099</v>
+        <v>302130</v>
       </c>
       <c r="P28" s="5">
-        <v>646803</v>
+        <v>646834</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99371937851345304</v>
+        <v>0.99376700553548902</v>
       </c>
       <c r="R28" s="5">
         <v>389073</v>
@@ -4886,14 +4886,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>169096</v>
+        <v>169117</v>
       </c>
       <c r="U28" s="5">
-        <v>386309</v>
+        <v>386330</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99289593469605963</v>
+        <v>0.99294990914301429</v>
       </c>
       <c r="W28" s="5">
         <v>397763</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>171181</v>
+        <v>171203</v>
       </c>
       <c r="Z28" s="5">
-        <v>391681</v>
+        <v>391703</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.98470948781058065</v>
+        <v>0.98476479712793796</v>
       </c>
       <c r="AB28" s="5">
         <v>660941</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>292763</v>
+        <v>292806</v>
       </c>
       <c r="AE28" s="5">
-        <v>657401</v>
+        <v>657444</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99464399999394804</v>
+        <v>0.99470905875108373</v>
       </c>
       <c r="AG28" s="5">
         <v>397417</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>163386</v>
+        <v>163418</v>
       </c>
       <c r="AJ28" s="5">
-        <v>394399</v>
+        <v>394431</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.99240596149636273</v>
+        <v>0.9924864814539891</v>
       </c>
       <c r="AL28" s="5">
         <v>405895</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="24"/>
-        <v>168474</v>
+        <v>168516</v>
       </c>
       <c r="AO28" s="5">
-        <v>398789</v>
+        <v>398831</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" ref="AP28:AP33" si="28">AO28/AL28</f>
-        <v>0.98249300927579797</v>
+        <v>0.98259648431244528</v>
       </c>
       <c r="AQ28" s="5">
         <v>670091</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="25"/>
-        <v>295900</v>
+        <v>295962</v>
       </c>
       <c r="AT28" s="5">
-        <v>667028</v>
+        <v>667090</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" ref="AU28:AU33" si="29">AT28/AQ28</f>
-        <v>0.9954289790491142</v>
+        <v>0.9955215037957531</v>
       </c>
       <c r="AV28" s="5">
         <v>405395</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="26"/>
-        <v>166442</v>
+        <v>166492</v>
       </c>
       <c r="AY28" s="5">
-        <v>402145</v>
+        <v>402195</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" ref="AZ28:AZ33" si="30">AY28/AV28</f>
-        <v>0.99198312756694085</v>
+        <v>0.99210646406591108</v>
       </c>
       <c r="BA28" s="5">
         <v>412255</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="27"/>
-        <v>167675</v>
+        <v>167728</v>
       </c>
       <c r="BD28" s="5">
-        <v>406681</v>
+        <v>406734</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" ref="BE28:BE33" si="31">BD28/BA28</f>
-        <v>0.98647924221658922</v>
+        <v>0.98660780342263887</v>
       </c>
       <c r="BF28" s="5">
         <v>680839</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>320635</v>
+        <v>320735</v>
       </c>
       <c r="BI28" s="5">
-        <v>677323</v>
+        <v>677423</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99483578349653878</v>
+        <v>0.99498266109902633</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>65985</v>
+        <v>65990</v>
       </c>
       <c r="F29" s="5">
-        <v>126979</v>
+        <v>126984</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99546869242769898</v>
+        <v>0.99550789059008915</v>
       </c>
       <c r="H29" s="5">
         <v>129829</v>
@@ -5064,14 +5064,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>67250</v>
+        <v>67259</v>
       </c>
       <c r="K29" s="5">
-        <v>128358</v>
+        <v>128367</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98866971169769469</v>
+        <v>0.98873903365195759</v>
       </c>
       <c r="M29" s="5">
         <v>176637</v>
@@ -5081,14 +5081,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>93963</v>
+        <v>93975</v>
       </c>
       <c r="P29" s="5">
-        <v>174556</v>
+        <v>174568</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98821877636055866</v>
+        <v>0.98828671229697063</v>
       </c>
       <c r="R29" s="5">
         <v>129740</v>
@@ -5098,14 +5098,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>67073</v>
+        <v>67082</v>
       </c>
       <c r="U29" s="5">
-        <v>128513</v>
+        <v>128522</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.9905426237089564</v>
+        <v>0.99061199321720361</v>
       </c>
       <c r="W29" s="5">
         <v>131766</v>
@@ -5115,14 +5115,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>67090</v>
+        <v>67103</v>
       </c>
       <c r="Z29" s="5">
-        <v>129596</v>
+        <v>129609</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.9835314117450632</v>
+        <v>0.9836300714903693</v>
       </c>
       <c r="AB29" s="5">
         <v>178083</v>
@@ -5132,14 +5132,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>93866</v>
+        <v>93885</v>
       </c>
       <c r="AE29" s="5">
-        <v>176647</v>
+        <v>176666</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.99193634428889899</v>
+        <v>0.99204303611237454</v>
       </c>
       <c r="AG29" s="5">
         <v>131984</v>
@@ -5149,14 +5149,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>68223</v>
+        <v>68240</v>
       </c>
       <c r="AJ29" s="5">
-        <v>130608</v>
+        <v>130625</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98957449387804586</v>
+        <v>0.98970329736937812</v>
       </c>
       <c r="AL29" s="5">
         <v>133676</v>
@@ -5166,14 +5166,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="24"/>
-        <v>68562</v>
+        <v>68583</v>
       </c>
       <c r="AO29" s="5">
-        <v>131832</v>
+        <v>131853</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="28"/>
-        <v>0.98620545198838983</v>
+        <v>0.9863625482509949</v>
       </c>
       <c r="AQ29" s="5">
         <v>179800</v>
@@ -5183,14 +5183,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="25"/>
-        <v>93871</v>
+        <v>93900</v>
       </c>
       <c r="AT29" s="5">
-        <v>179236</v>
+        <v>179265</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="29"/>
-        <v>0.99686318131256957</v>
+        <v>0.99702447163515018</v>
       </c>
       <c r="AV29" s="5">
         <v>134089</v>
@@ -5200,14 +5200,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="26"/>
-        <v>66885</v>
+        <v>66907</v>
       </c>
       <c r="AY29" s="5">
-        <v>133017</v>
+        <v>133039</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="30"/>
-        <v>0.99200530990610714</v>
+        <v>0.99216938003863109</v>
       </c>
       <c r="BA29" s="5">
         <v>136058</v>
@@ -5217,14 +5217,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="27"/>
-        <v>68586</v>
+        <v>68606</v>
       </c>
       <c r="BD29" s="5">
-        <v>134413</v>
+        <v>134433</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="31"/>
-        <v>0.98790956797836216</v>
+        <v>0.98805656411236387</v>
       </c>
       <c r="BF29" s="5">
         <v>182623</v>
@@ -5234,14 +5234,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>100450</v>
+        <v>100480</v>
       </c>
       <c r="BI29" s="5">
-        <v>181725</v>
+        <v>181755</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.99508276613570035</v>
+        <v>0.99524703898194644</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5259,14 +5259,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>95626</v>
+        <v>95638</v>
       </c>
       <c r="F30" s="5">
-        <v>166210</v>
+        <v>166222</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99590159023092506</v>
+        <v>0.99597349215669828</v>
       </c>
       <c r="H30" s="5">
         <v>172134</v>
@@ -5276,14 +5276,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>97064</v>
+        <v>97076</v>
       </c>
       <c r="K30" s="5">
-        <v>169415</v>
+        <v>169427</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98420416652143095</v>
+        <v>0.98427387965189905</v>
       </c>
       <c r="M30" s="5">
         <v>289249</v>
@@ -5293,14 +5293,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>172685</v>
+        <v>172711</v>
       </c>
       <c r="P30" s="5">
-        <v>286716</v>
+        <v>286742</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.99124283921465584</v>
+        <v>0.99133272716586751</v>
       </c>
       <c r="R30" s="5">
         <v>169142</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>95674</v>
+        <v>95690</v>
       </c>
       <c r="U30" s="5">
-        <v>167632</v>
+        <v>167648</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99107258989488123</v>
+        <v>0.99116718496884271</v>
       </c>
       <c r="W30" s="5">
         <v>174259</v>
@@ -5327,14 +5327,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>95191</v>
+        <v>95210</v>
       </c>
       <c r="Z30" s="5">
-        <v>170767</v>
+        <v>170786</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97996086285356854</v>
+        <v>0.98006989595946259</v>
       </c>
       <c r="AB30" s="5">
         <v>293307</v>
@@ -5344,14 +5344,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>173181</v>
+        <v>173225</v>
       </c>
       <c r="AE30" s="5">
-        <v>291106</v>
+        <v>291150</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.9924959172471165</v>
+        <v>0.99264593071423457</v>
       </c>
       <c r="AG30" s="5">
         <v>172053</v>
@@ -5361,14 +5361,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>94730</v>
+        <v>94757</v>
       </c>
       <c r="AJ30" s="5">
-        <v>170758</v>
+        <v>170785</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.9924732495219496</v>
+        <v>0.99263017791029506</v>
       </c>
       <c r="AL30" s="5">
         <v>176835</v>
@@ -5378,14 +5378,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="24"/>
-        <v>96529</v>
+        <v>96562</v>
       </c>
       <c r="AO30" s="5">
-        <v>173477</v>
+        <v>173510</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="28"/>
-        <v>0.98101054655469788</v>
+        <v>0.98119716119546474</v>
       </c>
       <c r="AQ30" s="5">
         <v>297651</v>
@@ -5395,14 +5395,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="25"/>
-        <v>175529</v>
+        <v>175594</v>
       </c>
       <c r="AT30" s="5">
-        <v>296745</v>
+        <v>296810</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="29"/>
-        <v>0.99695616678593391</v>
+        <v>0.99717454334102695</v>
       </c>
       <c r="AV30" s="5">
         <v>175428</v>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="26"/>
-        <v>96802</v>
+        <v>96837</v>
       </c>
       <c r="AY30" s="5">
-        <v>174037</v>
+        <v>174072</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="30"/>
-        <v>0.99207082107759303</v>
+        <v>0.99227033312812096</v>
       </c>
       <c r="BA30" s="5">
         <v>179593</v>
@@ -5429,14 +5429,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="27"/>
-        <v>98749</v>
+        <v>98788</v>
       </c>
       <c r="BD30" s="5">
-        <v>176011</v>
+        <v>176050</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="31"/>
-        <v>0.98005490191711253</v>
+        <v>0.98027205960143216</v>
       </c>
       <c r="BF30" s="5">
         <v>302258</v>
@@ -5446,14 +5446,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>184983</v>
+        <v>185063</v>
       </c>
       <c r="BI30" s="5">
-        <v>300016</v>
+        <v>300096</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99258249574866508</v>
+        <v>0.992847170298222</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35548</v>
+        <v>35551</v>
       </c>
       <c r="F31" s="5">
-        <v>74328</v>
+        <v>74331</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>0.99755737484901352</v>
+        <v>0.9975976379009529</v>
       </c>
       <c r="H31" s="5">
         <v>76671</v>
@@ -5488,14 +5488,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35324</v>
+        <v>35328</v>
       </c>
       <c r="K31" s="5">
-        <v>75508</v>
+        <v>75512</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.98483129214435705</v>
+        <v>0.98488346310860686</v>
       </c>
       <c r="M31" s="5">
         <v>133745</v>
@@ -5505,14 +5505,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>70002</v>
+        <v>70011</v>
       </c>
       <c r="P31" s="5">
-        <v>133836</v>
+        <v>133845</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0006803992672624</v>
+        <v>1.000747691502486</v>
       </c>
       <c r="R31" s="5">
         <v>74974</v>
@@ -5522,14 +5522,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34155</v>
+        <v>34161</v>
       </c>
       <c r="U31" s="5">
-        <v>74774</v>
+        <v>74780</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>0.99733240856830363</v>
+        <v>0.99741243631125454</v>
       </c>
       <c r="W31" s="5">
         <v>77586</v>
@@ -5539,14 +5539,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>34632</v>
+        <v>34637</v>
       </c>
       <c r="Z31" s="5">
-        <v>75890</v>
+        <v>75895</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.97814038615214083</v>
+        <v>0.97820483076843756</v>
       </c>
       <c r="AB31" s="5">
         <v>135116</v>
@@ -5556,14 +5556,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>70298</v>
+        <v>70311</v>
       </c>
       <c r="AE31" s="5">
-        <v>135411</v>
+        <v>135424</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0021833091565766</v>
+        <v>1.0022795227804258</v>
       </c>
       <c r="AG31" s="5">
         <v>76230</v>
@@ -5573,14 +5573,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>33295</v>
+        <v>33309</v>
       </c>
       <c r="AJ31" s="5">
-        <v>75660</v>
+        <v>75674</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>0.9925226288862653</v>
+        <v>0.9927062836153745</v>
       </c>
       <c r="AL31" s="5">
         <v>77611</v>
@@ -5590,14 +5590,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="24"/>
-        <v>33376</v>
+        <v>33392</v>
       </c>
       <c r="AO31" s="5">
-        <v>76698</v>
+        <v>76714</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="28"/>
-        <v>0.98823620363092857</v>
+        <v>0.98844235997474583</v>
       </c>
       <c r="AQ31" s="5">
         <v>136879</v>
@@ -5607,14 +5607,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="25"/>
-        <v>69294</v>
+        <v>69314</v>
       </c>
       <c r="AT31" s="5">
-        <v>137656</v>
+        <v>137676</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="29"/>
-        <v>1.0056765464388255</v>
+        <v>1.0058226608902754</v>
       </c>
       <c r="AV31" s="5">
         <v>76719</v>
@@ -5624,14 +5624,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="26"/>
-        <v>33118</v>
+        <v>33132</v>
       </c>
       <c r="AY31" s="5">
-        <v>76681</v>
+        <v>76695</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="30"/>
-        <v>0.99950468593177699</v>
+        <v>0.999687170062175</v>
       </c>
       <c r="BA31" s="5">
         <v>78720</v>
@@ -5641,14 +5641,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="27"/>
-        <v>33776</v>
+        <v>33792</v>
       </c>
       <c r="BD31" s="5">
-        <v>78189</v>
+        <v>78205</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="31"/>
-        <v>0.99325457317073174</v>
+        <v>0.99345782520325199</v>
       </c>
       <c r="BF31" s="5">
         <v>140181</v>
@@ -5658,14 +5658,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>76219</v>
+        <v>76253</v>
       </c>
       <c r="BI31" s="5">
-        <v>140452</v>
+        <v>140486</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.0019332149150026</v>
+        <v>1.0021757584836746</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5683,14 +5683,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>93775</v>
+        <v>93780</v>
       </c>
       <c r="F32" s="5">
-        <v>202827</v>
+        <v>202832</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99562630695373011</v>
+        <v>0.99565085068575188</v>
       </c>
       <c r="H32" s="5">
         <v>210874</v>
@@ -5700,14 +5700,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>94704</v>
+        <v>94714</v>
       </c>
       <c r="K32" s="5">
-        <v>207273</v>
+        <v>207283</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98292345191915553</v>
+        <v>0.98297087360224589</v>
       </c>
       <c r="M32" s="5">
         <v>441035</v>
@@ -5717,14 +5717,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>233968</v>
+        <v>233990</v>
       </c>
       <c r="P32" s="5">
-        <v>439402</v>
+        <v>439424</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99629734601562236</v>
+        <v>0.99634722867799608</v>
       </c>
       <c r="R32" s="5">
         <v>206418</v>
@@ -5734,14 +5734,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>92285</v>
+        <v>92298</v>
       </c>
       <c r="U32" s="5">
-        <v>204361</v>
+        <v>204374</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99003478378823551</v>
+        <v>0.99009776279200457</v>
       </c>
       <c r="W32" s="5">
         <v>212709</v>
@@ -5751,14 +5751,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>95908</v>
+        <v>95923</v>
       </c>
       <c r="Z32" s="5">
-        <v>208777</v>
+        <v>208792</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.98151465147219907</v>
+        <v>0.98158517035010273</v>
       </c>
       <c r="AB32" s="5">
         <v>446806</v>
@@ -5768,14 +5768,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>237799</v>
+        <v>237840</v>
       </c>
       <c r="AE32" s="5">
-        <v>445827</v>
+        <v>445868</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99780889244996707</v>
+        <v>0.9979006548703464</v>
       </c>
       <c r="AG32" s="5">
         <v>210129</v>
@@ -5785,14 +5785,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>92529</v>
+        <v>92551</v>
       </c>
       <c r="AJ32" s="5">
-        <v>208755</v>
+        <v>208777</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99346115957340486</v>
+        <v>0.99356585716393264</v>
       </c>
       <c r="AL32" s="5">
         <v>217332</v>
@@ -5802,14 +5802,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="24"/>
-        <v>93027</v>
+        <v>93050</v>
       </c>
       <c r="AO32" s="5">
-        <v>212362</v>
+        <v>212385</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="28"/>
-        <v>0.97713176154454939</v>
+        <v>0.97723759041466507</v>
       </c>
       <c r="AQ32" s="5">
         <v>453805</v>
@@ -5819,14 +5819,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="25"/>
-        <v>229472</v>
+        <v>229524</v>
       </c>
       <c r="AT32" s="5">
-        <v>453586</v>
+        <v>453638</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="29"/>
-        <v>0.99951741386718962</v>
+        <v>0.99963200052886148</v>
       </c>
       <c r="AV32" s="5">
         <v>213428</v>
@@ -5836,14 +5836,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="26"/>
-        <v>91537</v>
+        <v>91562</v>
       </c>
       <c r="AY32" s="5">
-        <v>212564</v>
+        <v>212589</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="30"/>
-        <v>0.99595179639035181</v>
+        <v>0.99606893191146428</v>
       </c>
       <c r="BA32" s="5">
         <v>220509</v>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="27"/>
-        <v>94352</v>
+        <v>94375</v>
       </c>
       <c r="BD32" s="5">
-        <v>217082</v>
+        <v>217105</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="31"/>
-        <v>0.98445868422604066</v>
+        <v>0.98456298835875178</v>
       </c>
       <c r="BF32" s="5">
         <v>463937</v>
@@ -5870,14 +5870,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>253871</v>
+        <v>253933</v>
       </c>
       <c r="BI32" s="5">
-        <v>461845</v>
+        <v>461907</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99549076706535589</v>
+        <v>0.99562440589993895</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5895,14 +5895,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>96262</v>
+        <v>96267</v>
       </c>
       <c r="F33" s="5">
-        <v>620521</v>
+        <v>620526</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99923670883018378</v>
+        <v>0.99924476042480215</v>
       </c>
       <c r="H33" s="5">
         <v>630476</v>
@@ -5912,14 +5912,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="K33" s="5">
-        <v>628330</v>
+        <v>628335</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99659622253662317</v>
+        <v>0.99660415305261418</v>
       </c>
       <c r="M33" s="5">
         <v>1032030</v>
@@ -5929,14 +5929,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>184034</v>
+        <v>184047</v>
       </c>
       <c r="P33" s="5">
-        <v>1033734</v>
+        <v>1033747</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0016511147931746</v>
+        <v>1.0016637113262212</v>
       </c>
       <c r="R33" s="5">
         <v>629419</v>
@@ -5946,14 +5946,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>97163</v>
+        <v>97170</v>
       </c>
       <c r="U33" s="5">
-        <v>627889</v>
+        <v>627896</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>0.99756918682149731</v>
+        <v>0.99758030818898058</v>
       </c>
       <c r="W33" s="5">
         <v>637378</v>
@@ -5963,14 +5963,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>101387</v>
+        <v>101396</v>
       </c>
       <c r="Z33" s="5">
-        <v>634247</v>
+        <v>634256</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99508768736919062</v>
+        <v>0.99510180771849677</v>
       </c>
       <c r="AB33" s="5">
         <v>1041984</v>
@@ -5980,14 +5980,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>184387</v>
+        <v>184406</v>
       </c>
       <c r="AE33" s="5">
-        <v>1043566</v>
+        <v>1043585</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0015182574780419</v>
+        <v>1.0015364919231005</v>
       </c>
       <c r="AG33" s="5">
         <v>638215</v>
@@ -5997,14 +5997,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>78003</v>
+        <v>78014</v>
       </c>
       <c r="AJ33" s="5">
-        <v>637042</v>
+        <v>637053</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>0.99816206137430175</v>
+        <v>0.99817929694538676</v>
       </c>
       <c r="AL33" s="5">
         <v>645318</v>
@@ -6014,14 +6014,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="24"/>
-        <v>94780</v>
+        <v>94792</v>
       </c>
       <c r="AO33" s="5">
-        <v>641685</v>
+        <v>641697</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="28"/>
-        <v>0.99437021747417553</v>
+        <v>0.99438881295733261</v>
       </c>
       <c r="AQ33" s="5">
         <v>1053133</v>
@@ -6031,14 +6031,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="25"/>
-        <v>167698</v>
+        <v>167717</v>
       </c>
       <c r="AT33" s="5">
-        <v>1055154</v>
+        <v>1055173</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="29"/>
-        <v>1.0019190358672647</v>
+        <v>1.001937077273241</v>
       </c>
       <c r="AV33" s="5">
         <v>647979</v>
@@ -6048,14 +6048,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="26"/>
-        <v>89164</v>
+        <v>89176</v>
       </c>
       <c r="AY33" s="5">
-        <v>647867</v>
+        <v>647879</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="30"/>
-        <v>0.99982715489236529</v>
+        <v>0.99984567401104052</v>
       </c>
       <c r="BA33" s="5">
         <v>657743</v>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="27"/>
-        <v>89562</v>
+        <v>89579</v>
       </c>
       <c r="BD33" s="5">
-        <v>657167</v>
+        <v>657184</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="31"/>
-        <v>0.99912427802348336</v>
+        <v>0.99915012398459579</v>
       </c>
       <c r="BF33" s="5">
         <v>1071541</v>
@@ -6082,14 +6082,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>189745</v>
+        <v>189767</v>
       </c>
       <c r="BI33" s="5">
-        <v>1072541</v>
+        <v>1072563</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0009332354058313</v>
+        <v>1.0009537665847597</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6507,14 +6507,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>253962</v>
+        <v>253983</v>
       </c>
       <c r="F36" s="5">
-        <v>833161</v>
+        <v>833182</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.99655996086297616</v>
+        <v>0.99658507936849683</v>
       </c>
       <c r="H36" s="5">
         <v>854298</v>
@@ -6524,14 +6524,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="32"/>
-        <v>261227</v>
+        <v>261255</v>
       </c>
       <c r="K36" s="5">
-        <v>843317</v>
+        <v>843345</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98714617147646366</v>
+        <v>0.98717894692484354</v>
       </c>
       <c r="M36" s="5">
         <v>1510524</v>
@@ -6541,14 +6541,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="34"/>
-        <v>489781</v>
+        <v>489829</v>
       </c>
       <c r="P36" s="5">
-        <v>1504172</v>
+        <v>1504220</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99579483675863478</v>
+        <v>0.99582661381083648</v>
       </c>
       <c r="R36" s="5">
         <v>845008</v>
@@ -6558,14 +6558,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="36"/>
-        <v>248777</v>
+        <v>248819</v>
       </c>
       <c r="U36" s="5">
-        <v>839743</v>
+        <v>839785</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99376928975820344</v>
+        <v>0.99381899342964797</v>
       </c>
       <c r="W36" s="5">
         <v>865288</v>
@@ -6575,14 +6575,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="38"/>
-        <v>251330</v>
+        <v>251371</v>
       </c>
       <c r="Z36" s="5">
-        <v>849415</v>
+        <v>849456</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98165581864073004</v>
+        <v>0.98170320170856407</v>
       </c>
       <c r="AB36" s="5">
         <v>1522408</v>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="40"/>
-        <v>485882</v>
+        <v>485962</v>
       </c>
       <c r="AE36" s="5">
-        <v>1517852</v>
+        <v>1517932</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="41"/>
-        <v>0.99700737253088523</v>
+        <v>0.99705992086221307</v>
       </c>
       <c r="AG36" s="5">
         <v>860909</v>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="42"/>
-        <v>232858</v>
+        <v>232908</v>
       </c>
       <c r="AJ36" s="5">
-        <v>855751</v>
+        <v>855801</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="43"/>
-        <v>0.99400865829024898</v>
+        <v>0.99406673643788135</v>
       </c>
       <c r="AL36" s="5">
         <v>879793</v>
@@ -6626,14 +6626,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="44"/>
-        <v>238495</v>
+        <v>238547</v>
       </c>
       <c r="AO36" s="5">
-        <v>866235</v>
+        <v>866287</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="45"/>
-        <v>0.98458955686167082</v>
+        <v>0.98464866167382559</v>
       </c>
       <c r="AQ36" s="5">
         <v>1539776</v>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="46"/>
-        <v>458572</v>
+        <v>458667</v>
       </c>
       <c r="AT36" s="5">
-        <v>1539348</v>
+        <v>1539443</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="47"/>
-        <v>0.9997220374911675</v>
+        <v>0.99978373477700655</v>
       </c>
       <c r="AV36" s="5">
         <v>875330</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="48"/>
-        <v>234244</v>
+        <v>234309</v>
       </c>
       <c r="AY36" s="5">
-        <v>872395</v>
+        <v>872460</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="49"/>
-        <v>0.99664697885368947</v>
+        <v>0.99672123656221079</v>
       </c>
       <c r="BA36" s="5">
         <v>893595</v>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="50"/>
-        <v>235901</v>
+        <v>235970</v>
       </c>
       <c r="BD36" s="5">
-        <v>883631</v>
+        <v>883700</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="51"/>
-        <v>0.98884953474448711</v>
+        <v>0.98892675093302895</v>
       </c>
       <c r="BF36" s="5">
         <v>1566403</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="52"/>
-        <v>507150</v>
+        <v>507289</v>
       </c>
       <c r="BI36" s="5">
-        <v>1560221</v>
+        <v>1560360</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="53"/>
-        <v>0.99605337834516405</v>
+        <v>0.99614211668389296</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>283653</v>
+        <v>283674</v>
       </c>
       <c r="F37" s="5">
-        <v>667662</v>
+        <v>667683</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.98832505118059533</v>
+        <v>0.98835613700856639</v>
       </c>
       <c r="H37" s="5">
         <v>681828</v>
@@ -6736,14 +6736,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="32"/>
-        <v>274129</v>
+        <v>274153</v>
       </c>
       <c r="K37" s="5">
-        <v>670530</v>
+        <v>670554</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98342983861032396</v>
+        <v>0.98346503810345132</v>
       </c>
       <c r="M37" s="5">
         <v>856106</v>
@@ -6753,14 +6753,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="34"/>
-        <v>347641</v>
+        <v>347682</v>
       </c>
       <c r="P37" s="5">
-        <v>846277</v>
+        <v>846318</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98851894508390314</v>
+        <v>0.98856683634970433</v>
       </c>
       <c r="R37" s="5">
         <v>679636</v>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="36"/>
-        <v>268902</v>
+        <v>268939</v>
       </c>
       <c r="U37" s="5">
-        <v>671451</v>
+        <v>671488</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98795678863391578</v>
+        <v>0.98801122954051879</v>
       </c>
       <c r="W37" s="5">
         <v>687189</v>
@@ -6787,14 +6787,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="38"/>
-        <v>273231</v>
+        <v>273272</v>
       </c>
       <c r="Z37" s="5">
-        <v>676546</v>
+        <v>676587</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98451226663989089</v>
+        <v>0.98457192999305865</v>
       </c>
       <c r="AB37" s="5">
         <v>863912</v>
@@ -6804,14 +6804,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="40"/>
-        <v>349201</v>
+        <v>349257</v>
       </c>
       <c r="AE37" s="5">
-        <v>855372</v>
+        <v>855428</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99011473390808324</v>
+        <v>0.9901795553250794</v>
       </c>
       <c r="AG37" s="5">
         <v>690763</v>
@@ -6821,14 +6821,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="42"/>
-        <v>260575</v>
+        <v>260630</v>
       </c>
       <c r="AJ37" s="5">
-        <v>682555</v>
+        <v>682610</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="43"/>
-        <v>0.98811748747399619</v>
+        <v>0.9881971095730373</v>
       </c>
       <c r="AL37" s="5">
         <v>697437</v>
@@ -6838,14 +6838,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="44"/>
-        <v>264923</v>
+        <v>264978</v>
       </c>
       <c r="AO37" s="5">
-        <v>688539</v>
+        <v>688594</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98724185840441503</v>
+        <v>0.98732071857386405</v>
       </c>
       <c r="AQ37" s="5">
         <v>873380</v>
@@ -6855,14 +6855,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="46"/>
-        <v>338433</v>
+        <v>338527</v>
       </c>
       <c r="AT37" s="5">
-        <v>868843</v>
+        <v>868937</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99480523941468779</v>
+        <v>0.99491286725136829</v>
       </c>
       <c r="AV37" s="5">
         <v>700086</v>
@@ -6872,14 +6872,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="48"/>
-        <v>266871</v>
+        <v>266937</v>
       </c>
       <c r="AY37" s="5">
-        <v>694384</v>
+        <v>694450</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="49"/>
-        <v>0.9918552863505341</v>
+        <v>0.99194956048256933</v>
       </c>
       <c r="BA37" s="5">
         <v>708485</v>
@@ -6889,14 +6889,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="50"/>
-        <v>268763</v>
+        <v>268829</v>
       </c>
       <c r="BD37" s="5">
-        <v>699363</v>
+        <v>699429</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="51"/>
-        <v>0.98712463919490179</v>
+        <v>0.98721779571903423</v>
       </c>
       <c r="BF37" s="5">
         <v>887779</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="52"/>
-        <v>384003</v>
+        <v>384126</v>
       </c>
       <c r="BI37" s="5">
-        <v>878064</v>
+        <v>878187</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="53"/>
-        <v>0.98905696124823861</v>
+        <v>0.98919550924272825</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6931,14 +6931,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="0"/>
-        <v>9413</v>
+        <v>9415</v>
       </c>
       <c r="F38" s="5">
-        <v>22897</v>
+        <v>22899</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="1"/>
-        <v>1.0070369881690637</v>
+        <v>1.007124950521177</v>
       </c>
       <c r="H38" s="5">
         <v>23122</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="32"/>
-        <v>9600</v>
+        <v>9602</v>
       </c>
       <c r="K38" s="5">
-        <v>23170</v>
+        <v>23172</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="33"/>
-        <v>1.0020759449874579</v>
+        <v>1.0021624426952687</v>
       </c>
       <c r="M38" s="5">
         <v>35582</v>
@@ -6965,14 +6965,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="34"/>
-        <v>14385</v>
+        <v>14388</v>
       </c>
       <c r="P38" s="5">
-        <v>35826</v>
+        <v>35829</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0068573998088921</v>
+        <v>1.0069417121016244</v>
       </c>
       <c r="R38" s="5">
         <v>22911</v>
@@ -6982,14 +6982,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="36"/>
-        <v>9350</v>
+        <v>9352</v>
       </c>
       <c r="U38" s="5">
-        <v>23139</v>
+        <v>23141</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0099515516564095</v>
+        <v>1.0100388459691851</v>
       </c>
       <c r="W38" s="5">
         <v>23450</v>
@@ -6999,14 +6999,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="38"/>
-        <v>9180</v>
+        <v>9182</v>
       </c>
       <c r="Z38" s="5">
-        <v>23348</v>
+        <v>23350</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="39"/>
-        <v>0.99565031982942431</v>
+        <v>0.99573560767590619</v>
       </c>
       <c r="AB38" s="5">
         <v>35915</v>
@@ -7016,14 +7016,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="40"/>
-        <v>14256</v>
+        <v>14259</v>
       </c>
       <c r="AE38" s="5">
-        <v>36323</v>
+        <v>36326</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0113601559237086</v>
+        <v>1.0114436864819714</v>
       </c>
       <c r="AG38" s="5">
         <v>23414</v>
@@ -7033,14 +7033,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="42"/>
-        <v>8890</v>
+        <v>8894</v>
       </c>
       <c r="AJ38" s="5">
-        <v>23628</v>
+        <v>23632</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0091398308704194</v>
+        <v>1.0093106688306142</v>
       </c>
       <c r="AL38" s="5">
         <v>23927</v>
@@ -7050,14 +7050,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="44"/>
-        <v>8954</v>
+        <v>8956</v>
       </c>
       <c r="AO38" s="5">
-        <v>23905</v>
+        <v>23907</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="45"/>
-        <v>0.99908053663225649</v>
+        <v>0.9991641242111422</v>
       </c>
       <c r="AQ38" s="5">
         <v>36551</v>
@@ -7067,14 +7067,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="46"/>
-        <v>13383</v>
+        <v>13389</v>
       </c>
       <c r="AT38" s="5">
-        <v>37081</v>
+        <v>37087</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0145002872698421</v>
+        <v>1.0146644414653498</v>
       </c>
       <c r="AV38" s="5">
         <v>23833</v>
@@ -7084,14 +7084,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="48"/>
-        <v>8934</v>
+        <v>8938</v>
       </c>
       <c r="AY38" s="5">
-        <v>24138</v>
+        <v>24142</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="49"/>
-        <v>1.0127973817815634</v>
+        <v>1.0129652162967315</v>
       </c>
       <c r="BA38" s="5">
         <v>24292</v>
@@ -7101,14 +7101,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="50"/>
-        <v>8896</v>
+        <v>8900</v>
       </c>
       <c r="BD38" s="5">
-        <v>24400</v>
+        <v>24404</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="51"/>
-        <v>1.0044459081178989</v>
+        <v>1.0046105713815248</v>
       </c>
       <c r="BF38" s="5">
         <v>37393</v>
@@ -7118,14 +7118,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="52"/>
-        <v>15231</v>
+        <v>15240</v>
       </c>
       <c r="BI38" s="5">
-        <v>37586</v>
+        <v>37595</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="53"/>
-        <v>1.0051613938437676</v>
+        <v>1.0054020806033215</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>104840</v>
+        <v>104857</v>
       </c>
       <c r="F40" s="5">
-        <v>275824</v>
+        <v>275841</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.99316582769820183</v>
+        <v>0.99322703998962991</v>
       </c>
       <c r="H40" s="5">
         <v>279588</v>
@@ -7372,14 +7372,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="32"/>
-        <v>108033</v>
+        <v>108054</v>
       </c>
       <c r="K40" s="5">
-        <v>277522</v>
+        <v>277543</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99261055553171096</v>
+        <v>0.99268566605147579</v>
       </c>
       <c r="M40" s="5">
         <v>339205</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="34"/>
-        <v>135096</v>
+        <v>135121</v>
       </c>
       <c r="P40" s="5">
-        <v>337498</v>
+        <v>337523</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="35"/>
-        <v>0.9949676449344792</v>
+        <v>0.99504134667826238</v>
       </c>
       <c r="R40" s="5">
         <v>280405</v>
@@ -7406,14 +7406,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="36"/>
-        <v>104671</v>
+        <v>104700</v>
       </c>
       <c r="U40" s="5">
-        <v>278827</v>
+        <v>278856</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99437242559868766</v>
+        <v>0.99447584743496009</v>
       </c>
       <c r="W40" s="5">
         <v>283529</v>
@@ -7423,14 +7423,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="38"/>
-        <v>110209</v>
+        <v>110238</v>
       </c>
       <c r="Z40" s="5">
-        <v>280773</v>
+        <v>280802</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99027965393310735</v>
+        <v>0.99038193623932647</v>
       </c>
       <c r="AB40" s="5">
         <v>342699</v>
@@ -7440,14 +7440,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="40"/>
-        <v>136207</v>
+        <v>136240</v>
       </c>
       <c r="AE40" s="5">
-        <v>341634</v>
+        <v>341667</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99689231658102295</v>
+        <v>0.99698861099682223</v>
       </c>
       <c r="AG40" s="5">
         <v>284836</v>
@@ -7457,14 +7457,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="42"/>
-        <v>104242</v>
+        <v>104278</v>
       </c>
       <c r="AJ40" s="5">
-        <v>283373</v>
+        <v>283409</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99486371104776083</v>
+        <v>0.9949900995660661</v>
       </c>
       <c r="AL40" s="5">
         <v>287465</v>
@@ -7474,14 +7474,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="44"/>
-        <v>109752</v>
+        <v>109793</v>
       </c>
       <c r="AO40" s="5">
-        <v>285595</v>
+        <v>285636</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="45"/>
-        <v>0.9934948602438558</v>
+        <v>0.99363748630268034</v>
       </c>
       <c r="AQ40" s="5">
         <v>346543</v>
@@ -7491,14 +7491,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="46"/>
-        <v>133762</v>
+        <v>133807</v>
       </c>
       <c r="AT40" s="5">
-        <v>346422</v>
+        <v>346467</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99965083698126933</v>
+        <v>0.99978069099649969</v>
       </c>
       <c r="AV40" s="5">
         <v>288959</v>
@@ -7508,14 +7508,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="48"/>
-        <v>110610</v>
+        <v>110657</v>
       </c>
       <c r="AY40" s="5">
-        <v>287706</v>
+        <v>287753</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="49"/>
-        <v>0.99566374468350183</v>
+        <v>0.99582639751660273</v>
       </c>
       <c r="BA40" s="5">
         <v>291465</v>
@@ -7525,14 +7525,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="50"/>
-        <v>109480</v>
+        <v>109528</v>
       </c>
       <c r="BD40" s="5">
-        <v>288880</v>
+        <v>288928</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="51"/>
-        <v>0.99113101058446129</v>
+        <v>0.99129569588115207</v>
       </c>
       <c r="BF40" s="5">
         <v>351557</v>
@@ -7542,14 +7542,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="52"/>
-        <v>149219</v>
+        <v>149274</v>
       </c>
       <c r="BI40" s="5">
-        <v>349368</v>
+        <v>349423</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="53"/>
-        <v>0.99377341369962768</v>
+        <v>0.99392986059159683</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>345372</v>
+        <v>345419</v>
       </c>
       <c r="F41" s="5">
-        <v>905498</v>
+        <v>905545</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.99274652071999769</v>
+        <v>0.99279804936663618</v>
       </c>
       <c r="H41" s="5">
         <v>920596</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="32"/>
-        <v>358188</v>
+        <v>358253</v>
       </c>
       <c r="K41" s="5">
-        <v>910495</v>
+        <v>910560</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98902776027703787</v>
+        <v>0.98909836671026163</v>
       </c>
       <c r="M41" s="5">
         <v>1028922</v>
@@ -7601,14 +7601,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="34"/>
-        <v>396118</v>
+        <v>396200</v>
       </c>
       <c r="P41" s="5">
-        <v>1018225</v>
+        <v>1018307</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="35"/>
-        <v>0.98960368230050477</v>
+        <v>0.98968337735999423</v>
       </c>
       <c r="R41" s="5">
         <v>924082</v>
@@ -7618,14 +7618,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="36"/>
-        <v>360426</v>
+        <v>360513</v>
       </c>
       <c r="U41" s="5">
-        <v>914946</v>
+        <v>915033</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99011343149201048</v>
+        <v>0.99020757898108613</v>
       </c>
       <c r="W41" s="5">
         <v>929406</v>
@@ -7635,14 +7635,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="38"/>
-        <v>356104</v>
+        <v>356185</v>
       </c>
       <c r="Z41" s="5">
-        <v>918908</v>
+        <v>918989</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="39"/>
-        <v>0.98870461348431149</v>
+        <v>0.9887917659236114</v>
       </c>
       <c r="AB41" s="5">
         <v>1036539</v>
@@ -7652,14 +7652,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="40"/>
-        <v>396499</v>
+        <v>396598</v>
       </c>
       <c r="AE41" s="5">
-        <v>1027315</v>
+        <v>1027414</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99110115490106976</v>
+        <v>0.99119666505553583</v>
       </c>
       <c r="AG41" s="5">
         <v>935526</v>
@@ -7669,14 +7669,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="42"/>
-        <v>348820</v>
+        <v>348919</v>
       </c>
       <c r="AJ41" s="5">
-        <v>925452</v>
+        <v>925551</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="43"/>
-        <v>0.98923172632294565</v>
+        <v>0.98933754914347649</v>
       </c>
       <c r="AL41" s="5">
         <v>940174</v>
@@ -7686,14 +7686,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="44"/>
-        <v>363607</v>
+        <v>363714</v>
       </c>
       <c r="AO41" s="5">
-        <v>930009</v>
+        <v>930116</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="45"/>
-        <v>0.98918817155122352</v>
+        <v>0.98930198027173688</v>
       </c>
       <c r="AQ41" s="5">
         <v>1046219</v>
@@ -7703,14 +7703,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="46"/>
-        <v>385896</v>
+        <v>386017</v>
       </c>
       <c r="AT41" s="5">
-        <v>1038783</v>
+        <v>1038904</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="47"/>
-        <v>0.9928925014743567</v>
+        <v>0.99300815603616455</v>
       </c>
       <c r="AV41" s="5">
         <v>945246</v>
@@ -7720,14 +7720,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="48"/>
-        <v>357354</v>
+        <v>357466</v>
       </c>
       <c r="AY41" s="5">
-        <v>936793</v>
+        <v>936905</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="49"/>
-        <v>0.9910573543818223</v>
+        <v>0.99117584205593046</v>
       </c>
       <c r="BA41" s="5">
         <v>950318</v>
@@ -7737,14 +7737,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="50"/>
-        <v>354850</v>
+        <v>354973</v>
       </c>
       <c r="BD41" s="5">
-        <v>940725</v>
+        <v>940848</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="51"/>
-        <v>0.98990548426947611</v>
+        <v>0.99003491462857696</v>
       </c>
       <c r="BF41" s="5">
         <v>1056723</v>
@@ -7754,14 +7754,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="52"/>
-        <v>421798</v>
+        <v>421949</v>
       </c>
       <c r="BI41" s="5">
-        <v>1049038</v>
+        <v>1049189</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="53"/>
-        <v>0.99272751705035278</v>
+        <v>0.99287041164051504</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7779,14 +7779,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="0"/>
-        <v>8185</v>
+        <v>8186</v>
       </c>
       <c r="F42" s="5">
-        <v>18236</v>
+        <v>18237</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="1"/>
-        <v>0.98866901599349422</v>
+        <v>0.98872323122797501</v>
       </c>
       <c r="H42" s="5">
         <v>18615</v>
@@ -7796,14 +7796,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="32"/>
-        <v>8627</v>
+        <v>8628</v>
       </c>
       <c r="K42" s="5">
-        <v>18358</v>
+        <v>18359</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="33"/>
-        <v>0.9861939296266452</v>
+        <v>0.98624764974482948</v>
       </c>
       <c r="M42" s="5">
         <v>20702</v>
@@ -7813,14 +7813,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="34"/>
-        <v>9320</v>
+        <v>9321</v>
       </c>
       <c r="P42" s="5">
-        <v>20397</v>
+        <v>20398</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="35"/>
-        <v>0.98526712394937688</v>
+        <v>0.98531542846101827</v>
       </c>
       <c r="R42" s="5">
         <v>18543</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="36"/>
-        <v>8476</v>
+        <v>8477</v>
       </c>
       <c r="U42" s="5">
-        <v>18335</v>
+        <v>18336</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="37"/>
-        <v>0.98878282909992987</v>
+        <v>0.98883675780618019</v>
       </c>
       <c r="W42" s="5">
         <v>18720</v>
@@ -7847,14 +7847,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="38"/>
-        <v>8427</v>
+        <v>8428</v>
       </c>
       <c r="Z42" s="5">
-        <v>18399</v>
+        <v>18400</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="39"/>
-        <v>0.98285256410256405</v>
+        <v>0.98290598290598286</v>
       </c>
       <c r="AB42" s="5">
         <v>20718</v>
@@ -7864,14 +7864,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="40"/>
-        <v>9145</v>
+        <v>9147</v>
       </c>
       <c r="AE42" s="5">
-        <v>20343</v>
+        <v>20345</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="41"/>
-        <v>0.98189979727772947</v>
+        <v>0.98199633169224831</v>
       </c>
       <c r="AG42" s="5">
         <v>18665</v>
@@ -7881,14 +7881,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="42"/>
-        <v>8087</v>
+        <v>8088</v>
       </c>
       <c r="AJ42" s="5">
-        <v>18415</v>
+        <v>18416</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="43"/>
-        <v>0.98660594695954995</v>
+        <v>0.98665952317171179</v>
       </c>
       <c r="AL42" s="5">
         <v>18792</v>
@@ -7898,14 +7898,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="44"/>
-        <v>8159</v>
+        <v>8160</v>
       </c>
       <c r="AO42" s="5">
-        <v>18525</v>
+        <v>18526</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="45"/>
-        <v>0.9857918263090677</v>
+        <v>0.98584504044274157</v>
       </c>
       <c r="AQ42" s="5">
         <v>20796</v>
@@ -7915,14 +7915,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="46"/>
-        <v>8825</v>
+        <v>8828</v>
       </c>
       <c r="AT42" s="5">
-        <v>20576</v>
+        <v>20579</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="47"/>
-        <v>0.98942104250817464</v>
+        <v>0.98956530101942686</v>
       </c>
       <c r="AV42" s="5">
         <v>18829</v>
@@ -7932,14 +7932,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="48"/>
-        <v>8271</v>
+        <v>8273</v>
       </c>
       <c r="AY42" s="5">
-        <v>18604</v>
+        <v>18606</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="49"/>
-        <v>0.988050347867651</v>
+        <v>0.98815656699771626</v>
       </c>
       <c r="BA42" s="5">
         <v>18938</v>
@@ -7949,14 +7949,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="50"/>
-        <v>8314</v>
+        <v>8317</v>
       </c>
       <c r="BD42" s="5">
-        <v>18718</v>
+        <v>18721</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="51"/>
-        <v>0.988383144999472</v>
+        <v>0.98854155665857002</v>
       </c>
       <c r="BF42" s="5">
         <v>21042</v>
@@ -7966,14 +7966,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="52"/>
-        <v>9643</v>
+        <v>9646</v>
       </c>
       <c r="BI42" s="5">
-        <v>20809</v>
+        <v>20812</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="53"/>
-        <v>0.98892690808858474</v>
+        <v>0.98906948008744411</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="34"/>
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="P43" s="5">
-        <v>4352</v>
+        <v>4353</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99021615472127422</v>
+        <v>0.99044368600682597</v>
       </c>
       <c r="R43" s="5">
         <v>3498</v>
@@ -8059,14 +8059,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="38"/>
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Z43" s="5">
-        <v>3519</v>
+        <v>3520</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="39"/>
-        <v>0.99098845395663193</v>
+        <v>0.99127006477048718</v>
       </c>
       <c r="AB43" s="5">
         <v>4429</v>
@@ -8076,14 +8076,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="40"/>
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="AE43" s="5">
-        <v>4389</v>
+        <v>4391</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="41"/>
-        <v>0.99096861594039287</v>
+        <v>0.99142018514337327</v>
       </c>
       <c r="AG43" s="5">
         <v>3560</v>
@@ -8093,14 +8093,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="42"/>
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3545</v>
+        <v>3546</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="43"/>
-        <v>0.9957865168539326</v>
+        <v>0.99606741573033708</v>
       </c>
       <c r="AL43" s="5">
         <v>3588</v>
@@ -8110,14 +8110,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="44"/>
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="AO43" s="5">
-        <v>3580</v>
+        <v>3581</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="45"/>
-        <v>0.99777034559643252</v>
+        <v>0.99804905239687847</v>
       </c>
       <c r="AQ43" s="5">
         <v>4449</v>
@@ -8127,14 +8127,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="46"/>
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="AT43" s="5">
-        <v>4468</v>
+        <v>4470</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="47"/>
-        <v>1.004270622611823</v>
+        <v>1.0047201618341199</v>
       </c>
       <c r="AV43" s="5">
         <v>3616</v>
@@ -8144,14 +8144,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="48"/>
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="AY43" s="5">
-        <v>3631</v>
+        <v>3632</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="49"/>
-        <v>1.0041482300884956</v>
+        <v>1.0044247787610618</v>
       </c>
       <c r="BA43" s="5">
         <v>3655</v>
@@ -8161,14 +8161,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="50"/>
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="BD43" s="5">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="51"/>
-        <v>0.99945280437756501</v>
+        <v>0.9997264021887825</v>
       </c>
       <c r="BF43" s="5">
         <v>4544</v>
@@ -8178,14 +8178,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="52"/>
-        <v>2775</v>
+        <v>2776</v>
       </c>
       <c r="BI43" s="5">
-        <v>4549</v>
+        <v>4550</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="53"/>
-        <v>1.001100352112676</v>
+        <v>1.0013204225352113</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8203,14 +8203,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>164107</v>
+        <v>164122</v>
       </c>
       <c r="F44" s="5">
-        <v>333675</v>
+        <v>333690</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.99240693814911307</v>
+        <v>0.99245155073343083</v>
       </c>
       <c r="H44" s="5">
         <v>340996</v>
@@ -8220,14 +8220,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="32"/>
-        <v>169311</v>
+        <v>169331</v>
       </c>
       <c r="K44" s="5">
-        <v>337592</v>
+        <v>337612</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="33"/>
-        <v>0.99001747821088815</v>
+        <v>0.99007612992527771</v>
       </c>
       <c r="M44" s="5">
         <v>408512</v>
@@ -8237,14 +8237,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="34"/>
-        <v>200367</v>
+        <v>200391</v>
       </c>
       <c r="P44" s="5">
-        <v>404863</v>
+        <v>404887</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="35"/>
-        <v>0.99106758185806043</v>
+        <v>0.99112633166222774</v>
       </c>
       <c r="R44" s="5">
         <v>342556</v>
@@ -8254,14 +8254,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="36"/>
-        <v>167598</v>
+        <v>167617</v>
       </c>
       <c r="U44" s="5">
-        <v>339629</v>
+        <v>339648</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="37"/>
-        <v>0.9914554116699168</v>
+        <v>0.9915108770536788</v>
       </c>
       <c r="W44" s="5">
         <v>347597</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="38"/>
-        <v>168781</v>
+        <v>168804</v>
       </c>
       <c r="Z44" s="5">
-        <v>343505</v>
+        <v>343528</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98822774649953826</v>
+        <v>0.98829391507981945</v>
       </c>
       <c r="AB44" s="5">
         <v>416340</v>
@@ -8288,14 +8288,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="40"/>
-        <v>203149</v>
+        <v>203181</v>
       </c>
       <c r="AE44" s="5">
-        <v>413174</v>
+        <v>413206</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="41"/>
-        <v>0.99239563818033338</v>
+        <v>0.99247249843877605</v>
       </c>
       <c r="AG44" s="5">
         <v>350469</v>
@@ -8305,14 +8305,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="42"/>
-        <v>166164</v>
+        <v>166195</v>
       </c>
       <c r="AJ44" s="5">
-        <v>347589</v>
+        <v>347620</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="43"/>
-        <v>0.99178244010169225</v>
+        <v>0.9918708930033755</v>
       </c>
       <c r="AL44" s="5">
         <v>355186</v>
@@ -8322,14 +8322,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="44"/>
-        <v>169332</v>
+        <v>169366</v>
       </c>
       <c r="AO44" s="5">
-        <v>351065</v>
+        <v>351099</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98839762828489863</v>
+        <v>0.98849335277854422</v>
       </c>
       <c r="AQ44" s="5">
         <v>424208</v>
@@ -8339,14 +8339,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="46"/>
-        <v>198236</v>
+        <v>198276</v>
       </c>
       <c r="AT44" s="5">
-        <v>421823</v>
+        <v>421863</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="47"/>
-        <v>0.99437775808094142</v>
+        <v>0.99447205144646023</v>
       </c>
       <c r="AV44" s="5">
         <v>358114</v>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="48"/>
-        <v>167098</v>
+        <v>167137</v>
       </c>
       <c r="AY44" s="5">
-        <v>354659</v>
+        <v>354698</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="49"/>
-        <v>0.99035223420475049</v>
+        <v>0.9904611380733509</v>
       </c>
       <c r="BA44" s="5">
         <v>361984</v>
@@ -8373,14 +8373,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="50"/>
-        <v>170806</v>
+        <v>170848</v>
       </c>
       <c r="BD44" s="5">
-        <v>357757</v>
+        <v>357799</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="51"/>
-        <v>0.98832268829561531</v>
+        <v>0.98843871552333806</v>
       </c>
       <c r="BF44" s="5">
         <v>432310</v>
@@ -8390,14 +8390,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="52"/>
-        <v>225387</v>
+        <v>225447</v>
       </c>
       <c r="BI44" s="5">
-        <v>427983</v>
+        <v>428043</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="53"/>
-        <v>0.98999097869584329</v>
+        <v>0.99012976799056229</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>116359</v>
+        <v>116367</v>
       </c>
       <c r="F45" s="5">
-        <v>251472</v>
+        <v>251480</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.98401145728171291</v>
+        <v>0.98404276133010904</v>
       </c>
       <c r="H45" s="5">
         <v>257610</v>
@@ -8432,14 +8432,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="32"/>
-        <v>119213</v>
+        <v>119223</v>
       </c>
       <c r="K45" s="5">
-        <v>253396</v>
+        <v>253406</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="33"/>
-        <v>0.98364193936570787</v>
+        <v>0.98368075773455999</v>
       </c>
       <c r="M45" s="5">
         <v>310366</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="34"/>
-        <v>144162</v>
+        <v>144177</v>
       </c>
       <c r="P45" s="5">
-        <v>305396</v>
+        <v>305411</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98398664802201274</v>
+        <v>0.98403497805816353</v>
       </c>
       <c r="R45" s="5">
         <v>257356</v>
@@ -8466,14 +8466,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="36"/>
-        <v>118773</v>
+        <v>118785</v>
       </c>
       <c r="U45" s="5">
-        <v>253915</v>
+        <v>253927</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98662941606179766</v>
+        <v>0.98667604407901899</v>
       </c>
       <c r="W45" s="5">
         <v>260553</v>
@@ -8483,14 +8483,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="38"/>
-        <v>120975</v>
+        <v>120988</v>
       </c>
       <c r="Z45" s="5">
-        <v>255876</v>
+        <v>255889</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98204971733198232</v>
+        <v>0.98209961121153855</v>
       </c>
       <c r="AB45" s="5">
         <v>313911</v>
@@ -8500,14 +8500,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="40"/>
-        <v>148006</v>
+        <v>148033</v>
       </c>
       <c r="AE45" s="5">
-        <v>309000</v>
+        <v>309027</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="41"/>
-        <v>0.98435543832487549</v>
+        <v>0.98444144996511751</v>
       </c>
       <c r="AG45" s="5">
         <v>261210</v>
@@ -8517,14 +8517,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="42"/>
-        <v>116263</v>
+        <v>116285</v>
       </c>
       <c r="AJ45" s="5">
-        <v>257187</v>
+        <v>257209</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="43"/>
-        <v>0.98459859882852874</v>
+        <v>0.98468282225029669</v>
       </c>
       <c r="AL45" s="5">
         <v>264020</v>
@@ -8534,14 +8534,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="44"/>
-        <v>120883</v>
+        <v>120908</v>
       </c>
       <c r="AO45" s="5">
-        <v>259577</v>
+        <v>259602</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98317172941443831</v>
+        <v>0.98326641921066582</v>
       </c>
       <c r="AQ45" s="5">
         <v>317407</v>
@@ -8551,14 +8551,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="46"/>
-        <v>143457</v>
+        <v>143490</v>
       </c>
       <c r="AT45" s="5">
-        <v>311995</v>
+        <v>312028</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="47"/>
-        <v>0.98294933634103843</v>
+        <v>0.98305330380237366</v>
       </c>
       <c r="AV45" s="5">
         <v>263886</v>
@@ -8568,14 +8568,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="48"/>
-        <v>118273</v>
+        <v>118303</v>
       </c>
       <c r="AY45" s="5">
-        <v>259575</v>
+        <v>259605</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="49"/>
-        <v>0.98366340010459064</v>
+        <v>0.98377708555967347</v>
       </c>
       <c r="BA45" s="5">
         <v>265781</v>
@@ -8585,14 +8585,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="50"/>
-        <v>120857</v>
+        <v>120887</v>
       </c>
       <c r="BD45" s="5">
-        <v>261403</v>
+        <v>261433</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="51"/>
-        <v>0.98352779167811089</v>
+        <v>0.98364066656382509</v>
       </c>
       <c r="BF45" s="5">
         <v>319799</v>
@@ -8602,14 +8602,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="52"/>
-        <v>165042</v>
+        <v>165090</v>
       </c>
       <c r="BI45" s="5">
-        <v>315107</v>
+        <v>315155</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="53"/>
-        <v>0.98532828432859387</v>
+        <v>0.98547837860656229</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="34"/>
-        <v>4406</v>
+        <v>4407</v>
       </c>
       <c r="P46" s="5">
-        <v>6877</v>
+        <v>6878</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0281058454178502</v>
+        <v>1.0282553445956046</v>
       </c>
       <c r="R46" s="5">
         <v>2186</v>
@@ -8712,14 +8712,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="40"/>
-        <v>4609</v>
+        <v>4610</v>
       </c>
       <c r="AE46" s="5">
-        <v>7163</v>
+        <v>7164</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="41"/>
-        <v>1.0351156069364162</v>
+        <v>1.0352601156069363</v>
       </c>
       <c r="AG46" s="5">
         <v>2260</v>
@@ -8763,14 +8763,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="46"/>
-        <v>4293</v>
+        <v>4294</v>
       </c>
       <c r="AT46" s="5">
-        <v>7363</v>
+        <v>7364</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0307993840123197</v>
+        <v>1.0309393812123757</v>
       </c>
       <c r="AV46" s="5">
         <v>2225</v>
@@ -8814,14 +8814,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="52"/>
-        <v>4643</v>
+        <v>4645</v>
       </c>
       <c r="BI46" s="5">
-        <v>7563</v>
+        <v>7565</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="53"/>
-        <v>1.0210611583637099</v>
+        <v>1.0213311732145267</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9037,10 +9037,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="18"/>
+      <c r="B48" s="14"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>7712416</v>
@@ -9051,15 +9051,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3007310</v>
+        <v>3007621</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>7666239</v>
+        <v>7666550</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.99401264143427948</v>
+        <v>0.99405296602257964</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9071,15 +9071,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3057859</v>
+        <v>3058262</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7764714</v>
+        <v>7765117</v>
       </c>
       <c r="L48" s="6">
         <f>K48/H48</f>
-        <v>0.98695493676137713</v>
+        <v>0.98700616116442852</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9091,15 +9091,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>4953672</v>
+        <v>4954381</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12076336</v>
+        <v>12077045</v>
       </c>
       <c r="Q48" s="6">
         <f>P48/M48</f>
-        <v>0.99375292744093857</v>
+        <v>0.99381127053652274</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9111,15 +9111,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3022609</v>
+        <v>3023136</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7733973</v>
+        <v>7734500</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.99078644813604289</v>
+        <v>0.99085396123159775</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3061932</v>
+        <v>3062513</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7825637</v>
+        <v>7826218</v>
       </c>
       <c r="AA48" s="6">
         <f>Z48/W48</f>
-        <v>0.98462549090437379</v>
+        <v>0.98469859260973214</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>4961277</v>
+        <v>4962317</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12219731</v>
+        <v>12220771</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.9947535769382716</v>
+        <v>0.99483823868082677</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2973384</v>
+        <v>2974140</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7865564</v>
+        <v>7866320</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.99132610891378359</v>
+        <v>0.99142139038861987</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3043340</v>
+        <v>3044162</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7954470</v>
+        <v>7955292</v>
       </c>
       <c r="AP48" s="6">
         <f>AO48/AL48</f>
-        <v>0.98464970563139564</v>
+        <v>0.98475145748387971</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4872180</v>
+        <v>4873580</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12409498</v>
+        <v>12410898</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.99712757787190387</v>
+        <v>0.99724007062616515</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>2994082</v>
+        <v>2995053</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8000995</v>
+        <v>8001966</v>
       </c>
       <c r="AZ48" s="6">
         <f>AY48/AV48</f>
-        <v>0.99251476430209584</v>
+        <v>0.99263521580045788</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3027737</v>
+        <v>3028792</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8094136</v>
+        <v>8095191</v>
       </c>
       <c r="BE48" s="6">
         <f>BD48/BA48</f>
-        <v>0.98679431950556262</v>
+        <v>0.98692293953456622</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9271,25 +9271,19 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5323752</v>
+        <v>5325719</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12580347</v>
+        <v>12582314</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99401764846247564</v>
+        <v>0.99417306807963934</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9302,6 +9296,12 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2023-2024.xlsx
+++ b/gstdatabase/GSTR-1-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744966EB-8BDD-4459-9953-AFC501B81962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C89DBC7-3685-43A0-9ABD-C0B2688723EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
 CD</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -362,6 +362,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -373,18 +385,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -684,13 +684,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -702,10 +702,10 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -722,107 +722,107 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="8" spans="1:62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="15">
         <v>45017</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="18">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="15">
         <v>45047</v>
       </c>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="18">
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="15">
         <v>45078</v>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="18">
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="15">
         <v>45108</v>
       </c>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="18">
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="15">
         <v>45139</v>
       </c>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="18">
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="15">
         <v>45170</v>
       </c>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="20"/>
-      <c r="AG8" s="18">
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="15">
         <v>45200</v>
       </c>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="19"/>
-      <c r="AK8" s="20"/>
-      <c r="AL8" s="18">
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="15">
         <v>45231</v>
       </c>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="20"/>
-      <c r="AQ8" s="18">
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16"/>
+      <c r="AO8" s="16"/>
+      <c r="AP8" s="17"/>
+      <c r="AQ8" s="15">
         <v>45261</v>
       </c>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="19"/>
-      <c r="AT8" s="19"/>
-      <c r="AU8" s="20"/>
-      <c r="AV8" s="18">
+      <c r="AR8" s="16"/>
+      <c r="AS8" s="16"/>
+      <c r="AT8" s="16"/>
+      <c r="AU8" s="17"/>
+      <c r="AV8" s="15">
         <v>45292</v>
       </c>
-      <c r="AW8" s="19"/>
-      <c r="AX8" s="19"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="20"/>
-      <c r="BA8" s="18">
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="16"/>
+      <c r="AY8" s="16"/>
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="15">
         <v>45323</v>
       </c>
-      <c r="BB8" s="19"/>
-      <c r="BC8" s="19"/>
-      <c r="BD8" s="19"/>
-      <c r="BE8" s="20"/>
-      <c r="BF8" s="18">
+      <c r="BB8" s="16"/>
+      <c r="BC8" s="16"/>
+      <c r="BD8" s="16"/>
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="15">
         <v>45352</v>
       </c>
-      <c r="BG8" s="19"/>
-      <c r="BH8" s="19"/>
-      <c r="BI8" s="19"/>
-      <c r="BJ8" s="20"/>
+      <c r="BG8" s="16"/>
+      <c r="BH8" s="16"/>
+      <c r="BI8" s="16"/>
+      <c r="BJ8" s="17"/>
     </row>
     <row r="9" spans="1:62" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>77024</v>
+        <v>77025</v>
       </c>
       <c r="AE10" s="5">
-        <v>123624</v>
+        <v>123625</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>1.0005665538954627</v>
+        <v>1.0005746475225408</v>
       </c>
       <c r="AG10" s="5">
         <v>71950</v>
@@ -1121,14 +1121,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41863</v>
+        <v>41864</v>
       </c>
       <c r="AJ10" s="5">
-        <v>71914</v>
+        <v>71915</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99949965253648365</v>
+        <v>0.99951355107713691</v>
       </c>
       <c r="AL10" s="5">
         <v>73532</v>
@@ -1206,14 +1206,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>85642</v>
+        <v>85644</v>
       </c>
       <c r="BI10" s="5">
-        <v>128165</v>
+        <v>128167</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>1.0002809668381085</v>
+        <v>1.0002965761068923</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>17307</v>
+        <v>17309</v>
       </c>
       <c r="Z11" s="5">
-        <v>45904</v>
+        <v>45906</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.98877759827679057</v>
+        <v>0.98882067851373179</v>
       </c>
       <c r="AB11" s="5">
         <v>103964</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>44415</v>
+        <v>44418</v>
       </c>
       <c r="AE11" s="5">
-        <v>104337</v>
+        <v>104340</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.003587780385518</v>
+        <v>1.003616636528029</v>
       </c>
       <c r="AG11" s="5">
         <v>45569</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15640</v>
+        <v>15641</v>
       </c>
       <c r="AJ11" s="5">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99517215650990809</v>
+        <v>0.99519410125304486</v>
       </c>
       <c r="AL11" s="5">
         <v>46951</v>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN25" si="14">AO11-AM11</f>
-        <v>16009</v>
+        <v>16011</v>
       </c>
       <c r="AO11" s="5">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP26" si="15">AO11/AL11</f>
-        <v>0.98528252859364018</v>
+        <v>0.98532512619539525</v>
       </c>
       <c r="AQ11" s="5">
         <v>105644</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS25" si="16">AT11-AR11</f>
-        <v>42437</v>
+        <v>42442</v>
       </c>
       <c r="AT11" s="5">
-        <v>106043</v>
+        <v>106048</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU26" si="17">AT11/AQ11</f>
-        <v>1.0037768354094885</v>
+        <v>1.0038241641740184</v>
       </c>
       <c r="AV11" s="5">
         <v>46072</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX25" si="18">AY11-AW11</f>
-        <v>15102</v>
+        <v>15105</v>
       </c>
       <c r="AY11" s="5">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ26" si="19">AY11/AV11</f>
-        <v>0.99728685535683281</v>
+        <v>0.99735197082826876</v>
       </c>
       <c r="BA11" s="5">
         <v>47252</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC25" si="20">BD11-BB11</f>
-        <v>15567</v>
+        <v>15569</v>
       </c>
       <c r="BD11" s="5">
-        <v>46913</v>
+        <v>46915</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE26" si="21">BD11/BA11</f>
-        <v>0.99282570049944974</v>
+        <v>0.99286802675019048</v>
       </c>
       <c r="BF11" s="5">
         <v>107665</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>46572</v>
+        <v>46577</v>
       </c>
       <c r="BI11" s="5">
-        <v>107768</v>
+        <v>107773</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>1.0009566711559001</v>
+        <v>1.001003111503274</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1477,14 +1477,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>96118</v>
+        <v>96119</v>
       </c>
       <c r="P12" s="5">
-        <v>343879</v>
+        <v>343880</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99711199710039866</v>
+        <v>0.9971148967017035</v>
       </c>
       <c r="R12" s="5">
         <v>167705</v>
@@ -1528,14 +1528,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>93190</v>
+        <v>93193</v>
       </c>
       <c r="AE12" s="5">
-        <v>348644</v>
+        <v>348647</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99884256606541222</v>
+        <v>0.99885116087185721</v>
       </c>
       <c r="AG12" s="5">
         <v>170526</v>
@@ -1562,14 +1562,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>38323</v>
+        <v>38324</v>
       </c>
       <c r="AO12" s="5">
-        <v>172271</v>
+        <v>172272</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98501360839832586</v>
+        <v>0.98501932621274846</v>
       </c>
       <c r="AQ12" s="5">
         <v>353589</v>
@@ -1579,14 +1579,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94333</v>
+        <v>94342</v>
       </c>
       <c r="AT12" s="5">
-        <v>353352</v>
+        <v>353361</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99932973028007088</v>
+        <v>0.99935518356057451</v>
       </c>
       <c r="AV12" s="5">
         <v>172980</v>
@@ -1596,14 +1596,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36200</v>
+        <v>36203</v>
       </c>
       <c r="AY12" s="5">
-        <v>171876</v>
+        <v>171879</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99361775927852936</v>
+        <v>0.99363510232396812</v>
       </c>
       <c r="BA12" s="5">
         <v>177212</v>
@@ -1613,14 +1613,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>36708</v>
+        <v>36712</v>
       </c>
       <c r="BD12" s="5">
-        <v>174602</v>
+        <v>174606</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98527187775094238</v>
+        <v>0.98529444958580681</v>
       </c>
       <c r="BF12" s="5">
         <v>359260</v>
@@ -1630,14 +1630,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>100751</v>
+        <v>100762</v>
       </c>
       <c r="BI12" s="5">
-        <v>357991</v>
+        <v>358002</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99646773924177479</v>
+        <v>0.9964983577353449</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1867,14 +1867,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>36552</v>
+        <v>36555</v>
       </c>
       <c r="F14" s="5">
-        <v>84996</v>
+        <v>84999</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99546748181722355</v>
+        <v>0.99550261761709002</v>
       </c>
       <c r="H14" s="5">
         <v>88261</v>
@@ -1884,14 +1884,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>37981</v>
+        <v>37984</v>
       </c>
       <c r="K14" s="5">
-        <v>86806</v>
+        <v>86809</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.9835148026874837</v>
+        <v>0.98354879278503526</v>
       </c>
       <c r="M14" s="5">
         <v>157146</v>
@@ -1901,14 +1901,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>76986</v>
+        <v>76990</v>
       </c>
       <c r="P14" s="5">
-        <v>155887</v>
+        <v>155891</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99198834205134079</v>
+        <v>0.99201379608771456</v>
       </c>
       <c r="R14" s="5">
         <v>86469</v>
@@ -1918,14 +1918,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>36755</v>
+        <v>36758</v>
       </c>
       <c r="U14" s="5">
-        <v>85087</v>
+        <v>85090</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.98401739351675166</v>
+        <v>0.98405208803154887</v>
       </c>
       <c r="W14" s="5">
         <v>88169</v>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>37737</v>
+        <v>37741</v>
       </c>
       <c r="Z14" s="5">
-        <v>86302</v>
+        <v>86306</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97882475700075988</v>
+        <v>0.97887012442014765</v>
       </c>
       <c r="AB14" s="5">
         <v>157930</v>
@@ -1952,14 +1952,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>76138</v>
+        <v>76148</v>
       </c>
       <c r="AE14" s="5">
-        <v>157554</v>
+        <v>157564</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99761919837902868</v>
+        <v>0.99768251757107584</v>
       </c>
       <c r="AG14" s="5">
         <v>87312</v>
@@ -1969,14 +1969,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>37763</v>
+        <v>37770</v>
       </c>
       <c r="AJ14" s="5">
-        <v>86619</v>
+        <v>86626</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99206294667399675</v>
+        <v>0.99214311892981488</v>
       </c>
       <c r="AL14" s="5">
         <v>89337</v>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>37694</v>
+        <v>37702</v>
       </c>
       <c r="AO14" s="5">
-        <v>87812</v>
+        <v>87820</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.9829298051199391</v>
+        <v>0.98301935368324433</v>
       </c>
       <c r="AQ14" s="5">
         <v>160173</v>
@@ -2003,14 +2003,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>77640</v>
+        <v>77652</v>
       </c>
       <c r="AT14" s="5">
-        <v>160650</v>
+        <v>160662</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>1.002978030005057</v>
+        <v>1.0030529489988949</v>
       </c>
       <c r="AV14" s="5">
         <v>88523</v>
@@ -2020,14 +2020,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>37626</v>
+        <v>37635</v>
       </c>
       <c r="AY14" s="5">
-        <v>88163</v>
+        <v>88172</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.9959332602826384</v>
+        <v>0.99603492877557243</v>
       </c>
       <c r="BA14" s="5">
         <v>90782</v>
@@ -2037,14 +2037,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>37733</v>
+        <v>37741</v>
       </c>
       <c r="BD14" s="5">
-        <v>89647</v>
+        <v>89655</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98749752153510606</v>
+        <v>0.98758564473133437</v>
       </c>
       <c r="BF14" s="5">
         <v>163900</v>
@@ -2054,14 +2054,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>82149</v>
+        <v>82160</v>
       </c>
       <c r="BI14" s="5">
-        <v>163303</v>
+        <v>163314</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99635753508236735</v>
+        <v>0.996424649176327</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2181,14 +2181,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>78358</v>
+        <v>78359</v>
       </c>
       <c r="AJ15" s="5">
-        <v>289367</v>
+        <v>289368</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99074197712200118</v>
+        <v>0.99074540094703001</v>
       </c>
       <c r="AL15" s="5">
         <v>298411</v>
@@ -2198,14 +2198,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75045</v>
+        <v>75046</v>
       </c>
       <c r="AO15" s="5">
-        <v>293266</v>
+        <v>293267</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98275867846694664</v>
+        <v>0.98276202954984904</v>
       </c>
       <c r="AQ15" s="5">
         <v>502913</v>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137738</v>
+        <v>137739</v>
       </c>
       <c r="AT15" s="5">
-        <v>499826</v>
+        <v>499827</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99386176137821058</v>
+        <v>0.99386374979370185</v>
       </c>
       <c r="AV15" s="5">
         <v>298012</v>
@@ -2232,14 +2232,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>71733</v>
+        <v>71734</v>
       </c>
       <c r="AY15" s="5">
-        <v>294436</v>
+        <v>294437</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.98800048320201872</v>
+        <v>0.98800383877159303</v>
       </c>
       <c r="BA15" s="5">
         <v>303376</v>
@@ -2249,14 +2249,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>71595</v>
+        <v>71596</v>
       </c>
       <c r="BD15" s="5">
-        <v>298823</v>
+        <v>298824</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98499222087442651</v>
+        <v>0.98499551711407629</v>
       </c>
       <c r="BF15" s="5">
         <v>511329</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>149692</v>
+        <v>149696</v>
       </c>
       <c r="BI15" s="5">
-        <v>507698</v>
+        <v>507702</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99289889679638743</v>
+        <v>0.99290671954847076</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>107217</v>
+        <v>107224</v>
       </c>
       <c r="F16" s="5">
-        <v>426851</v>
+        <v>426858</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99121297618632953</v>
+        <v>0.99122923125152396</v>
       </c>
       <c r="H16" s="5">
         <v>441093</v>
@@ -2308,14 +2308,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>113334</v>
+        <v>113341</v>
       </c>
       <c r="K16" s="5">
-        <v>431260</v>
+        <v>431267</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97770764895384876</v>
+        <v>0.97772351862305684</v>
       </c>
       <c r="M16" s="5">
         <v>754668</v>
@@ -2325,14 +2325,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>199861</v>
+        <v>199874</v>
       </c>
       <c r="P16" s="5">
-        <v>751713</v>
+        <v>751726</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99608437087566981</v>
+        <v>0.99610159699364487</v>
       </c>
       <c r="R16" s="5">
         <v>429537</v>
@@ -2342,14 +2342,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>111560</v>
+        <v>111568</v>
       </c>
       <c r="U16" s="5">
-        <v>423862</v>
+        <v>423870</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.98678809974460868</v>
+        <v>0.98680672444981454</v>
       </c>
       <c r="W16" s="5">
         <v>433887</v>
@@ -2359,14 +2359,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>112634</v>
+        <v>112644</v>
       </c>
       <c r="Z16" s="5">
-        <v>426877</v>
+        <v>426887</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98384371967816509</v>
+        <v>0.98386676715365984</v>
       </c>
       <c r="AB16" s="5">
         <v>753330</v>
@@ -2376,14 +2376,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>200030</v>
+        <v>200052</v>
       </c>
       <c r="AE16" s="5">
-        <v>752108</v>
+        <v>752130</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99837786892862357</v>
+        <v>0.99840707259766637</v>
       </c>
       <c r="AG16" s="5">
         <v>431686</v>
@@ -2393,14 +2393,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>113789</v>
+        <v>113802</v>
       </c>
       <c r="AJ16" s="5">
-        <v>426130</v>
+        <v>426143</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98712953396681846</v>
+        <v>0.98715964844817761</v>
       </c>
       <c r="AL16" s="5">
         <v>438911</v>
@@ -2410,14 +2410,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>114049</v>
+        <v>114067</v>
       </c>
       <c r="AO16" s="5">
-        <v>430541</v>
+        <v>430559</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98093007466206128</v>
+        <v>0.98097108525418597</v>
       </c>
       <c r="AQ16" s="5">
         <v>759875</v>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>195643</v>
+        <v>195670</v>
       </c>
       <c r="AT16" s="5">
-        <v>758642</v>
+        <v>758669</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99837736469814109</v>
+        <v>0.99841289685803591</v>
       </c>
       <c r="AV16" s="5">
         <v>437477</v>
@@ -2444,14 +2444,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108349</v>
+        <v>108369</v>
       </c>
       <c r="AY16" s="5">
-        <v>431090</v>
+        <v>431110</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.98540037533401759</v>
+        <v>0.9854460920231235</v>
       </c>
       <c r="BA16" s="5">
         <v>445887</v>
@@ -2461,14 +2461,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>109767</v>
+        <v>109788</v>
       </c>
       <c r="BD16" s="5">
-        <v>436935</v>
+        <v>436956</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.97992316438918381</v>
+        <v>0.97997026152365962</v>
       </c>
       <c r="BF16" s="5">
         <v>770088</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>207378</v>
+        <v>207416</v>
       </c>
       <c r="BI16" s="5">
-        <v>764960</v>
+        <v>764998</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99334102076645781</v>
+        <v>0.99339036577637885</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>89306</v>
+        <v>89310</v>
       </c>
       <c r="F17" s="5">
-        <v>301152</v>
+        <v>301156</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.9953003232267148</v>
+        <v>0.99531354313325004</v>
       </c>
       <c r="H17" s="5">
         <v>314962</v>
@@ -2520,14 +2520,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>92347</v>
+        <v>92351</v>
       </c>
       <c r="K17" s="5">
-        <v>309398</v>
+        <v>309402</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98233437684546077</v>
+        <v>0.98234707679021593</v>
       </c>
       <c r="M17" s="5">
         <v>695415</v>
@@ -2537,14 +2537,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>249466</v>
+        <v>249485</v>
       </c>
       <c r="P17" s="5">
-        <v>691745</v>
+        <v>691764</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99472257572816236</v>
+        <v>0.99474989754319365</v>
       </c>
       <c r="R17" s="5">
         <v>305324</v>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>90703</v>
+        <v>90709</v>
       </c>
       <c r="U17" s="5">
-        <v>302689</v>
+        <v>302695</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99136982353172365</v>
+        <v>0.99138947478743888</v>
       </c>
       <c r="W17" s="5">
         <v>316716</v>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="Z17" s="5">
-        <v>309800</v>
+        <v>309806</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97816340191212314</v>
+        <v>0.97818234632920342</v>
       </c>
       <c r="AB17" s="5">
         <v>703511</v>
@@ -2588,14 +2588,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>254073</v>
+        <v>254095</v>
       </c>
       <c r="AE17" s="5">
-        <v>699748</v>
+        <v>699770</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99465111419721941</v>
+        <v>0.99468238591862812</v>
       </c>
       <c r="AG17" s="5">
         <v>311084</v>
@@ -2605,14 +2605,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>90878</v>
+        <v>90885</v>
       </c>
       <c r="AJ17" s="5">
-        <v>308972</v>
+        <v>308979</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.9932108369443623</v>
+        <v>0.99323333890524745</v>
       </c>
       <c r="AL17" s="5">
         <v>323550</v>
@@ -2622,14 +2622,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93528</v>
+        <v>93535</v>
       </c>
       <c r="AO17" s="5">
-        <v>316273</v>
+        <v>316280</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97750888579817652</v>
+        <v>0.97753052078504099</v>
       </c>
       <c r="AQ17" s="5">
         <v>714257</v>
@@ -2639,14 +2639,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>244243</v>
+        <v>244268</v>
       </c>
       <c r="AT17" s="5">
-        <v>714167</v>
+        <v>714192</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99987399493459639</v>
+        <v>0.99990899634165298</v>
       </c>
       <c r="AV17" s="5">
         <v>316308</v>
@@ -2656,14 +2656,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>87059</v>
+        <v>87067</v>
       </c>
       <c r="AY17" s="5">
-        <v>314715</v>
+        <v>314723</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99496376949049659</v>
+        <v>0.99498906129468745</v>
       </c>
       <c r="BA17" s="5">
         <v>328067</v>
@@ -2673,14 +2673,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>88484</v>
+        <v>88492</v>
       </c>
       <c r="BD17" s="5">
-        <v>321654</v>
+        <v>321662</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.98045216373484689</v>
+        <v>0.98047654899761327</v>
       </c>
       <c r="BF17" s="5">
         <v>726752</v>
@@ -2690,14 +2690,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>273093</v>
+        <v>273130</v>
       </c>
       <c r="BI17" s="5">
-        <v>725563</v>
+        <v>725600</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99836395359077101</v>
+        <v>0.99841486504337107</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>454337</v>
+        <v>454341</v>
       </c>
       <c r="F18" s="5">
-        <v>917870</v>
+        <v>917874</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99634621313105431</v>
+        <v>0.99635055512376847</v>
       </c>
       <c r="H18" s="5">
         <v>943261</v>
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>449505</v>
+        <v>449510</v>
       </c>
       <c r="K18" s="5">
-        <v>932535</v>
+        <v>932540</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98862881005363312</v>
+        <v>0.98863411081344399</v>
       </c>
       <c r="M18" s="5">
         <v>1440086</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>736537</v>
+        <v>736554</v>
       </c>
       <c r="P18" s="5">
-        <v>1430627</v>
+        <v>1430644</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.9934316422769196</v>
+        <v>0.99344344712746324</v>
       </c>
       <c r="R18" s="5">
         <v>938677</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>455678</v>
+        <v>455687</v>
       </c>
       <c r="U18" s="5">
-        <v>928245</v>
+        <v>928254</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98888648597973527</v>
+        <v>0.98889607394236778</v>
       </c>
       <c r="W18" s="5">
         <v>958009</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>462163</v>
+        <v>462175</v>
       </c>
       <c r="Z18" s="5">
-        <v>943343</v>
+        <v>943355</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.98469116678444568</v>
+        <v>0.9847036927628029</v>
       </c>
       <c r="AB18" s="5">
         <v>1463397</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>751121</v>
+        <v>751148</v>
       </c>
       <c r="AE18" s="5">
-        <v>1454879</v>
+        <v>1454906</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.99417929652718984</v>
+        <v>0.994197746749515</v>
       </c>
       <c r="AG18" s="5">
         <v>959088</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>469070</v>
+        <v>469086</v>
       </c>
       <c r="AJ18" s="5">
-        <v>951041</v>
+        <v>951057</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99160973758403814</v>
+        <v>0.99162642009909419</v>
       </c>
       <c r="AL18" s="5">
         <v>980581</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>470061</v>
+        <v>470081</v>
       </c>
       <c r="AO18" s="5">
-        <v>964082</v>
+        <v>964102</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98317426097385119</v>
+        <v>0.98319465704515996</v>
       </c>
       <c r="AQ18" s="5">
         <v>1490329</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>752954</v>
+        <v>752985</v>
       </c>
       <c r="AT18" s="5">
-        <v>1485937</v>
+        <v>1485968</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99705299970677619</v>
+        <v>0.99707380048298055</v>
       </c>
       <c r="AV18" s="5">
         <v>983291</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>464853</v>
+        <v>464880</v>
       </c>
       <c r="AY18" s="5">
-        <v>974151</v>
+        <v>974178</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99070468457455629</v>
+        <v>0.99073214338379989</v>
       </c>
       <c r="BA18" s="5">
         <v>1002255</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>473118</v>
+        <v>473145</v>
       </c>
       <c r="BD18" s="5">
-        <v>987631</v>
+        <v>987658</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98540890292390659</v>
+        <v>0.98543584217589331</v>
       </c>
       <c r="BF18" s="5">
         <v>1522890</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>809130</v>
+        <v>809183</v>
       </c>
       <c r="BI18" s="5">
-        <v>1512749</v>
+        <v>1512802</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99334095042977499</v>
+        <v>0.99337575268075828</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>185660</v>
+        <v>185666</v>
       </c>
       <c r="F19" s="5">
-        <v>271124</v>
+        <v>271130</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.98520685332218971</v>
+        <v>0.9852286560438962</v>
       </c>
       <c r="H19" s="5">
         <v>285702</v>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>189612</v>
+        <v>189618</v>
       </c>
       <c r="K19" s="5">
-        <v>277220</v>
+        <v>277226</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.97031172340410643</v>
+        <v>0.97033272430714523</v>
       </c>
       <c r="M19" s="5">
         <v>479092</v>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>327921</v>
+        <v>327929</v>
       </c>
       <c r="P19" s="5">
-        <v>470319</v>
+        <v>470327</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98168827699064065</v>
+        <v>0.98170497524483813</v>
       </c>
       <c r="R19" s="5">
         <v>279649</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>185540</v>
+        <v>185549</v>
       </c>
       <c r="U19" s="5">
-        <v>272357</v>
+        <v>272366</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.9739244552993217</v>
+        <v>0.97395663850040581</v>
       </c>
       <c r="W19" s="5">
         <v>287758</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>188428</v>
+        <v>188439</v>
       </c>
       <c r="Z19" s="5">
-        <v>276658</v>
+        <v>276669</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96142592039144004</v>
+        <v>0.96146414695681792</v>
       </c>
       <c r="AB19" s="5">
         <v>485015</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>331877</v>
+        <v>331892</v>
       </c>
       <c r="AE19" s="5">
-        <v>476435</v>
+        <v>476450</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.98230982546931533</v>
+        <v>0.98234075234786555</v>
       </c>
       <c r="AG19" s="5">
         <v>283525</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>184047</v>
+        <v>184061</v>
       </c>
       <c r="AJ19" s="5">
-        <v>276439</v>
+        <v>276453</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97500749492990035</v>
+        <v>0.97505687329159685</v>
       </c>
       <c r="AL19" s="5">
         <v>295027</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>188095</v>
+        <v>188113</v>
       </c>
       <c r="AO19" s="5">
-        <v>282041</v>
+        <v>282059</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.95598368962840685</v>
+        <v>0.95604470099346839</v>
       </c>
       <c r="AQ19" s="5">
         <v>494059</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>335748</v>
+        <v>335777</v>
       </c>
       <c r="AT19" s="5">
-        <v>487887</v>
+        <v>487916</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.98750756488597513</v>
+        <v>0.98756626232899314</v>
       </c>
       <c r="AV19" s="5">
         <v>287237</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>186005</v>
+        <v>186026</v>
       </c>
       <c r="AY19" s="5">
-        <v>282995</v>
+        <v>283016</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.9852317076142697</v>
+        <v>0.98530481797261493</v>
       </c>
       <c r="BA19" s="5">
         <v>298081</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>191238</v>
+        <v>191258</v>
       </c>
       <c r="BD19" s="5">
-        <v>287430</v>
+        <v>287450</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.96426810162338428</v>
+        <v>0.96433519747987961</v>
       </c>
       <c r="BF19" s="5">
         <v>503654</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>355454</v>
+        <v>355491</v>
       </c>
       <c r="BI19" s="5">
-        <v>494038</v>
+        <v>494075</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.98090752778693313</v>
+        <v>0.98098099091836855</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3275,14 +3275,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5968</v>
+        <v>5969</v>
       </c>
       <c r="AT20" s="5">
-        <v>9743</v>
+        <v>9744</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.0115240863787376</v>
+        <v>1.0116279069767442</v>
       </c>
       <c r="AV20" s="5">
         <v>6297</v>
@@ -3292,14 +3292,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="AY20" s="5">
-        <v>6249</v>
+        <v>6250</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.99237732253454025</v>
+        <v>0.99253612831507065</v>
       </c>
       <c r="BA20" s="5">
         <v>6366</v>
@@ -3309,14 +3309,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3727</v>
+        <v>3728</v>
       </c>
       <c r="BD20" s="5">
-        <v>6291</v>
+        <v>6292</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.9882186616399623</v>
+        <v>0.98837574615142942</v>
       </c>
       <c r="BF20" s="5">
         <v>9853</v>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="BI20" s="5">
-        <v>9896</v>
+        <v>9897</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>1.0043641530498326</v>
+        <v>1.0044656449812239</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3351,14 +3351,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>7619</v>
+        <v>7623</v>
       </c>
       <c r="F21" s="5">
-        <v>9836</v>
+        <v>9840</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.0276878069167277</v>
+        <v>1.0281057360777348</v>
       </c>
       <c r="H21" s="5">
         <v>10057</v>
@@ -3368,14 +3368,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7260</v>
+        <v>7264</v>
       </c>
       <c r="K21" s="5">
-        <v>9977</v>
+        <v>9981</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99204534155314705</v>
+        <v>0.99244307447548974</v>
       </c>
       <c r="M21" s="5">
         <v>12982</v>
@@ -3385,14 +3385,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>9806</v>
+        <v>9813</v>
       </c>
       <c r="P21" s="5">
-        <v>13250</v>
+        <v>13257</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0206439685718687</v>
+        <v>1.0211831767062085</v>
       </c>
       <c r="R21" s="5">
         <v>9811</v>
@@ -3402,14 +3402,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>7324</v>
+        <v>7330</v>
       </c>
       <c r="U21" s="5">
-        <v>10038</v>
+        <v>10044</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0231372948731017</v>
+        <v>1.0237488533278973</v>
       </c>
       <c r="W21" s="5">
         <v>10152</v>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>7383</v>
+        <v>7387</v>
       </c>
       <c r="Z21" s="5">
-        <v>10174</v>
+        <v>10178</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0021670606776989</v>
+        <v>1.002561071710008</v>
       </c>
       <c r="AB21" s="5">
         <v>13231</v>
@@ -3436,14 +3436,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>9729</v>
+        <v>9736</v>
       </c>
       <c r="AE21" s="5">
-        <v>13573</v>
+        <v>13580</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.025848386365354</v>
+        <v>1.0263774469049958</v>
       </c>
       <c r="AG21" s="5">
         <v>10040</v>
@@ -3453,14 +3453,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>7392</v>
+        <v>7397</v>
       </c>
       <c r="AJ21" s="5">
-        <v>10246</v>
+        <v>10251</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0205179282868526</v>
+        <v>1.02101593625498</v>
       </c>
       <c r="AL21" s="5">
         <v>10211</v>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>7519</v>
+        <v>7524</v>
       </c>
       <c r="AO21" s="5">
-        <v>10398</v>
+        <v>10403</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0183135833904613</v>
+        <v>1.0188032513955538</v>
       </c>
       <c r="AQ21" s="5">
         <v>13473</v>
@@ -3487,14 +3487,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10087</v>
+        <v>10095</v>
       </c>
       <c r="AT21" s="5">
-        <v>13901</v>
+        <v>13909</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.0317672381800638</v>
+        <v>1.0323610183329621</v>
       </c>
       <c r="AV21" s="5">
         <v>10213</v>
@@ -3504,14 +3504,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>7702</v>
+        <v>7707</v>
       </c>
       <c r="AY21" s="5">
-        <v>10506</v>
+        <v>10511</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0286889258787819</v>
+        <v>1.0291784979927543</v>
       </c>
       <c r="BA21" s="5">
         <v>10449</v>
@@ -3521,14 +3521,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>7808</v>
+        <v>7814</v>
       </c>
       <c r="BD21" s="5">
-        <v>10646</v>
+        <v>10652</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0188534788017991</v>
+        <v>1.0194276964302804</v>
       </c>
       <c r="BF21" s="5">
         <v>13925</v>
@@ -3538,14 +3538,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>10893</v>
+        <v>10904</v>
       </c>
       <c r="BI21" s="5">
-        <v>14341</v>
+        <v>14352</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0298743267504489</v>
+        <v>1.0306642728904847</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>4202</v>
       </c>
       <c r="F22" s="5">
-        <v>6228</v>
+        <v>6230</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>1.0112031173891864</v>
+        <v>1.0115278454294527</v>
       </c>
       <c r="H22" s="5">
         <v>6265</v>
@@ -3580,14 +3580,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4371</v>
+        <v>4373</v>
       </c>
       <c r="K22" s="5">
-        <v>6314</v>
+        <v>6316</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.0078212290502793</v>
+        <v>1.0081404628890662</v>
       </c>
       <c r="M22" s="5">
         <v>7537</v>
@@ -3597,14 +3597,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5104</v>
+        <v>5106</v>
       </c>
       <c r="P22" s="5">
-        <v>7612</v>
+        <v>7614</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.009950908849675</v>
+        <v>1.0102162664189995</v>
       </c>
       <c r="R22" s="5">
         <v>6306</v>
@@ -3614,14 +3614,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4407</v>
+        <v>4409</v>
       </c>
       <c r="U22" s="5">
-        <v>6365</v>
+        <v>6367</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0093561687281953</v>
+        <v>1.0096733269901681</v>
       </c>
       <c r="W22" s="5">
         <v>6435</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4398</v>
+        <v>4400</v>
       </c>
       <c r="Z22" s="5">
-        <v>6440</v>
+        <v>6442</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>1.0007770007770007</v>
+        <v>1.001087801087801</v>
       </c>
       <c r="AB22" s="5">
         <v>7668</v>
@@ -3648,14 +3648,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5295</v>
+        <v>5297</v>
       </c>
       <c r="AE22" s="5">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0070422535211268</v>
+        <v>1.0073030777256129</v>
       </c>
       <c r="AG22" s="5">
         <v>6422</v>
@@ -3665,14 +3665,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4406</v>
+        <v>4408</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6458</v>
+        <v>6460</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0056057303020867</v>
+        <v>1.0059171597633136</v>
       </c>
       <c r="AL22" s="5">
         <v>6508</v>
@@ -3682,14 +3682,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4428</v>
+        <v>4429</v>
       </c>
       <c r="AO22" s="5">
-        <v>6508</v>
+        <v>6509</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>1.0001536570374923</v>
       </c>
       <c r="AQ22" s="5">
         <v>7781</v>
@@ -3699,14 +3699,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5399</v>
+        <v>5400</v>
       </c>
       <c r="AT22" s="5">
-        <v>7815</v>
+        <v>7816</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0043696183009896</v>
+        <v>1.0044981364863128</v>
       </c>
       <c r="AV22" s="5">
         <v>6603</v>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="AY22" s="5">
-        <v>6522</v>
+        <v>6523</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.987732848705134</v>
+        <v>0.98788429501741637</v>
       </c>
       <c r="BA22" s="5">
         <v>6608</v>
@@ -3733,14 +3733,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4417</v>
+        <v>4419</v>
       </c>
       <c r="BD22" s="5">
-        <v>6562</v>
+        <v>6564</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.99303874092009681</v>
+        <v>0.9933414043583535</v>
       </c>
       <c r="BF22" s="5">
         <v>7906</v>
@@ -3750,14 +3750,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5607</v>
+        <v>5610</v>
       </c>
       <c r="BI22" s="5">
-        <v>7955</v>
+        <v>7958</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>1.0061978244371363</v>
+        <v>1.0065772830761448</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>7373</v>
+        <v>7374</v>
       </c>
       <c r="F23" s="5">
-        <v>8492</v>
+        <v>8493</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.96499999999999997</v>
+        <v>0.96511363636363634</v>
       </c>
       <c r="H23" s="5">
         <v>8763</v>
@@ -3792,14 +3792,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7007</v>
+        <v>7008</v>
       </c>
       <c r="K23" s="5">
-        <v>8525</v>
+        <v>8526</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.97284035147780445</v>
+        <v>0.9729544676480657</v>
       </c>
       <c r="M23" s="5">
         <v>10654</v>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8128</v>
+        <v>8129</v>
       </c>
       <c r="P23" s="5">
-        <v>10513</v>
+        <v>10514</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98676553407171019</v>
+        <v>0.98685939553219448</v>
       </c>
       <c r="R23" s="5">
         <v>8621</v>
@@ -3826,14 +3826,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6404</v>
+        <v>6405</v>
       </c>
       <c r="U23" s="5">
-        <v>8393</v>
+        <v>8394</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.97355295209372461</v>
+        <v>0.97366894791787495</v>
       </c>
       <c r="W23" s="5">
         <v>8774</v>
@@ -3843,14 +3843,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6294</v>
+        <v>6295</v>
       </c>
       <c r="Z23" s="5">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.96307271483929791</v>
+        <v>0.96318668794164575</v>
       </c>
       <c r="AB23" s="5">
         <v>10734</v>
@@ -3860,14 +3860,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>7676</v>
+        <v>7677</v>
       </c>
       <c r="AE23" s="5">
-        <v>10581</v>
+        <v>10582</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98574622694242597</v>
+        <v>0.98583938885783495</v>
       </c>
       <c r="AG23" s="5">
         <v>8589</v>
@@ -3877,14 +3877,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6124</v>
+        <v>6125</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8447</v>
+        <v>8448</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.98346722552101529</v>
+        <v>0.98358365351030386</v>
       </c>
       <c r="AL23" s="5">
         <v>8660</v>
@@ -3894,14 +3894,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>5946</v>
+        <v>5947</v>
       </c>
       <c r="AO23" s="5">
-        <v>8520</v>
+        <v>8521</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.9838337182448037</v>
+        <v>0.98394919168591222</v>
       </c>
       <c r="AQ23" s="5">
         <v>10698</v>
@@ -3911,14 +3911,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>7645</v>
+        <v>7646</v>
       </c>
       <c r="AT23" s="5">
-        <v>10752</v>
+        <v>10753</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>1.0050476724621424</v>
+        <v>1.005141147878108</v>
       </c>
       <c r="AV23" s="5">
         <v>8445</v>
@@ -3928,14 +3928,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6083</v>
+        <v>6084</v>
       </c>
       <c r="AY23" s="5">
-        <v>8503</v>
+        <v>8504</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>1.0068679692125517</v>
+        <v>1.0069863824748371</v>
       </c>
       <c r="BA23" s="5">
         <v>8623</v>
@@ -3945,14 +3945,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="BD23" s="5">
-        <v>8550</v>
+        <v>8551</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.9915342688159573</v>
+        <v>0.99165023773628669</v>
       </c>
       <c r="BF23" s="5">
         <v>11023</v>
@@ -3962,14 +3962,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>7960</v>
+        <v>7961</v>
       </c>
       <c r="BI23" s="5">
-        <v>10938</v>
+        <v>10939</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.99228885058514016</v>
+        <v>0.99237956999002086</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4038,14 +4038,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4151</v>
+        <v>4152</v>
       </c>
       <c r="U24" s="5">
-        <v>5734</v>
+        <v>5735</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98505411441333102</v>
+        <v>0.9852259062016836</v>
       </c>
       <c r="W24" s="5">
         <v>5925</v>
@@ -4055,14 +4055,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4401</v>
+        <v>4402</v>
       </c>
       <c r="Z24" s="5">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.98025316455696199</v>
+        <v>0.98042194092827006</v>
       </c>
       <c r="AB24" s="5">
         <v>6940</v>
@@ -4072,14 +4072,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5239</v>
+        <v>5240</v>
       </c>
       <c r="AE24" s="5">
-        <v>6816</v>
+        <v>6817</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.98213256484149858</v>
+        <v>0.9822766570605187</v>
       </c>
       <c r="AG24" s="5">
         <v>6076</v>
@@ -4089,14 +4089,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4621</v>
+        <v>4622</v>
       </c>
       <c r="AJ24" s="5">
-        <v>5953</v>
+        <v>5954</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.97975641869651087</v>
+        <v>0.97992100065832788</v>
       </c>
       <c r="AL24" s="5">
         <v>6181</v>
@@ -4386,14 +4386,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>16936</v>
+        <v>16937</v>
       </c>
       <c r="BI25" s="5">
-        <v>27806</v>
+        <v>27807</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>1.0060421867650784</v>
+        <v>1.0060783675241507</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4411,14 +4411,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>8941</v>
+        <v>8944</v>
       </c>
       <c r="F26" s="5">
-        <v>13319</v>
+        <v>13322</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.98404137421499815</v>
+        <v>0.98426302179534542</v>
       </c>
       <c r="H26" s="5">
         <v>13884</v>
@@ -4428,14 +4428,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9408</v>
+        <v>9411</v>
       </c>
       <c r="K26" s="5">
-        <v>13914</v>
+        <v>13917</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>1.002160760587727</v>
+        <v>1.0023768366464996</v>
       </c>
       <c r="M26" s="5">
         <v>25920</v>
@@ -4445,14 +4445,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>17762</v>
+        <v>17768</v>
       </c>
       <c r="P26" s="5">
-        <v>26341</v>
+        <v>26347</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>1.0162422839506173</v>
+        <v>1.0164737654320988</v>
       </c>
       <c r="R26" s="5">
         <v>13869</v>
@@ -4462,14 +4462,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9527</v>
+        <v>9531</v>
       </c>
       <c r="U26" s="5">
-        <v>14117</v>
+        <v>14121</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>1.0178816064604514</v>
+        <v>1.018170019467878</v>
       </c>
       <c r="W26" s="5">
         <v>14474</v>
@@ -4479,14 +4479,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9566</v>
+        <v>9571</v>
       </c>
       <c r="Z26" s="5">
-        <v>14424</v>
+        <v>14429</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.99654552991571088</v>
+        <v>0.99689097692413986</v>
       </c>
       <c r="AB26" s="5">
         <v>27035</v>
@@ -4496,14 +4496,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>18146</v>
+        <v>18156</v>
       </c>
       <c r="AE26" s="5">
-        <v>27014</v>
+        <v>27024</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.99922322914740147</v>
+        <v>0.99959312002959122</v>
       </c>
       <c r="AG26" s="5">
         <v>14053</v>
@@ -4513,14 +4513,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9388</v>
+        <v>9393</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14056</v>
+        <v>14061</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>1.0002134775492777</v>
+        <v>1.0005692734647407</v>
       </c>
       <c r="AL26" s="5">
         <v>14372</v>
@@ -4530,14 +4530,14 @@
       </c>
       <c r="AN26" s="3">
         <f>AO26-AM26</f>
-        <v>9109</v>
+        <v>9114</v>
       </c>
       <c r="AO26" s="5">
-        <v>14217</v>
+        <v>14222</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.98921514055107151</v>
+        <v>0.9895630392429724</v>
       </c>
       <c r="AQ26" s="5">
         <v>27267</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="AS26" s="3">
         <f>AT26-AR26</f>
-        <v>19120</v>
+        <v>19131</v>
       </c>
       <c r="AT26" s="5">
-        <v>27119</v>
+        <v>27130</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99457219349396708</v>
+        <v>0.99497561154509118</v>
       </c>
       <c r="AV26" s="5">
         <v>14007</v>
@@ -4564,14 +4564,14 @@
       </c>
       <c r="AX26" s="3">
         <f>AY26-AW26</f>
-        <v>9378</v>
+        <v>9383</v>
       </c>
       <c r="AY26" s="5">
-        <v>13984</v>
+        <v>13989</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99835796387520526</v>
+        <v>0.99871492825016062</v>
       </c>
       <c r="BA26" s="5">
         <v>14398</v>
@@ -4581,14 +4581,14 @@
       </c>
       <c r="BC26" s="3">
         <f>BD26-BB26</f>
-        <v>9285</v>
+        <v>9290</v>
       </c>
       <c r="BD26" s="5">
-        <v>14079</v>
+        <v>14084</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97784414502014172</v>
+        <v>0.9781914154743715</v>
       </c>
       <c r="BF26" s="5">
         <v>27339</v>
@@ -4598,14 +4598,14 @@
       </c>
       <c r="BH26" s="3">
         <f>BI26-BG26</f>
-        <v>19185</v>
+        <v>19196</v>
       </c>
       <c r="BI26" s="5">
-        <v>27138</v>
+        <v>27149</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99264786568638208</v>
+        <v>0.99305022129558507</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>74114</v>
+        <v>74120</v>
       </c>
       <c r="F27" s="5">
-        <v>120705</v>
+        <v>120711</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>1.0018508988894608</v>
+        <v>1.0019006988595807</v>
       </c>
       <c r="H27" s="5">
         <v>123649</v>
@@ -4640,14 +4640,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>75146</v>
+        <v>75153</v>
       </c>
       <c r="K27" s="5">
-        <v>122568</v>
+        <v>122575</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.9912575111808426</v>
+        <v>0.99131412304183619</v>
       </c>
       <c r="M27" s="5">
         <v>182121</v>
@@ -4657,14 +4657,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>115197</v>
+        <v>115211</v>
       </c>
       <c r="P27" s="5">
-        <v>181407</v>
+        <v>181421</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99607952954354517</v>
+        <v>0.99615640151327967</v>
       </c>
       <c r="R27" s="5">
         <v>122848</v>
@@ -4674,14 +4674,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>73647</v>
+        <v>73656</v>
       </c>
       <c r="U27" s="5">
-        <v>121972</v>
+        <v>121981</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99286923678041161</v>
+        <v>0.99294249804636625</v>
       </c>
       <c r="W27" s="5">
         <v>125846</v>
@@ -4691,14 +4691,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>74942</v>
+        <v>74956</v>
       </c>
       <c r="Z27" s="5">
-        <v>123325</v>
+        <v>123339</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.9799675794224687</v>
+        <v>0.98007882650223288</v>
       </c>
       <c r="AB27" s="5">
         <v>184102</v>
@@ -4708,14 +4708,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>113341</v>
+        <v>113363</v>
       </c>
       <c r="AE27" s="5">
-        <v>183151</v>
+        <v>183173</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99483438528641732</v>
+        <v>0.99495388425981246</v>
       </c>
       <c r="AG27" s="5">
         <v>124176</v>
@@ -4725,14 +4725,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>72885</v>
+        <v>72900</v>
       </c>
       <c r="AJ27" s="5">
-        <v>123148</v>
+        <v>123163</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99172142765107585</v>
+        <v>0.99184222394021393</v>
       </c>
       <c r="AL27" s="5">
         <v>126536</v>
@@ -4742,14 +4742,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" ref="AN27:AN33" si="24">AO27-AM27</f>
-        <v>74019</v>
+        <v>74037</v>
       </c>
       <c r="AO27" s="5">
-        <v>124083</v>
+        <v>124101</v>
       </c>
       <c r="AP27" s="4">
         <f>AO27/AL27</f>
-        <v>0.98061421255611048</v>
+        <v>0.98075646456344434</v>
       </c>
       <c r="AQ27" s="5">
         <v>184835</v>
@@ -4759,14 +4759,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" ref="AS27:AS33" si="25">AT27-AR27</f>
-        <v>115215</v>
+        <v>115246</v>
       </c>
       <c r="AT27" s="5">
-        <v>184668</v>
+        <v>184699</v>
       </c>
       <c r="AU27" s="4">
         <f>AT27/AQ27</f>
-        <v>0.99909649146536095</v>
+        <v>0.99926420861849763</v>
       </c>
       <c r="AV27" s="5">
         <v>124975</v>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" ref="AX27:AX33" si="26">AY27-AW27</f>
-        <v>73612</v>
+        <v>73633</v>
       </c>
       <c r="AY27" s="5">
-        <v>124197</v>
+        <v>124218</v>
       </c>
       <c r="AZ27" s="4">
         <f>AY27/AV27</f>
-        <v>0.99377475495099021</v>
+        <v>0.99394278855771157</v>
       </c>
       <c r="BA27" s="5">
         <v>127493</v>
@@ -4793,14 +4793,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" ref="BC27:BC33" si="27">BD27-BB27</f>
-        <v>74233</v>
+        <v>74257</v>
       </c>
       <c r="BD27" s="5">
-        <v>125327</v>
+        <v>125351</v>
       </c>
       <c r="BE27" s="4">
         <f>BD27/BA27</f>
-        <v>0.98301083196724526</v>
+        <v>0.983199077596417</v>
       </c>
       <c r="BF27" s="5">
         <v>187636</v>
@@ -4810,14 +4810,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>121561</v>
+        <v>121604</v>
       </c>
       <c r="BI27" s="5">
-        <v>186109</v>
+        <v>186152</v>
       </c>
       <c r="BJ27" s="4">
         <f>BI27/BF27</f>
-        <v>0.99186190283314501</v>
+        <v>0.99209106994393403</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4835,14 +4835,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>164960</v>
+        <v>164961</v>
       </c>
       <c r="F28" s="5">
-        <v>379833</v>
+        <v>379834</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99378610599464168</v>
+        <v>0.99378872237106497</v>
       </c>
       <c r="H28" s="5">
         <v>389922</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>167360</v>
+        <v>167362</v>
       </c>
       <c r="K28" s="5">
-        <v>384969</v>
+        <v>384971</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.9872974594918984</v>
+        <v>0.9873025887228728</v>
       </c>
       <c r="M28" s="5">
         <v>650891</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>302130</v>
+        <v>302138</v>
       </c>
       <c r="P28" s="5">
-        <v>646834</v>
+        <v>646842</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99376700553548902</v>
+        <v>0.99377929637988538</v>
       </c>
       <c r="R28" s="5">
         <v>389073</v>
@@ -4886,14 +4886,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>169117</v>
+        <v>169121</v>
       </c>
       <c r="U28" s="5">
-        <v>386330</v>
+        <v>386334</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99294990914301429</v>
+        <v>0.99296018999005331</v>
       </c>
       <c r="W28" s="5">
         <v>397763</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>171203</v>
+        <v>171208</v>
       </c>
       <c r="Z28" s="5">
-        <v>391703</v>
+        <v>391708</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.98476479712793796</v>
+        <v>0.98477736742733735</v>
       </c>
       <c r="AB28" s="5">
         <v>660941</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>292806</v>
+        <v>292824</v>
       </c>
       <c r="AE28" s="5">
-        <v>657444</v>
+        <v>657462</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99470905875108373</v>
+        <v>0.99473629264941954</v>
       </c>
       <c r="AG28" s="5">
         <v>397417</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>163418</v>
+        <v>163426</v>
       </c>
       <c r="AJ28" s="5">
-        <v>394431</v>
+        <v>394439</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.9924864814539891</v>
+        <v>0.99250661144339569</v>
       </c>
       <c r="AL28" s="5">
         <v>405895</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="24"/>
-        <v>168516</v>
+        <v>168525</v>
       </c>
       <c r="AO28" s="5">
-        <v>398831</v>
+        <v>398840</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" ref="AP28:AP33" si="28">AO28/AL28</f>
-        <v>0.98259648431244528</v>
+        <v>0.98261865753458411</v>
       </c>
       <c r="AQ28" s="5">
         <v>670091</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="25"/>
-        <v>295962</v>
+        <v>295986</v>
       </c>
       <c r="AT28" s="5">
-        <v>667090</v>
+        <v>667114</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" ref="AU28:AU33" si="29">AT28/AQ28</f>
-        <v>0.9955215037957531</v>
+        <v>0.99555731982671014</v>
       </c>
       <c r="AV28" s="5">
         <v>405395</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="26"/>
-        <v>166492</v>
+        <v>166507</v>
       </c>
       <c r="AY28" s="5">
-        <v>402195</v>
+        <v>402210</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" ref="AZ28:AZ33" si="30">AY28/AV28</f>
-        <v>0.99210646406591108</v>
+        <v>0.99214346501560202</v>
       </c>
       <c r="BA28" s="5">
         <v>412255</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="27"/>
-        <v>167728</v>
+        <v>167744</v>
       </c>
       <c r="BD28" s="5">
-        <v>406734</v>
+        <v>406750</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" ref="BE28:BE33" si="31">BD28/BA28</f>
-        <v>0.98660780342263887</v>
+        <v>0.98664661435276713</v>
       </c>
       <c r="BF28" s="5">
         <v>680839</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>320735</v>
+        <v>320773</v>
       </c>
       <c r="BI28" s="5">
-        <v>677423</v>
+        <v>677461</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99498266109902633</v>
+        <v>0.99503847458797157</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>93975</v>
+        <v>93977</v>
       </c>
       <c r="P29" s="5">
-        <v>174568</v>
+        <v>174570</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98828671229697063</v>
+        <v>0.98829803495303925</v>
       </c>
       <c r="R29" s="5">
         <v>129740</v>
@@ -5098,14 +5098,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>67082</v>
+        <v>67084</v>
       </c>
       <c r="U29" s="5">
-        <v>128522</v>
+        <v>128524</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.99061199321720361</v>
+        <v>0.99062740866348076</v>
       </c>
       <c r="W29" s="5">
         <v>131766</v>
@@ -5115,14 +5115,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>67103</v>
+        <v>67104</v>
       </c>
       <c r="Z29" s="5">
-        <v>129609</v>
+        <v>129610</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.9836300714903693</v>
+        <v>0.98363766070154668</v>
       </c>
       <c r="AB29" s="5">
         <v>178083</v>
@@ -5132,14 +5132,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>93885</v>
+        <v>93892</v>
       </c>
       <c r="AE29" s="5">
-        <v>176666</v>
+        <v>176673</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.99204303611237454</v>
+        <v>0.99208234362628667</v>
       </c>
       <c r="AG29" s="5">
         <v>131984</v>
@@ -5149,14 +5149,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>68240</v>
+        <v>68242</v>
       </c>
       <c r="AJ29" s="5">
-        <v>130625</v>
+        <v>130627</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98970329736937812</v>
+        <v>0.9897184507212996</v>
       </c>
       <c r="AL29" s="5">
         <v>133676</v>
@@ -5166,14 +5166,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="24"/>
-        <v>68583</v>
+        <v>68586</v>
       </c>
       <c r="AO29" s="5">
-        <v>131853</v>
+        <v>131856</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="28"/>
-        <v>0.9863625482509949</v>
+        <v>0.98638499057422424</v>
       </c>
       <c r="AQ29" s="5">
         <v>179800</v>
@@ -5183,14 +5183,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="25"/>
-        <v>93900</v>
+        <v>93905</v>
       </c>
       <c r="AT29" s="5">
-        <v>179265</v>
+        <v>179270</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="29"/>
-        <v>0.99702447163515018</v>
+        <v>0.99705228031145721</v>
       </c>
       <c r="AV29" s="5">
         <v>134089</v>
@@ -5217,14 +5217,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="27"/>
-        <v>68606</v>
+        <v>68607</v>
       </c>
       <c r="BD29" s="5">
-        <v>134433</v>
+        <v>134434</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="31"/>
-        <v>0.98805656411236387</v>
+        <v>0.9880639139190639</v>
       </c>
       <c r="BF29" s="5">
         <v>182623</v>
@@ -5234,14 +5234,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>100480</v>
+        <v>100484</v>
       </c>
       <c r="BI29" s="5">
-        <v>181755</v>
+        <v>181759</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.99524703898194644</v>
+        <v>0.99526894202811256</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5259,14 +5259,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>95638</v>
+        <v>95640</v>
       </c>
       <c r="F30" s="5">
-        <v>166222</v>
+        <v>166224</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99597349215669828</v>
+        <v>0.99598547581099384</v>
       </c>
       <c r="H30" s="5">
         <v>172134</v>
@@ -5276,14 +5276,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="K30" s="5">
-        <v>169427</v>
+        <v>169430</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98427387965189905</v>
+        <v>0.98429130793451614</v>
       </c>
       <c r="M30" s="5">
         <v>289249</v>
@@ -5293,14 +5293,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>172711</v>
+        <v>172719</v>
       </c>
       <c r="P30" s="5">
-        <v>286742</v>
+        <v>286750</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.99133272716586751</v>
+        <v>0.99136038499700951</v>
       </c>
       <c r="R30" s="5">
         <v>169142</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>95690</v>
+        <v>95693</v>
       </c>
       <c r="U30" s="5">
-        <v>167648</v>
+        <v>167651</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99116718496884271</v>
+        <v>0.99118492154521054</v>
       </c>
       <c r="W30" s="5">
         <v>174259</v>
@@ -5327,14 +5327,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>95210</v>
+        <v>95215</v>
       </c>
       <c r="Z30" s="5">
-        <v>170786</v>
+        <v>170791</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.98006989595946259</v>
+        <v>0.98009858888206636</v>
       </c>
       <c r="AB30" s="5">
         <v>293307</v>
@@ -5344,14 +5344,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>173225</v>
+        <v>173233</v>
       </c>
       <c r="AE30" s="5">
-        <v>291150</v>
+        <v>291158</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99264593071423457</v>
+        <v>0.99267320589007424</v>
       </c>
       <c r="AG30" s="5">
         <v>172053</v>
@@ -5361,14 +5361,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>94757</v>
+        <v>94761</v>
       </c>
       <c r="AJ30" s="5">
-        <v>170785</v>
+        <v>170789</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.99263017791029506</v>
+        <v>0.99265342656042033</v>
       </c>
       <c r="AL30" s="5">
         <v>176835</v>
@@ -5378,14 +5378,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="24"/>
-        <v>96562</v>
+        <v>96569</v>
       </c>
       <c r="AO30" s="5">
-        <v>173510</v>
+        <v>173517</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="28"/>
-        <v>0.98119716119546474</v>
+        <v>0.9812367461192637</v>
       </c>
       <c r="AQ30" s="5">
         <v>297651</v>
@@ -5395,14 +5395,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="25"/>
-        <v>175594</v>
+        <v>175608</v>
       </c>
       <c r="AT30" s="5">
-        <v>296810</v>
+        <v>296824</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="29"/>
-        <v>0.99717454334102695</v>
+        <v>0.9972215782913546</v>
       </c>
       <c r="AV30" s="5">
         <v>175428</v>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="26"/>
-        <v>96837</v>
+        <v>96847</v>
       </c>
       <c r="AY30" s="5">
-        <v>174072</v>
+        <v>174082</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="30"/>
-        <v>0.99227033312812096</v>
+        <v>0.99232733657112893</v>
       </c>
       <c r="BA30" s="5">
         <v>179593</v>
@@ -5429,14 +5429,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="27"/>
-        <v>98788</v>
+        <v>98799</v>
       </c>
       <c r="BD30" s="5">
-        <v>176050</v>
+        <v>176061</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="31"/>
-        <v>0.98027205960143216</v>
+        <v>0.98033330920470174</v>
       </c>
       <c r="BF30" s="5">
         <v>302258</v>
@@ -5446,14 +5446,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>185063</v>
+        <v>185084</v>
       </c>
       <c r="BI30" s="5">
-        <v>300096</v>
+        <v>300117</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.992847170298222</v>
+        <v>0.99291664736748075</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35551</v>
+        <v>35554</v>
       </c>
       <c r="F31" s="5">
-        <v>74331</v>
+        <v>74334</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>0.9975976379009529</v>
+        <v>0.99763790095289218</v>
       </c>
       <c r="H31" s="5">
         <v>76671</v>
@@ -5488,14 +5488,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35328</v>
+        <v>35330</v>
       </c>
       <c r="K31" s="5">
-        <v>75512</v>
+        <v>75514</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.98488346310860686</v>
+        <v>0.98490954859073188</v>
       </c>
       <c r="M31" s="5">
         <v>133745</v>
@@ -5505,14 +5505,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>70011</v>
+        <v>70017</v>
       </c>
       <c r="P31" s="5">
-        <v>133845</v>
+        <v>133851</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.000747691502486</v>
+        <v>1.0007925529926351</v>
       </c>
       <c r="R31" s="5">
         <v>74974</v>
@@ -5522,14 +5522,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34161</v>
+        <v>34162</v>
       </c>
       <c r="U31" s="5">
-        <v>74780</v>
+        <v>74781</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>0.99741243631125454</v>
+        <v>0.99742577426841306</v>
       </c>
       <c r="W31" s="5">
         <v>77586</v>
@@ -5539,14 +5539,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>34637</v>
+        <v>34639</v>
       </c>
       <c r="Z31" s="5">
-        <v>75895</v>
+        <v>75897</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.97820483076843756</v>
+        <v>0.97823060861495625</v>
       </c>
       <c r="AB31" s="5">
         <v>135116</v>
@@ -5556,14 +5556,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>70311</v>
+        <v>70315</v>
       </c>
       <c r="AE31" s="5">
-        <v>135424</v>
+        <v>135428</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0022795227804258</v>
+        <v>1.0023091269723794</v>
       </c>
       <c r="AG31" s="5">
         <v>76230</v>
@@ -5573,14 +5573,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>33309</v>
+        <v>33311</v>
       </c>
       <c r="AJ31" s="5">
-        <v>75674</v>
+        <v>75676</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>0.9927062836153745</v>
+        <v>0.99273252000524725</v>
       </c>
       <c r="AL31" s="5">
         <v>77611</v>
@@ -5590,14 +5590,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="24"/>
-        <v>33392</v>
+        <v>33394</v>
       </c>
       <c r="AO31" s="5">
-        <v>76714</v>
+        <v>76716</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="28"/>
-        <v>0.98844235997474583</v>
+        <v>0.988468129517723</v>
       </c>
       <c r="AQ31" s="5">
         <v>136879</v>
@@ -5607,14 +5607,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="25"/>
-        <v>69314</v>
+        <v>69318</v>
       </c>
       <c r="AT31" s="5">
-        <v>137676</v>
+        <v>137680</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="29"/>
-        <v>1.0058226608902754</v>
+        <v>1.0058518837805652</v>
       </c>
       <c r="AV31" s="5">
         <v>76719</v>
@@ -5624,14 +5624,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="26"/>
-        <v>33132</v>
+        <v>33135</v>
       </c>
       <c r="AY31" s="5">
-        <v>76695</v>
+        <v>76698</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="30"/>
-        <v>0.999687170062175</v>
+        <v>0.99972627380440304</v>
       </c>
       <c r="BA31" s="5">
         <v>78720</v>
@@ -5641,14 +5641,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="27"/>
-        <v>33792</v>
+        <v>33795</v>
       </c>
       <c r="BD31" s="5">
-        <v>78205</v>
+        <v>78208</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="31"/>
-        <v>0.99345782520325199</v>
+        <v>0.99349593495934962</v>
       </c>
       <c r="BF31" s="5">
         <v>140181</v>
@@ -5658,14 +5658,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>76253</v>
+        <v>76259</v>
       </c>
       <c r="BI31" s="5">
-        <v>140486</v>
+        <v>140492</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.0021757584836746</v>
+        <v>1.002218560289911</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5717,14 +5717,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>233990</v>
+        <v>233991</v>
       </c>
       <c r="P32" s="5">
-        <v>439424</v>
+        <v>439425</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99634722867799608</v>
+        <v>0.99634949607174039</v>
       </c>
       <c r="R32" s="5">
         <v>206418</v>
@@ -5734,14 +5734,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>92298</v>
+        <v>92300</v>
       </c>
       <c r="U32" s="5">
-        <v>204374</v>
+        <v>204376</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99009776279200457</v>
+        <v>0.99010745186950755</v>
       </c>
       <c r="W32" s="5">
         <v>212709</v>
@@ -5751,14 +5751,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>95923</v>
+        <v>95924</v>
       </c>
       <c r="Z32" s="5">
-        <v>208792</v>
+        <v>208793</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.98158517035010273</v>
+        <v>0.98158987160862965</v>
       </c>
       <c r="AB32" s="5">
         <v>446806</v>
@@ -5768,14 +5768,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>237840</v>
+        <v>237846</v>
       </c>
       <c r="AE32" s="5">
-        <v>445868</v>
+        <v>445874</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.9979006548703464</v>
+        <v>0.99791408351723121</v>
       </c>
       <c r="AG32" s="5">
         <v>210129</v>
@@ -5785,14 +5785,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>92551</v>
+        <v>92553</v>
       </c>
       <c r="AJ32" s="5">
-        <v>208777</v>
+        <v>208779</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99356585716393264</v>
+        <v>0.9935753751267079</v>
       </c>
       <c r="AL32" s="5">
         <v>217332</v>
@@ -5802,14 +5802,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="24"/>
-        <v>93050</v>
+        <v>93052</v>
       </c>
       <c r="AO32" s="5">
-        <v>212385</v>
+        <v>212387</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="28"/>
-        <v>0.97723759041466507</v>
+        <v>0.97724679292510996</v>
       </c>
       <c r="AQ32" s="5">
         <v>453805</v>
@@ -5819,14 +5819,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="25"/>
-        <v>229524</v>
+        <v>229535</v>
       </c>
       <c r="AT32" s="5">
-        <v>453638</v>
+        <v>453649</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="29"/>
-        <v>0.99963200052886148</v>
+        <v>0.99965624001498443</v>
       </c>
       <c r="AV32" s="5">
         <v>213428</v>
@@ -5836,14 +5836,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="26"/>
-        <v>91562</v>
+        <v>91566</v>
       </c>
       <c r="AY32" s="5">
-        <v>212589</v>
+        <v>212593</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="30"/>
-        <v>0.99606893191146428</v>
+        <v>0.99608767359484229</v>
       </c>
       <c r="BA32" s="5">
         <v>220509</v>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="27"/>
-        <v>94375</v>
+        <v>94377</v>
       </c>
       <c r="BD32" s="5">
-        <v>217105</v>
+        <v>217107</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="31"/>
-        <v>0.98456298835875178</v>
+        <v>0.98457205828333538</v>
       </c>
       <c r="BF32" s="5">
         <v>463937</v>
@@ -5870,14 +5870,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>253933</v>
+        <v>253946</v>
       </c>
       <c r="BI32" s="5">
-        <v>461907</v>
+        <v>461920</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99562440589993895</v>
+        <v>0.99565242694589995</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5895,14 +5895,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>96267</v>
+        <v>96268</v>
       </c>
       <c r="F33" s="5">
-        <v>620526</v>
+        <v>620527</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99924476042480215</v>
+        <v>0.9992463707437258</v>
       </c>
       <c r="H33" s="5">
         <v>630476</v>
@@ -5912,14 +5912,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="K33" s="5">
-        <v>628335</v>
+        <v>628336</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99660415305261418</v>
+        <v>0.99660573915581241</v>
       </c>
       <c r="M33" s="5">
         <v>1032030</v>
@@ -5929,14 +5929,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>184047</v>
+        <v>184051</v>
       </c>
       <c r="P33" s="5">
-        <v>1033747</v>
+        <v>1033751</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0016637113262212</v>
+        <v>1.0016675871825431</v>
       </c>
       <c r="R33" s="5">
         <v>629419</v>
@@ -5946,14 +5946,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>97170</v>
+        <v>97173</v>
       </c>
       <c r="U33" s="5">
-        <v>627896</v>
+        <v>627899</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>0.99758030818898058</v>
+        <v>0.99758507448933065</v>
       </c>
       <c r="W33" s="5">
         <v>637378</v>
@@ -5963,14 +5963,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>101396</v>
+        <v>101397</v>
       </c>
       <c r="Z33" s="5">
-        <v>634256</v>
+        <v>634257</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99510180771849677</v>
+        <v>0.99510337664619741</v>
       </c>
       <c r="AB33" s="5">
         <v>1041984</v>
@@ -5980,14 +5980,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>184406</v>
+        <v>184408</v>
       </c>
       <c r="AE33" s="5">
-        <v>1043585</v>
+        <v>1043587</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0015364919231005</v>
+        <v>1.0015384113383698</v>
       </c>
       <c r="AG33" s="5">
         <v>638215</v>
@@ -5997,14 +5997,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>78014</v>
+        <v>78015</v>
       </c>
       <c r="AJ33" s="5">
-        <v>637053</v>
+        <v>637054</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>0.99817929694538676</v>
+        <v>0.99818086381548543</v>
       </c>
       <c r="AL33" s="5">
         <v>645318</v>
@@ -6014,14 +6014,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="24"/>
-        <v>94792</v>
+        <v>94794</v>
       </c>
       <c r="AO33" s="5">
-        <v>641697</v>
+        <v>641699</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="28"/>
-        <v>0.99438881295733261</v>
+        <v>0.9943919122045255</v>
       </c>
       <c r="AQ33" s="5">
         <v>1053133</v>
@@ -6031,14 +6031,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="25"/>
-        <v>167717</v>
+        <v>167724</v>
       </c>
       <c r="AT33" s="5">
-        <v>1055173</v>
+        <v>1055180</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="29"/>
-        <v>1.001937077273241</v>
+        <v>1.0019437241070217</v>
       </c>
       <c r="AV33" s="5">
         <v>647979</v>
@@ -6048,14 +6048,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="26"/>
-        <v>89176</v>
+        <v>89182</v>
       </c>
       <c r="AY33" s="5">
-        <v>647879</v>
+        <v>647885</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="30"/>
-        <v>0.99984567401104052</v>
+        <v>0.99985493357037802</v>
       </c>
       <c r="BA33" s="5">
         <v>657743</v>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="27"/>
-        <v>89579</v>
+        <v>89584</v>
       </c>
       <c r="BD33" s="5">
-        <v>657184</v>
+        <v>657189</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="31"/>
-        <v>0.99915012398459579</v>
+        <v>0.99915772573786421</v>
       </c>
       <c r="BF33" s="5">
         <v>1071541</v>
@@ -6082,14 +6082,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>189767</v>
+        <v>189775</v>
       </c>
       <c r="BI33" s="5">
-        <v>1072563</v>
+        <v>1072571</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0009537665847597</v>
+        <v>1.0009612324680064</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="52">BI35-BG35</f>
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="BI35" s="5">
-        <v>14721</v>
+        <v>14722</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ47" si="53">BI35/BF35</f>
-        <v>0.99904988123515437</v>
+        <v>0.99911774686121479</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6507,14 +6507,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>253983</v>
+        <v>253990</v>
       </c>
       <c r="F36" s="5">
-        <v>833182</v>
+        <v>833189</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.99658507936849683</v>
+        <v>0.99659345220367046</v>
       </c>
       <c r="H36" s="5">
         <v>854298</v>
@@ -6524,14 +6524,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="32"/>
-        <v>261255</v>
+        <v>261263</v>
       </c>
       <c r="K36" s="5">
-        <v>843345</v>
+        <v>843353</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98717894692484354</v>
+        <v>0.98718831133866636</v>
       </c>
       <c r="M36" s="5">
         <v>1510524</v>
@@ -6541,14 +6541,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="34"/>
-        <v>489829</v>
+        <v>489849</v>
       </c>
       <c r="P36" s="5">
-        <v>1504220</v>
+        <v>1504240</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99582661381083648</v>
+        <v>0.99583985424925392</v>
       </c>
       <c r="R36" s="5">
         <v>845008</v>
@@ -6558,14 +6558,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="36"/>
-        <v>248819</v>
+        <v>248831</v>
       </c>
       <c r="U36" s="5">
-        <v>839785</v>
+        <v>839797</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99381899342964797</v>
+        <v>0.99383319447863216</v>
       </c>
       <c r="W36" s="5">
         <v>865288</v>
@@ -6575,14 +6575,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="38"/>
-        <v>251371</v>
+        <v>251384</v>
       </c>
       <c r="Z36" s="5">
-        <v>849456</v>
+        <v>849469</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98170320170856407</v>
+        <v>0.98171822560812128</v>
       </c>
       <c r="AB36" s="5">
         <v>1522408</v>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="40"/>
-        <v>485962</v>
+        <v>485987</v>
       </c>
       <c r="AE36" s="5">
-        <v>1517932</v>
+        <v>1517957</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="41"/>
-        <v>0.99705992086221307</v>
+        <v>0.99707634221575292</v>
       </c>
       <c r="AG36" s="5">
         <v>860909</v>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="42"/>
-        <v>232908</v>
+        <v>232924</v>
       </c>
       <c r="AJ36" s="5">
-        <v>855801</v>
+        <v>855817</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="43"/>
-        <v>0.99406673643788135</v>
+        <v>0.99408532144512374</v>
       </c>
       <c r="AL36" s="5">
         <v>879793</v>
@@ -6626,14 +6626,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="44"/>
-        <v>238547</v>
+        <v>238568</v>
       </c>
       <c r="AO36" s="5">
-        <v>866287</v>
+        <v>866308</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="45"/>
-        <v>0.98464866167382559</v>
+        <v>0.98467253092488805</v>
       </c>
       <c r="AQ36" s="5">
         <v>1539776</v>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="46"/>
-        <v>458667</v>
+        <v>458700</v>
       </c>
       <c r="AT36" s="5">
-        <v>1539443</v>
+        <v>1539476</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="47"/>
-        <v>0.99978373477700655</v>
+        <v>0.99980516646577167</v>
       </c>
       <c r="AV36" s="5">
         <v>875330</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="48"/>
-        <v>234309</v>
+        <v>234334</v>
       </c>
       <c r="AY36" s="5">
-        <v>872460</v>
+        <v>872485</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="49"/>
-        <v>0.99672123656221079</v>
+        <v>0.99674979721933443</v>
       </c>
       <c r="BA36" s="5">
         <v>893595</v>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="50"/>
-        <v>235970</v>
+        <v>235994</v>
       </c>
       <c r="BD36" s="5">
-        <v>883700</v>
+        <v>883724</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="51"/>
-        <v>0.98892675093302895</v>
+        <v>0.98895360873773919</v>
       </c>
       <c r="BF36" s="5">
         <v>1566403</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="52"/>
-        <v>507289</v>
+        <v>507335</v>
       </c>
       <c r="BI36" s="5">
-        <v>1560360</v>
+        <v>1560406</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="53"/>
-        <v>0.99614211668389296</v>
+        <v>0.99617148332836436</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>283674</v>
+        <v>283681</v>
       </c>
       <c r="F37" s="5">
-        <v>667683</v>
+        <v>667690</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.98835613700856639</v>
+        <v>0.98836649895122342</v>
       </c>
       <c r="H37" s="5">
         <v>681828</v>
@@ -6736,14 +6736,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="32"/>
-        <v>274153</v>
+        <v>274159</v>
       </c>
       <c r="K37" s="5">
-        <v>670554</v>
+        <v>670560</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98346503810345132</v>
+        <v>0.98347383797673316</v>
       </c>
       <c r="M37" s="5">
         <v>856106</v>
@@ -6753,14 +6753,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="34"/>
-        <v>347682</v>
+        <v>347695</v>
       </c>
       <c r="P37" s="5">
-        <v>846318</v>
+        <v>846331</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98856683634970433</v>
+        <v>0.98858202138520235</v>
       </c>
       <c r="R37" s="5">
         <v>679636</v>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="36"/>
-        <v>268939</v>
+        <v>268949</v>
       </c>
       <c r="U37" s="5">
-        <v>671488</v>
+        <v>671498</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98801122954051879</v>
+        <v>0.98802594329906013</v>
       </c>
       <c r="W37" s="5">
         <v>687189</v>
@@ -6787,14 +6787,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="38"/>
-        <v>273272</v>
+        <v>273282</v>
       </c>
       <c r="Z37" s="5">
-        <v>676587</v>
+        <v>676597</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98457192999305865</v>
+        <v>0.98458648203041665</v>
       </c>
       <c r="AB37" s="5">
         <v>863912</v>
@@ -6804,14 +6804,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="40"/>
-        <v>349257</v>
+        <v>349272</v>
       </c>
       <c r="AE37" s="5">
-        <v>855428</v>
+        <v>855443</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="41"/>
-        <v>0.9901795553250794</v>
+        <v>0.99019691820463196</v>
       </c>
       <c r="AG37" s="5">
         <v>690763</v>
@@ -6821,14 +6821,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="42"/>
-        <v>260630</v>
+        <v>260645</v>
       </c>
       <c r="AJ37" s="5">
-        <v>682610</v>
+        <v>682625</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="43"/>
-        <v>0.9881971095730373</v>
+        <v>0.98821882469095768</v>
       </c>
       <c r="AL37" s="5">
         <v>697437</v>
@@ -6838,14 +6838,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="44"/>
-        <v>264978</v>
+        <v>264998</v>
       </c>
       <c r="AO37" s="5">
-        <v>688594</v>
+        <v>688614</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98732071857386405</v>
+        <v>0.98734939499911822</v>
       </c>
       <c r="AQ37" s="5">
         <v>873380</v>
@@ -6855,14 +6855,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="46"/>
-        <v>338527</v>
+        <v>338552</v>
       </c>
       <c r="AT37" s="5">
-        <v>868937</v>
+        <v>868962</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99491286725136829</v>
+        <v>0.99494149167601731</v>
       </c>
       <c r="AV37" s="5">
         <v>700086</v>
@@ -6872,14 +6872,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="48"/>
-        <v>266937</v>
+        <v>266958</v>
       </c>
       <c r="AY37" s="5">
-        <v>694450</v>
+        <v>694471</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="49"/>
-        <v>0.99194956048256933</v>
+        <v>0.99197955679730776</v>
       </c>
       <c r="BA37" s="5">
         <v>708485</v>
@@ -6889,14 +6889,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="50"/>
-        <v>268829</v>
+        <v>268853</v>
       </c>
       <c r="BD37" s="5">
-        <v>699429</v>
+        <v>699453</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="51"/>
-        <v>0.98721779571903423</v>
+        <v>0.98725167081871879</v>
       </c>
       <c r="BF37" s="5">
         <v>887779</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="52"/>
-        <v>384126</v>
+        <v>384164</v>
       </c>
       <c r="BI37" s="5">
-        <v>878187</v>
+        <v>878225</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="53"/>
-        <v>0.98919550924272825</v>
+        <v>0.9892383126881803</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6965,14 +6965,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="34"/>
-        <v>14388</v>
+        <v>14389</v>
       </c>
       <c r="P38" s="5">
-        <v>35829</v>
+        <v>35830</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0069417121016244</v>
+        <v>1.0069698161992018</v>
       </c>
       <c r="R38" s="5">
         <v>22911</v>
@@ -6982,14 +6982,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="36"/>
-        <v>9352</v>
+        <v>9353</v>
       </c>
       <c r="U38" s="5">
-        <v>23141</v>
+        <v>23142</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0100388459691851</v>
+        <v>1.010082493125573</v>
       </c>
       <c r="W38" s="5">
         <v>23450</v>
@@ -6999,14 +6999,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="38"/>
-        <v>9182</v>
+        <v>9183</v>
       </c>
       <c r="Z38" s="5">
-        <v>23350</v>
+        <v>23351</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="39"/>
-        <v>0.99573560767590619</v>
+        <v>0.99577825159914712</v>
       </c>
       <c r="AB38" s="5">
         <v>35915</v>
@@ -7016,14 +7016,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="40"/>
-        <v>14259</v>
+        <v>14260</v>
       </c>
       <c r="AE38" s="5">
-        <v>36326</v>
+        <v>36327</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0114436864819714</v>
+        <v>1.0114715300013921</v>
       </c>
       <c r="AG38" s="5">
         <v>23414</v>
@@ -7033,14 +7033,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="42"/>
-        <v>8894</v>
+        <v>8896</v>
       </c>
       <c r="AJ38" s="5">
-        <v>23632</v>
+        <v>23634</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0093106688306142</v>
+        <v>1.0093960878107116</v>
       </c>
       <c r="AL38" s="5">
         <v>23927</v>
@@ -7050,14 +7050,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="44"/>
-        <v>8956</v>
+        <v>8958</v>
       </c>
       <c r="AO38" s="5">
-        <v>23907</v>
+        <v>23909</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="45"/>
-        <v>0.9991641242111422</v>
+        <v>0.99924771179002803</v>
       </c>
       <c r="AQ38" s="5">
         <v>36551</v>
@@ -7067,14 +7067,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="46"/>
-        <v>13389</v>
+        <v>13392</v>
       </c>
       <c r="AT38" s="5">
-        <v>37087</v>
+        <v>37090</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0146644414653498</v>
+        <v>1.0147465185631037</v>
       </c>
       <c r="AV38" s="5">
         <v>23833</v>
@@ -7084,14 +7084,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="48"/>
-        <v>8938</v>
+        <v>8940</v>
       </c>
       <c r="AY38" s="5">
-        <v>24142</v>
+        <v>24144</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="49"/>
-        <v>1.0129652162967315</v>
+        <v>1.0130491335543155</v>
       </c>
       <c r="BA38" s="5">
         <v>24292</v>
@@ -7101,14 +7101,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="50"/>
-        <v>8900</v>
+        <v>8902</v>
       </c>
       <c r="BD38" s="5">
-        <v>24404</v>
+        <v>24406</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="51"/>
-        <v>1.0046105713815248</v>
+        <v>1.0046929030133378</v>
       </c>
       <c r="BF38" s="5">
         <v>37393</v>
@@ -7118,14 +7118,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="52"/>
-        <v>15240</v>
+        <v>15244</v>
       </c>
       <c r="BI38" s="5">
-        <v>37595</v>
+        <v>37599</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="53"/>
-        <v>1.0054020806033215</v>
+        <v>1.0055090524964565</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>104857</v>
+        <v>104864</v>
       </c>
       <c r="F40" s="5">
-        <v>275841</v>
+        <v>275848</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.99322703998962991</v>
+        <v>0.99325224505080623</v>
       </c>
       <c r="H40" s="5">
         <v>279588</v>
@@ -7372,14 +7372,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="32"/>
-        <v>108054</v>
+        <v>108063</v>
       </c>
       <c r="K40" s="5">
-        <v>277543</v>
+        <v>277552</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99268566605147579</v>
+        <v>0.99271785627423204</v>
       </c>
       <c r="M40" s="5">
         <v>339205</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="34"/>
-        <v>135121</v>
+        <v>135130</v>
       </c>
       <c r="P40" s="5">
-        <v>337523</v>
+        <v>337532</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99504134667826238</v>
+        <v>0.99506787930602436</v>
       </c>
       <c r="R40" s="5">
         <v>280405</v>
@@ -7406,14 +7406,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="36"/>
-        <v>104700</v>
+        <v>104710</v>
       </c>
       <c r="U40" s="5">
-        <v>278856</v>
+        <v>278866</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99447584743496009</v>
+        <v>0.99451151013712313</v>
       </c>
       <c r="W40" s="5">
         <v>283529</v>
@@ -7423,14 +7423,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="38"/>
-        <v>110238</v>
+        <v>110246</v>
       </c>
       <c r="Z40" s="5">
-        <v>280802</v>
+        <v>280810</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99038193623932647</v>
+        <v>0.9904101520479387</v>
       </c>
       <c r="AB40" s="5">
         <v>342699</v>
@@ -7440,14 +7440,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="40"/>
-        <v>136240</v>
+        <v>136248</v>
       </c>
       <c r="AE40" s="5">
-        <v>341667</v>
+        <v>341675</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99698861099682223</v>
+        <v>0.99701195509762208</v>
       </c>
       <c r="AG40" s="5">
         <v>284836</v>
@@ -7457,14 +7457,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="42"/>
-        <v>104278</v>
+        <v>104284</v>
       </c>
       <c r="AJ40" s="5">
-        <v>283409</v>
+        <v>283415</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="43"/>
-        <v>0.9949900995660661</v>
+        <v>0.99501116431911696</v>
       </c>
       <c r="AL40" s="5">
         <v>287465</v>
@@ -7474,14 +7474,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="44"/>
-        <v>109793</v>
+        <v>109802</v>
       </c>
       <c r="AO40" s="5">
-        <v>285636</v>
+        <v>285645</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="45"/>
-        <v>0.99363748630268034</v>
+        <v>0.99366879446193446</v>
       </c>
       <c r="AQ40" s="5">
         <v>346543</v>
@@ -7491,14 +7491,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="46"/>
-        <v>133807</v>
+        <v>133819</v>
       </c>
       <c r="AT40" s="5">
-        <v>346467</v>
+        <v>346479</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99978069099649969</v>
+        <v>0.99981531873389451</v>
       </c>
       <c r="AV40" s="5">
         <v>288959</v>
@@ -7508,14 +7508,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="48"/>
-        <v>110657</v>
+        <v>110667</v>
       </c>
       <c r="AY40" s="5">
-        <v>287753</v>
+        <v>287763</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="49"/>
-        <v>0.99582639751660273</v>
+        <v>0.99586100450236881</v>
       </c>
       <c r="BA40" s="5">
         <v>291465</v>
@@ -7525,14 +7525,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="50"/>
-        <v>109528</v>
+        <v>109542</v>
       </c>
       <c r="BD40" s="5">
-        <v>288928</v>
+        <v>288942</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="51"/>
-        <v>0.99129569588115207</v>
+        <v>0.99134372909268698</v>
       </c>
       <c r="BF40" s="5">
         <v>351557</v>
@@ -7542,14 +7542,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="52"/>
-        <v>149274</v>
+        <v>149293</v>
       </c>
       <c r="BI40" s="5">
-        <v>349423</v>
+        <v>349442</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="53"/>
-        <v>0.99392986059159683</v>
+        <v>0.99398390588154983</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>345419</v>
+        <v>345435</v>
       </c>
       <c r="F41" s="5">
-        <v>905545</v>
+        <v>905561</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.99279804936663618</v>
+        <v>0.99281559103357697</v>
       </c>
       <c r="H41" s="5">
         <v>920596</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="32"/>
-        <v>358253</v>
+        <v>358267</v>
       </c>
       <c r="K41" s="5">
-        <v>910560</v>
+        <v>910574</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98909836671026163</v>
+        <v>0.98911357424972512</v>
       </c>
       <c r="M41" s="5">
         <v>1028922</v>
@@ -7601,14 +7601,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="34"/>
-        <v>396200</v>
+        <v>396213</v>
       </c>
       <c r="P41" s="5">
-        <v>1018307</v>
+        <v>1018320</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="35"/>
-        <v>0.98968337735999423</v>
+        <v>0.98969601194259627</v>
       </c>
       <c r="R41" s="5">
         <v>924082</v>
@@ -7618,14 +7618,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="36"/>
-        <v>360513</v>
+        <v>360527</v>
       </c>
       <c r="U41" s="5">
-        <v>915033</v>
+        <v>915047</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99020757898108613</v>
+        <v>0.99022272915174192</v>
       </c>
       <c r="W41" s="5">
         <v>929406</v>
@@ -7635,14 +7635,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="38"/>
-        <v>356185</v>
+        <v>356197</v>
       </c>
       <c r="Z41" s="5">
-        <v>918989</v>
+        <v>919001</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="39"/>
-        <v>0.9887917659236114</v>
+        <v>0.98880467739610034</v>
       </c>
       <c r="AB41" s="5">
         <v>1036539</v>
@@ -7652,14 +7652,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="40"/>
-        <v>396598</v>
+        <v>396619</v>
       </c>
       <c r="AE41" s="5">
-        <v>1027414</v>
+        <v>1027435</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99119666505553583</v>
+        <v>0.99121692478527101</v>
       </c>
       <c r="AG41" s="5">
         <v>935526</v>
@@ -7669,14 +7669,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="42"/>
-        <v>348919</v>
+        <v>348943</v>
       </c>
       <c r="AJ41" s="5">
-        <v>925551</v>
+        <v>925575</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="43"/>
-        <v>0.98933754914347649</v>
+        <v>0.98936320316057491</v>
       </c>
       <c r="AL41" s="5">
         <v>940174</v>
@@ -7686,14 +7686,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="44"/>
-        <v>363714</v>
+        <v>363738</v>
       </c>
       <c r="AO41" s="5">
-        <v>930116</v>
+        <v>930140</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="45"/>
-        <v>0.98930198027173688</v>
+        <v>0.98932750746138476</v>
       </c>
       <c r="AQ41" s="5">
         <v>1046219</v>
@@ -7703,14 +7703,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="46"/>
-        <v>386017</v>
+        <v>386048</v>
       </c>
       <c r="AT41" s="5">
-        <v>1038904</v>
+        <v>1038935</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99300815603616455</v>
+        <v>0.99303778654373509</v>
       </c>
       <c r="AV41" s="5">
         <v>945246</v>
@@ -7720,14 +7720,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="48"/>
-        <v>357466</v>
+        <v>357491</v>
       </c>
       <c r="AY41" s="5">
-        <v>936905</v>
+        <v>936930</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="49"/>
-        <v>0.99117584205593046</v>
+        <v>0.99120229019747241</v>
       </c>
       <c r="BA41" s="5">
         <v>950318</v>
@@ -7737,14 +7737,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="50"/>
-        <v>354973</v>
+        <v>355001</v>
       </c>
       <c r="BD41" s="5">
-        <v>940848</v>
+        <v>940876</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="51"/>
-        <v>0.99003491462857696</v>
+        <v>0.99006437845016093</v>
       </c>
       <c r="BF41" s="5">
         <v>1056723</v>
@@ -7754,14 +7754,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="52"/>
-        <v>421949</v>
+        <v>421991</v>
       </c>
       <c r="BI41" s="5">
-        <v>1049189</v>
+        <v>1049231</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="53"/>
-        <v>0.99287041164051504</v>
+        <v>0.99291015715565956</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7830,14 +7830,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="36"/>
-        <v>8477</v>
+        <v>8478</v>
       </c>
       <c r="U42" s="5">
-        <v>18336</v>
+        <v>18337</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="37"/>
-        <v>0.98883675780618019</v>
+        <v>0.98889068651243062</v>
       </c>
       <c r="W42" s="5">
         <v>18720</v>
@@ -7847,14 +7847,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="38"/>
-        <v>8428</v>
+        <v>8429</v>
       </c>
       <c r="Z42" s="5">
-        <v>18400</v>
+        <v>18401</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="39"/>
-        <v>0.98290598290598286</v>
+        <v>0.98295940170940166</v>
       </c>
       <c r="AB42" s="5">
         <v>20718</v>
@@ -7864,14 +7864,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="40"/>
-        <v>9147</v>
+        <v>9148</v>
       </c>
       <c r="AE42" s="5">
-        <v>20345</v>
+        <v>20346</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="41"/>
-        <v>0.98199633169224831</v>
+        <v>0.98204459889950768</v>
       </c>
       <c r="AG42" s="5">
         <v>18665</v>
@@ -7881,14 +7881,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="42"/>
-        <v>8088</v>
+        <v>8089</v>
       </c>
       <c r="AJ42" s="5">
-        <v>18416</v>
+        <v>18417</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="43"/>
-        <v>0.98665952317171179</v>
+        <v>0.98671309938387353</v>
       </c>
       <c r="AL42" s="5">
         <v>18792</v>
@@ -7898,14 +7898,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="44"/>
-        <v>8160</v>
+        <v>8162</v>
       </c>
       <c r="AO42" s="5">
-        <v>18526</v>
+        <v>18528</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="45"/>
-        <v>0.98584504044274157</v>
+        <v>0.98595146871008943</v>
       </c>
       <c r="AQ42" s="5">
         <v>20796</v>
@@ -7915,14 +7915,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="46"/>
-        <v>8828</v>
+        <v>8830</v>
       </c>
       <c r="AT42" s="5">
-        <v>20579</v>
+        <v>20581</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="47"/>
-        <v>0.98956530101942686</v>
+        <v>0.98966147336026156</v>
       </c>
       <c r="AV42" s="5">
         <v>18829</v>
@@ -7932,14 +7932,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="48"/>
-        <v>8273</v>
+        <v>8274</v>
       </c>
       <c r="AY42" s="5">
-        <v>18606</v>
+        <v>18607</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="49"/>
-        <v>0.98815656699771626</v>
+        <v>0.98820967656274894</v>
       </c>
       <c r="BA42" s="5">
         <v>18938</v>
@@ -7949,14 +7949,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="50"/>
-        <v>8317</v>
+        <v>8318</v>
       </c>
       <c r="BD42" s="5">
-        <v>18721</v>
+        <v>18722</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="51"/>
-        <v>0.98854155665857002</v>
+        <v>0.9885943605449361</v>
       </c>
       <c r="BF42" s="5">
         <v>21042</v>
@@ -7966,14 +7966,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="52"/>
-        <v>9646</v>
+        <v>9647</v>
       </c>
       <c r="BI42" s="5">
-        <v>20812</v>
+        <v>20813</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="53"/>
-        <v>0.98906948008744411</v>
+        <v>0.98911700408706393</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -7991,14 +7991,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="0"/>
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F43" s="5">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="1"/>
-        <v>1.0002894356005789</v>
+        <v>1.0005788712011578</v>
       </c>
       <c r="H43" s="5">
         <v>3541</v>
@@ -8008,14 +8008,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="32"/>
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="K43" s="5">
-        <v>3476</v>
+        <v>3477</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="33"/>
-        <v>0.98164360350183566</v>
+        <v>0.98192600960180743</v>
       </c>
       <c r="M43" s="5">
         <v>4395</v>
@@ -8025,14 +8025,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="34"/>
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="P43" s="5">
-        <v>4353</v>
+        <v>4354</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99044368600682597</v>
+        <v>0.99067121729237773</v>
       </c>
       <c r="R43" s="5">
         <v>3498</v>
@@ -8161,14 +8161,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="50"/>
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="BD43" s="5">
-        <v>3654</v>
+        <v>3655</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="51"/>
-        <v>0.9997264021887825</v>
+        <v>1</v>
       </c>
       <c r="BF43" s="5">
         <v>4544</v>
@@ -8203,14 +8203,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>164122</v>
+        <v>164126</v>
       </c>
       <c r="F44" s="5">
-        <v>333690</v>
+        <v>333694</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.99245155073343083</v>
+        <v>0.9924634474225823</v>
       </c>
       <c r="H44" s="5">
         <v>340996</v>
@@ -8220,14 +8220,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="32"/>
-        <v>169331</v>
+        <v>169336</v>
       </c>
       <c r="K44" s="5">
-        <v>337612</v>
+        <v>337617</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="33"/>
-        <v>0.99007612992527771</v>
+        <v>0.99009079285387513</v>
       </c>
       <c r="M44" s="5">
         <v>408512</v>
@@ -8237,14 +8237,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="34"/>
-        <v>200391</v>
+        <v>200397</v>
       </c>
       <c r="P44" s="5">
-        <v>404887</v>
+        <v>404893</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="35"/>
-        <v>0.99112633166222774</v>
+        <v>0.99114101911326957</v>
       </c>
       <c r="R44" s="5">
         <v>342556</v>
@@ -8254,14 +8254,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="36"/>
-        <v>167617</v>
+        <v>167623</v>
       </c>
       <c r="U44" s="5">
-        <v>339648</v>
+        <v>339654</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="37"/>
-        <v>0.9915108770536788</v>
+        <v>0.99152839243802471</v>
       </c>
       <c r="W44" s="5">
         <v>347597</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="38"/>
-        <v>168804</v>
+        <v>168811</v>
       </c>
       <c r="Z44" s="5">
-        <v>343528</v>
+        <v>343535</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98829391507981945</v>
+        <v>0.98831405334338329</v>
       </c>
       <c r="AB44" s="5">
         <v>416340</v>
@@ -8288,14 +8288,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="40"/>
-        <v>203181</v>
+        <v>203189</v>
       </c>
       <c r="AE44" s="5">
-        <v>413206</v>
+        <v>413214</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="41"/>
-        <v>0.99247249843877605</v>
+        <v>0.99249171350338661</v>
       </c>
       <c r="AG44" s="5">
         <v>350469</v>
@@ -8305,14 +8305,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="42"/>
-        <v>166195</v>
+        <v>166204</v>
       </c>
       <c r="AJ44" s="5">
-        <v>347620</v>
+        <v>347629</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="43"/>
-        <v>0.9918708930033755</v>
+        <v>0.99189657287805766</v>
       </c>
       <c r="AL44" s="5">
         <v>355186</v>
@@ -8322,14 +8322,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="44"/>
-        <v>169366</v>
+        <v>169376</v>
       </c>
       <c r="AO44" s="5">
-        <v>351099</v>
+        <v>351109</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98849335277854422</v>
+        <v>0.98852150704138109</v>
       </c>
       <c r="AQ44" s="5">
         <v>424208</v>
@@ -8339,14 +8339,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="46"/>
-        <v>198276</v>
+        <v>198287</v>
       </c>
       <c r="AT44" s="5">
-        <v>421863</v>
+        <v>421874</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="47"/>
-        <v>0.99447205144646023</v>
+        <v>0.99449798212197793</v>
       </c>
       <c r="AV44" s="5">
         <v>358114</v>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="48"/>
-        <v>167137</v>
+        <v>167147</v>
       </c>
       <c r="AY44" s="5">
-        <v>354698</v>
+        <v>354708</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="49"/>
-        <v>0.9904611380733509</v>
+        <v>0.99048906214222288</v>
       </c>
       <c r="BA44" s="5">
         <v>361984</v>
@@ -8373,14 +8373,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="50"/>
-        <v>170848</v>
+        <v>170858</v>
       </c>
       <c r="BD44" s="5">
-        <v>357799</v>
+        <v>357809</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="51"/>
-        <v>0.98843871552333806</v>
+        <v>0.9884663410537482</v>
       </c>
       <c r="BF44" s="5">
         <v>432310</v>
@@ -8390,14 +8390,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="52"/>
-        <v>225447</v>
+        <v>225462</v>
       </c>
       <c r="BI44" s="5">
-        <v>428043</v>
+        <v>428058</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="53"/>
-        <v>0.99012976799056229</v>
+        <v>0.99016446531424207</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>116367</v>
+        <v>116368</v>
       </c>
       <c r="F45" s="5">
-        <v>251480</v>
+        <v>251481</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.98404276133010904</v>
+        <v>0.98404667433615856</v>
       </c>
       <c r="H45" s="5">
         <v>257610</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="34"/>
-        <v>144177</v>
+        <v>144179</v>
       </c>
       <c r="P45" s="5">
-        <v>305411</v>
+        <v>305413</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98403497805816353</v>
+        <v>0.98404142206298373</v>
       </c>
       <c r="R45" s="5">
         <v>257356</v>
@@ -8466,14 +8466,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="36"/>
-        <v>118785</v>
+        <v>118788</v>
       </c>
       <c r="U45" s="5">
-        <v>253927</v>
+        <v>253930</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98667604407901899</v>
+        <v>0.98668770108332426</v>
       </c>
       <c r="W45" s="5">
         <v>260553</v>
@@ -8483,14 +8483,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="38"/>
-        <v>120988</v>
+        <v>120991</v>
       </c>
       <c r="Z45" s="5">
-        <v>255889</v>
+        <v>255892</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98209961121153855</v>
+        <v>0.98211112518374377</v>
       </c>
       <c r="AB45" s="5">
         <v>313911</v>
@@ -8500,14 +8500,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="40"/>
-        <v>148033</v>
+        <v>148037</v>
       </c>
       <c r="AE45" s="5">
-        <v>309027</v>
+        <v>309031</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="41"/>
-        <v>0.98444144996511751</v>
+        <v>0.98445419243033849</v>
       </c>
       <c r="AG45" s="5">
         <v>261210</v>
@@ -8517,14 +8517,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="42"/>
-        <v>116285</v>
+        <v>116293</v>
       </c>
       <c r="AJ45" s="5">
-        <v>257209</v>
+        <v>257217</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="43"/>
-        <v>0.98468282225029669</v>
+        <v>0.98471344894912138</v>
       </c>
       <c r="AL45" s="5">
         <v>264020</v>
@@ -8534,14 +8534,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="44"/>
-        <v>120908</v>
+        <v>120914</v>
       </c>
       <c r="AO45" s="5">
-        <v>259602</v>
+        <v>259608</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98326641921066582</v>
+        <v>0.98328914476176044</v>
       </c>
       <c r="AQ45" s="5">
         <v>317407</v>
@@ -8551,14 +8551,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="46"/>
-        <v>143490</v>
+        <v>143499</v>
       </c>
       <c r="AT45" s="5">
-        <v>312028</v>
+        <v>312037</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="47"/>
-        <v>0.98305330380237366</v>
+        <v>0.98308165856455587</v>
       </c>
       <c r="AV45" s="5">
         <v>263886</v>
@@ -8568,14 +8568,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="48"/>
-        <v>118303</v>
+        <v>118311</v>
       </c>
       <c r="AY45" s="5">
-        <v>259605</v>
+        <v>259613</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="49"/>
-        <v>0.98377708555967347</v>
+        <v>0.98380740168102898</v>
       </c>
       <c r="BA45" s="5">
         <v>265781</v>
@@ -8585,14 +8585,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="50"/>
-        <v>120887</v>
+        <v>120895</v>
       </c>
       <c r="BD45" s="5">
-        <v>261433</v>
+        <v>261441</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="51"/>
-        <v>0.98364066656382509</v>
+        <v>0.98367076653334884</v>
       </c>
       <c r="BF45" s="5">
         <v>319799</v>
@@ -8602,14 +8602,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="52"/>
-        <v>165090</v>
+        <v>165104</v>
       </c>
       <c r="BI45" s="5">
-        <v>315155</v>
+        <v>315169</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="53"/>
-        <v>0.98547837860656229</v>
+        <v>0.98552215610430305</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8627,14 +8627,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="0"/>
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="F46" s="5">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="1"/>
-        <v>1.0700090334236676</v>
+        <v>1.070460704607046</v>
       </c>
       <c r="H46" s="5">
         <v>2377</v>
@@ -8644,14 +8644,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="32"/>
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="K46" s="5">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="33"/>
-        <v>1.0555321834244846</v>
+        <v>1.0559528817837611</v>
       </c>
       <c r="M46" s="5">
         <v>6689</v>
@@ -8661,14 +8661,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="34"/>
-        <v>4407</v>
+        <v>4408</v>
       </c>
       <c r="P46" s="5">
-        <v>6878</v>
+        <v>6879</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0282553445956046</v>
+        <v>1.0284048437733593</v>
       </c>
       <c r="R46" s="5">
         <v>2186</v>
@@ -8678,14 +8678,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="36"/>
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="U46" s="5">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="37"/>
-        <v>1.0690759377859103</v>
+        <v>1.0695333943275389</v>
       </c>
       <c r="W46" s="5">
         <v>2396</v>
@@ -8695,14 +8695,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="38"/>
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="Z46" s="5">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="39"/>
-        <v>1.0204507512520868</v>
+        <v>1.0208681135225375</v>
       </c>
       <c r="AB46" s="5">
         <v>6920</v>
@@ -8712,14 +8712,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="40"/>
-        <v>4610</v>
+        <v>4611</v>
       </c>
       <c r="AE46" s="5">
-        <v>7164</v>
+        <v>7165</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="41"/>
-        <v>1.0352601156069363</v>
+        <v>1.0354046242774566</v>
       </c>
       <c r="AG46" s="5">
         <v>2260</v>
@@ -8729,14 +8729,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="42"/>
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="43"/>
-        <v>1.0438053097345132</v>
+        <v>1.0442477876106195</v>
       </c>
       <c r="AL46" s="5">
         <v>2436</v>
@@ -8746,14 +8746,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="44"/>
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="AO46" s="5">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="45"/>
-        <v>1.0053366174055829</v>
+        <v>1.0057471264367817</v>
       </c>
       <c r="AQ46" s="5">
         <v>7143</v>
@@ -8763,14 +8763,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="46"/>
-        <v>4294</v>
+        <v>4295</v>
       </c>
       <c r="AT46" s="5">
-        <v>7364</v>
+        <v>7365</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0309393812123757</v>
+        <v>1.0310793784124317</v>
       </c>
       <c r="AV46" s="5">
         <v>2225</v>
@@ -8780,14 +8780,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="48"/>
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="AY46" s="5">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="49"/>
-        <v>1.0588764044943819</v>
+        <v>1.0593258426966292</v>
       </c>
       <c r="BA46" s="5">
         <v>2388</v>
@@ -8797,14 +8797,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="50"/>
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="BD46" s="5">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="51"/>
-        <v>1.0129815745393635</v>
+        <v>1.0134003350083751</v>
       </c>
       <c r="BF46" s="5">
         <v>7407</v>
@@ -8814,14 +8814,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="52"/>
-        <v>4645</v>
+        <v>4646</v>
       </c>
       <c r="BI46" s="5">
-        <v>7565</v>
+        <v>7566</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="53"/>
-        <v>1.0213311732145267</v>
+        <v>1.0214661806399352</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9037,10 +9037,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="14"/>
+      <c r="B48" s="18"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>7712416</v>
@@ -9051,15 +9051,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3007621</v>
+        <v>3007712</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>7666550</v>
+        <v>7666641</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.99405296602257964</v>
+        <v>0.99406476517864184</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9071,15 +9071,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3058262</v>
+        <v>3058356</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7765117</v>
+        <v>7765211</v>
       </c>
       <c r="L48" s="6">
         <f>K48/H48</f>
-        <v>0.98700616116442852</v>
+        <v>0.9870181092882172</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9091,15 +9091,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>4954381</v>
+        <v>4954568</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12077045</v>
+        <v>12077232</v>
       </c>
       <c r="Q48" s="6">
         <f>P48/M48</f>
-        <v>0.99381127053652274</v>
+        <v>0.99382665863084474</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9111,15 +9111,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3023136</v>
+        <v>3023267</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7734500</v>
+        <v>7734631</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.99085396123159775</v>
+        <v>0.99087074342423087</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3062513</v>
+        <v>3062656</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7826218</v>
+        <v>7826361</v>
       </c>
       <c r="AA48" s="6">
         <f>Z48/W48</f>
-        <v>0.98469859260973214</v>
+        <v>0.98471658493996661</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>4962317</v>
+        <v>4962592</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12220771</v>
+        <v>12221046</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.99483823868082677</v>
+        <v>0.99486062519929086</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2974140</v>
+        <v>2974330</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7866320</v>
+        <v>7866510</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.99142139038861987</v>
+        <v>0.99144533679102576</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3044162</v>
+        <v>3044387</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7955292</v>
+        <v>7955517</v>
       </c>
       <c r="AP48" s="6">
         <f>AO48/AL48</f>
-        <v>0.98475145748387971</v>
+        <v>0.9847793092683188</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4873580</v>
+        <v>4873964</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12410898</v>
+        <v>12411282</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.99724007062616515</v>
+        <v>0.9972709257816198</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>2995053</v>
+        <v>2995320</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8001966</v>
+        <v>8002233</v>
       </c>
       <c r="AZ48" s="6">
         <f>AY48/AV48</f>
-        <v>0.99263521580045788</v>
+        <v>0.99266833686128453</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3028792</v>
+        <v>3029073</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8095191</v>
+        <v>8095472</v>
       </c>
       <c r="BE48" s="6">
         <f>BD48/BA48</f>
-        <v>0.98692293953456622</v>
+        <v>0.98695719757072731</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9271,19 +9271,25 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5325719</v>
+        <v>5326259</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12582314</v>
+        <v>12582854</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99417306807963934</v>
+        <v>0.99421573538684238</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9296,12 +9302,6 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="BA8:BE8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2023-2024.xlsx
+++ b/gstdatabase/GSTR-1-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C89DBC7-3685-43A0-9ABD-C0B2688723EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A326D8-06CB-4999-B744-41CED5C78AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
 CD</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -1053,14 +1053,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>74871</v>
+        <v>74872</v>
       </c>
       <c r="P10" s="5">
-        <v>120494</v>
+        <v>120495</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>1.0002324307273422</v>
+        <v>1.0002407318247473</v>
       </c>
       <c r="R10" s="5">
         <v>70979</v>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>41695</v>
+        <v>41696</v>
       </c>
       <c r="U10" s="5">
-        <v>71189</v>
+        <v>71190</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>1.0029586215641246</v>
+        <v>1.0029727102382395</v>
       </c>
       <c r="W10" s="5">
         <v>73348</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>77025</v>
+        <v>77026</v>
       </c>
       <c r="AE10" s="5">
-        <v>123625</v>
+        <v>123626</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>1.0005746475225408</v>
+        <v>1.0005827411496189</v>
       </c>
       <c r="AG10" s="5">
         <v>71950</v>
@@ -1121,14 +1121,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41864</v>
+        <v>41865</v>
       </c>
       <c r="AJ10" s="5">
-        <v>71915</v>
+        <v>71916</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99951355107713691</v>
+        <v>0.99952744961779016</v>
       </c>
       <c r="AL10" s="5">
         <v>73532</v>
@@ -1138,14 +1138,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>43047</v>
+        <v>43048</v>
       </c>
       <c r="AO10" s="5">
-        <v>72977</v>
+        <v>72978</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99245226568024802</v>
+        <v>0.99246586520154489</v>
       </c>
       <c r="AQ10" s="5">
         <v>125499</v>
@@ -1155,14 +1155,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79253</v>
+        <v>79256</v>
       </c>
       <c r="AT10" s="5">
-        <v>125968</v>
+        <v>125971</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.003737081570371</v>
+        <v>1.0037609861433159</v>
       </c>
       <c r="AV10" s="5">
         <v>72481</v>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>42363</v>
+        <v>42365</v>
       </c>
       <c r="AY10" s="5">
-        <v>72227</v>
+        <v>72229</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99649563333839208</v>
+        <v>0.99652322677667249</v>
       </c>
       <c r="BA10" s="5">
         <v>73790</v>
@@ -1189,14 +1189,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="BD10" s="5">
-        <v>73229</v>
+        <v>73230</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.99239734381352485</v>
+        <v>0.99241089578533681</v>
       </c>
       <c r="BF10" s="5">
         <v>128129</v>
@@ -1206,14 +1206,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>85644</v>
+        <v>85647</v>
       </c>
       <c r="BI10" s="5">
-        <v>128167</v>
+        <v>128170</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>1.0002965761068923</v>
+        <v>1.0003199900100679</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>17633</v>
+        <v>17635</v>
       </c>
       <c r="F11" s="5">
-        <v>44788</v>
+        <v>44790</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G47" si="1">F11/C11</f>
-        <v>1.0061553668508785</v>
+        <v>1.0062002965359214</v>
       </c>
       <c r="H11" s="5">
         <v>46110</v>
@@ -1248,14 +1248,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>18775</v>
+        <v>18777</v>
       </c>
       <c r="K11" s="5">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.99754933853827799</v>
+        <v>0.99759271307742359</v>
       </c>
       <c r="M11" s="5">
         <v>102242</v>
@@ -1265,14 +1265,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>52507</v>
+        <v>52510</v>
       </c>
       <c r="P11" s="5">
-        <v>102570</v>
+        <v>102573</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.0032080749594101</v>
+        <v>1.0032374171084291</v>
       </c>
       <c r="R11" s="5">
         <v>44890</v>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>16799</v>
+        <v>16801</v>
       </c>
       <c r="U11" s="5">
-        <v>44824</v>
+        <v>44826</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99852973936288703</v>
+        <v>0.99857429271552689</v>
       </c>
       <c r="W11" s="5">
         <v>46425</v>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>17309</v>
+        <v>17311</v>
       </c>
       <c r="Z11" s="5">
-        <v>45906</v>
+        <v>45908</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.98882067851373179</v>
+        <v>0.98886375875067312</v>
       </c>
       <c r="AB11" s="5">
         <v>103964</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>44418</v>
+        <v>44422</v>
       </c>
       <c r="AE11" s="5">
-        <v>104340</v>
+        <v>104344</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.003616636528029</v>
+        <v>1.0036551113847101</v>
       </c>
       <c r="AG11" s="5">
         <v>45569</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15641</v>
+        <v>15645</v>
       </c>
       <c r="AJ11" s="5">
-        <v>45350</v>
+        <v>45354</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99519410125304486</v>
+        <v>0.99528188022559194</v>
       </c>
       <c r="AL11" s="5">
         <v>46951</v>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN25" si="14">AO11-AM11</f>
-        <v>16011</v>
+        <v>16015</v>
       </c>
       <c r="AO11" s="5">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP26" si="15">AO11/AL11</f>
-        <v>0.98532512619539525</v>
+        <v>0.98541032139890528</v>
       </c>
       <c r="AQ11" s="5">
         <v>105644</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS25" si="16">AT11-AR11</f>
-        <v>42442</v>
+        <v>42448</v>
       </c>
       <c r="AT11" s="5">
-        <v>106048</v>
+        <v>106054</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU26" si="17">AT11/AQ11</f>
-        <v>1.0038241641740184</v>
+        <v>1.0038809586914543</v>
       </c>
       <c r="AV11" s="5">
         <v>46072</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX25" si="18">AY11-AW11</f>
-        <v>15105</v>
+        <v>15108</v>
       </c>
       <c r="AY11" s="5">
-        <v>45950</v>
+        <v>45953</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ26" si="19">AY11/AV11</f>
-        <v>0.99735197082826876</v>
+        <v>0.99741708629970482</v>
       </c>
       <c r="BA11" s="5">
         <v>47252</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC25" si="20">BD11-BB11</f>
-        <v>15569</v>
+        <v>15574</v>
       </c>
       <c r="BD11" s="5">
-        <v>46915</v>
+        <v>46920</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE26" si="21">BD11/BA11</f>
-        <v>0.99286802675019048</v>
+        <v>0.99297384237704223</v>
       </c>
       <c r="BF11" s="5">
         <v>107665</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>46577</v>
+        <v>46587</v>
       </c>
       <c r="BI11" s="5">
-        <v>107773</v>
+        <v>107783</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>1.001003111503274</v>
+        <v>1.0010959921980216</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1528,14 +1528,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>93193</v>
+        <v>93197</v>
       </c>
       <c r="AE12" s="5">
-        <v>348647</v>
+        <v>348651</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99885116087185721</v>
+        <v>0.99886262061378372</v>
       </c>
       <c r="AG12" s="5">
         <v>170526</v>
@@ -1545,14 +1545,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>38081</v>
+        <v>38084</v>
       </c>
       <c r="AJ12" s="5">
-        <v>169857</v>
+        <v>169860</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.99607684458674928</v>
+        <v>0.99609443721192081</v>
       </c>
       <c r="AL12" s="5">
         <v>174892</v>
@@ -1562,14 +1562,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>38324</v>
+        <v>38327</v>
       </c>
       <c r="AO12" s="5">
-        <v>172272</v>
+        <v>172275</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98501932621274846</v>
+        <v>0.98503647965601626</v>
       </c>
       <c r="AQ12" s="5">
         <v>353589</v>
@@ -1579,14 +1579,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94342</v>
+        <v>94345</v>
       </c>
       <c r="AT12" s="5">
-        <v>353361</v>
+        <v>353364</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99935518356057451</v>
+        <v>0.99936366798740917</v>
       </c>
       <c r="AV12" s="5">
         <v>172980</v>
@@ -1596,14 +1596,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36203</v>
+        <v>36205</v>
       </c>
       <c r="AY12" s="5">
-        <v>171879</v>
+        <v>171881</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99363510232396812</v>
+        <v>0.99364666435426063</v>
       </c>
       <c r="BA12" s="5">
         <v>177212</v>
@@ -1613,14 +1613,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>36712</v>
+        <v>36715</v>
       </c>
       <c r="BD12" s="5">
-        <v>174606</v>
+        <v>174609</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98529444958580681</v>
+        <v>0.98531137846195516</v>
       </c>
       <c r="BF12" s="5">
         <v>359260</v>
@@ -1630,14 +1630,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>100762</v>
+        <v>100768</v>
       </c>
       <c r="BI12" s="5">
-        <v>358002</v>
+        <v>358008</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.9964983577353449</v>
+        <v>0.99651505873183766</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7063</v>
+        <v>7064</v>
       </c>
       <c r="BI13" s="5">
-        <v>28705</v>
+        <v>28706</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>1.0045845873871351</v>
+        <v>1.0046195842374186</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -1867,14 +1867,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>36555</v>
+        <v>36557</v>
       </c>
       <c r="F14" s="5">
-        <v>84999</v>
+        <v>85001</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99550261761709002</v>
+        <v>0.99552604148366775</v>
       </c>
       <c r="H14" s="5">
         <v>88261</v>
@@ -1884,14 +1884,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>37984</v>
+        <v>37986</v>
       </c>
       <c r="K14" s="5">
-        <v>86809</v>
+        <v>86811</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.98354879278503526</v>
+        <v>0.98357145285006964</v>
       </c>
       <c r="M14" s="5">
         <v>157146</v>
@@ -1901,14 +1901,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>76990</v>
+        <v>76995</v>
       </c>
       <c r="P14" s="5">
-        <v>155891</v>
+        <v>155896</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99201379608771456</v>
+        <v>0.99204561363318189</v>
       </c>
       <c r="R14" s="5">
         <v>86469</v>
@@ -1918,14 +1918,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>36758</v>
+        <v>36762</v>
       </c>
       <c r="U14" s="5">
-        <v>85090</v>
+        <v>85094</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.98405208803154887</v>
+        <v>0.98409834738461177</v>
       </c>
       <c r="W14" s="5">
         <v>88169</v>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>37741</v>
+        <v>37745</v>
       </c>
       <c r="Z14" s="5">
-        <v>86306</v>
+        <v>86310</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97887012442014765</v>
+        <v>0.97891549183953541</v>
       </c>
       <c r="AB14" s="5">
         <v>157930</v>
@@ -1952,14 +1952,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>76148</v>
+        <v>76156</v>
       </c>
       <c r="AE14" s="5">
-        <v>157564</v>
+        <v>157572</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99768251757107584</v>
+        <v>0.99773317292471353</v>
       </c>
       <c r="AG14" s="5">
         <v>87312</v>
@@ -1969,14 +1969,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>37770</v>
+        <v>37775</v>
       </c>
       <c r="AJ14" s="5">
-        <v>86626</v>
+        <v>86631</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99214311892981488</v>
+        <v>0.99220038482682793</v>
       </c>
       <c r="AL14" s="5">
         <v>89337</v>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>37702</v>
+        <v>37708</v>
       </c>
       <c r="AO14" s="5">
-        <v>87820</v>
+        <v>87826</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.98301935368324433</v>
+        <v>0.98308651510572331</v>
       </c>
       <c r="AQ14" s="5">
         <v>160173</v>
@@ -2003,14 +2003,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>77652</v>
+        <v>77660</v>
       </c>
       <c r="AT14" s="5">
-        <v>160662</v>
+        <v>160670</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>1.0030529489988949</v>
+        <v>1.0031028949947869</v>
       </c>
       <c r="AV14" s="5">
         <v>88523</v>
@@ -2020,14 +2020,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>37635</v>
+        <v>37639</v>
       </c>
       <c r="AY14" s="5">
-        <v>88172</v>
+        <v>88176</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99603492877557243</v>
+        <v>0.99608011477243197</v>
       </c>
       <c r="BA14" s="5">
         <v>90782</v>
@@ -2037,14 +2037,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>37741</v>
+        <v>37745</v>
       </c>
       <c r="BD14" s="5">
-        <v>89655</v>
+        <v>89659</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98758564473133437</v>
+        <v>0.98762970632944858</v>
       </c>
       <c r="BF14" s="5">
         <v>163900</v>
@@ -2054,14 +2054,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>82160</v>
+        <v>82167</v>
       </c>
       <c r="BI14" s="5">
-        <v>163314</v>
+        <v>163321</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.996424649176327</v>
+        <v>0.99646735814521048</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2079,14 +2079,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>72334</v>
+        <v>72335</v>
       </c>
       <c r="F15" s="5">
-        <v>282212</v>
+        <v>282213</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.9927883431482224</v>
+        <v>0.99279186102961348</v>
       </c>
       <c r="H15" s="5">
         <v>290906</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>76325</v>
+        <v>76326</v>
       </c>
       <c r="K15" s="5">
-        <v>286775</v>
+        <v>286776</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.98579953662007658</v>
+        <v>0.98580297415660045</v>
       </c>
       <c r="M15" s="5">
         <v>490131</v>
@@ -2113,14 +2113,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>147284</v>
+        <v>147285</v>
       </c>
       <c r="P15" s="5">
-        <v>486600</v>
+        <v>486601</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99279580357088204</v>
+        <v>0.99279784384174841</v>
       </c>
       <c r="R15" s="5">
         <v>287010</v>
@@ -2130,14 +2130,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>74984</v>
+        <v>74985</v>
       </c>
       <c r="U15" s="5">
-        <v>283574</v>
+        <v>283575</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.98802829169715345</v>
+        <v>0.98803177589631019</v>
       </c>
       <c r="W15" s="5">
         <v>292338</v>
@@ -2147,14 +2147,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>74392</v>
+        <v>74393</v>
       </c>
       <c r="Z15" s="5">
-        <v>287485</v>
+        <v>287486</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98339935280394608</v>
+        <v>0.9834027735019053</v>
       </c>
       <c r="AB15" s="5">
         <v>495688</v>
@@ -2164,14 +2164,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>142479</v>
+        <v>142481</v>
       </c>
       <c r="AE15" s="5">
-        <v>492167</v>
+        <v>492169</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99289674149868468</v>
+        <v>0.99290077629476603</v>
       </c>
       <c r="AG15" s="5">
         <v>292071</v>
@@ -2181,14 +2181,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>78359</v>
+        <v>78361</v>
       </c>
       <c r="AJ15" s="5">
-        <v>289368</v>
+        <v>289370</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99074540094703001</v>
+        <v>0.99075224859708766</v>
       </c>
       <c r="AL15" s="5">
         <v>298411</v>
@@ -2198,14 +2198,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75046</v>
+        <v>75048</v>
       </c>
       <c r="AO15" s="5">
-        <v>293267</v>
+        <v>293269</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98276202954984904</v>
+        <v>0.98276873171565393</v>
       </c>
       <c r="AQ15" s="5">
         <v>502913</v>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137739</v>
+        <v>137744</v>
       </c>
       <c r="AT15" s="5">
-        <v>499827</v>
+        <v>499832</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99386374979370185</v>
+        <v>0.99387369187115859</v>
       </c>
       <c r="AV15" s="5">
         <v>298012</v>
@@ -2232,14 +2232,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>71734</v>
+        <v>71737</v>
       </c>
       <c r="AY15" s="5">
-        <v>294437</v>
+        <v>294440</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.98800383877159303</v>
+        <v>0.9880139054803162</v>
       </c>
       <c r="BA15" s="5">
         <v>303376</v>
@@ -2249,14 +2249,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>71596</v>
+        <v>71599</v>
       </c>
       <c r="BD15" s="5">
-        <v>298824</v>
+        <v>298827</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98499551711407629</v>
+        <v>0.98500540583302565</v>
       </c>
       <c r="BF15" s="5">
         <v>511329</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>149696</v>
+        <v>149701</v>
       </c>
       <c r="BI15" s="5">
-        <v>507702</v>
+        <v>507707</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99290671954847076</v>
+        <v>0.99291649798857484</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>107224</v>
+        <v>107231</v>
       </c>
       <c r="F16" s="5">
-        <v>426858</v>
+        <v>426865</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99122923125152396</v>
+        <v>0.99124548631671838</v>
       </c>
       <c r="H16" s="5">
         <v>441093</v>
@@ -2308,14 +2308,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>113341</v>
+        <v>113348</v>
       </c>
       <c r="K16" s="5">
-        <v>431267</v>
+        <v>431274</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97772351862305684</v>
+        <v>0.97773938829226492</v>
       </c>
       <c r="M16" s="5">
         <v>754668</v>
@@ -2325,14 +2325,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>199874</v>
+        <v>199886</v>
       </c>
       <c r="P16" s="5">
-        <v>751726</v>
+        <v>751738</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99610159699364487</v>
+        <v>0.99611749802562188</v>
       </c>
       <c r="R16" s="5">
         <v>429537</v>
@@ -2342,14 +2342,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>111568</v>
+        <v>111577</v>
       </c>
       <c r="U16" s="5">
-        <v>423870</v>
+        <v>423879</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.98680672444981454</v>
+        <v>0.98682767724317111</v>
       </c>
       <c r="W16" s="5">
         <v>433887</v>
@@ -2359,14 +2359,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>112644</v>
+        <v>112655</v>
       </c>
       <c r="Z16" s="5">
-        <v>426887</v>
+        <v>426898</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98386676715365984</v>
+        <v>0.98389211937670407</v>
       </c>
       <c r="AB16" s="5">
         <v>753330</v>
@@ -2376,14 +2376,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>200052</v>
+        <v>200078</v>
       </c>
       <c r="AE16" s="5">
-        <v>752130</v>
+        <v>752156</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99840707259766637</v>
+        <v>0.99844158602471689</v>
       </c>
       <c r="AG16" s="5">
         <v>431686</v>
@@ -2393,14 +2393,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>113802</v>
+        <v>113817</v>
       </c>
       <c r="AJ16" s="5">
-        <v>426143</v>
+        <v>426158</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98715964844817761</v>
+        <v>0.98719439592666891</v>
       </c>
       <c r="AL16" s="5">
         <v>438911</v>
@@ -2410,14 +2410,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>114067</v>
+        <v>114085</v>
       </c>
       <c r="AO16" s="5">
-        <v>430559</v>
+        <v>430577</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98097108525418597</v>
+        <v>0.98101209584631055</v>
       </c>
       <c r="AQ16" s="5">
         <v>759875</v>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>195670</v>
+        <v>195703</v>
       </c>
       <c r="AT16" s="5">
-        <v>758669</v>
+        <v>758702</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99841289685803591</v>
+        <v>0.99845632505346271</v>
       </c>
       <c r="AV16" s="5">
         <v>437477</v>
@@ -2444,14 +2444,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108369</v>
+        <v>108389</v>
       </c>
       <c r="AY16" s="5">
-        <v>431110</v>
+        <v>431130</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.9854460920231235</v>
+        <v>0.98549180871222941</v>
       </c>
       <c r="BA16" s="5">
         <v>445887</v>
@@ -2461,14 +2461,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>109788</v>
+        <v>109813</v>
       </c>
       <c r="BD16" s="5">
-        <v>436956</v>
+        <v>436981</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.97997026152365962</v>
+        <v>0.98002632954089264</v>
       </c>
       <c r="BF16" s="5">
         <v>770088</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>207416</v>
+        <v>207460</v>
       </c>
       <c r="BI16" s="5">
-        <v>764998</v>
+        <v>765042</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99339036577637885</v>
+        <v>0.99344750210365573</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>89310</v>
+        <v>89316</v>
       </c>
       <c r="F17" s="5">
-        <v>301156</v>
+        <v>301162</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99531354313325004</v>
+        <v>0.99533337299305291</v>
       </c>
       <c r="H17" s="5">
         <v>314962</v>
@@ -2520,14 +2520,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>92351</v>
+        <v>92357</v>
       </c>
       <c r="K17" s="5">
-        <v>309402</v>
+        <v>309408</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98234707679021593</v>
+        <v>0.9823661267073488</v>
       </c>
       <c r="M17" s="5">
         <v>695415</v>
@@ -2537,14 +2537,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>249485</v>
+        <v>249502</v>
       </c>
       <c r="P17" s="5">
-        <v>691764</v>
+        <v>691781</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99474989754319365</v>
+        <v>0.99477434337769532</v>
       </c>
       <c r="R17" s="5">
         <v>305324</v>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>90709</v>
+        <v>90718</v>
       </c>
       <c r="U17" s="5">
-        <v>302695</v>
+        <v>302704</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99138947478743888</v>
+        <v>0.99141895167101179</v>
       </c>
       <c r="W17" s="5">
         <v>316716</v>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>93453</v>
+        <v>93462</v>
       </c>
       <c r="Z17" s="5">
-        <v>309806</v>
+        <v>309815</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.97818234632920342</v>
+        <v>0.9782107629548239</v>
       </c>
       <c r="AB17" s="5">
         <v>703511</v>
@@ -2588,14 +2588,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>254095</v>
+        <v>254117</v>
       </c>
       <c r="AE17" s="5">
-        <v>699770</v>
+        <v>699792</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99468238591862812</v>
+        <v>0.99471365764003694</v>
       </c>
       <c r="AG17" s="5">
         <v>311084</v>
@@ -2605,14 +2605,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>90885</v>
+        <v>90898</v>
       </c>
       <c r="AJ17" s="5">
-        <v>308979</v>
+        <v>308992</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99323333890524745</v>
+        <v>0.99327512826117703</v>
       </c>
       <c r="AL17" s="5">
         <v>323550</v>
@@ -2622,14 +2622,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93535</v>
+        <v>93548</v>
       </c>
       <c r="AO17" s="5">
-        <v>316280</v>
+        <v>316293</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97753052078504099</v>
+        <v>0.97757070004636071</v>
       </c>
       <c r="AQ17" s="5">
         <v>714257</v>
@@ -2639,14 +2639,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>244268</v>
+        <v>244294</v>
       </c>
       <c r="AT17" s="5">
-        <v>714192</v>
+        <v>714218</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99990899634165298</v>
+        <v>0.99994539780499181</v>
       </c>
       <c r="AV17" s="5">
         <v>316308</v>
@@ -2656,14 +2656,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>87067</v>
+        <v>87078</v>
       </c>
       <c r="AY17" s="5">
-        <v>314723</v>
+        <v>314734</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99498906129468745</v>
+        <v>0.99502383752544987</v>
       </c>
       <c r="BA17" s="5">
         <v>328067</v>
@@ -2673,14 +2673,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>88492</v>
+        <v>88504</v>
       </c>
       <c r="BD17" s="5">
-        <v>321662</v>
+        <v>321674</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.98047654899761327</v>
+        <v>0.98051312689176295</v>
       </c>
       <c r="BF17" s="5">
         <v>726752</v>
@@ -2690,14 +2690,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>273130</v>
+        <v>273154</v>
       </c>
       <c r="BI17" s="5">
-        <v>725600</v>
+        <v>725624</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99841486504337107</v>
+        <v>0.99844788868830081</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>454341</v>
+        <v>454349</v>
       </c>
       <c r="F18" s="5">
-        <v>917874</v>
+        <v>917882</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99635055512376847</v>
+        <v>0.99635923910919677</v>
       </c>
       <c r="H18" s="5">
         <v>943261</v>
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>449510</v>
+        <v>449519</v>
       </c>
       <c r="K18" s="5">
-        <v>932540</v>
+        <v>932549</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98863411081344399</v>
+        <v>0.98864365218110362</v>
       </c>
       <c r="M18" s="5">
         <v>1440086</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>736554</v>
+        <v>736568</v>
       </c>
       <c r="P18" s="5">
-        <v>1430644</v>
+        <v>1430658</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99344344712746324</v>
+        <v>0.9934531687690874</v>
       </c>
       <c r="R18" s="5">
         <v>938677</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>455687</v>
+        <v>455701</v>
       </c>
       <c r="U18" s="5">
-        <v>928254</v>
+        <v>928268</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98889607394236778</v>
+        <v>0.98891098855090731</v>
       </c>
       <c r="W18" s="5">
         <v>958009</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>462175</v>
+        <v>462188</v>
       </c>
       <c r="Z18" s="5">
-        <v>943355</v>
+        <v>943368</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.9847036927628029</v>
+        <v>0.98471726257268977</v>
       </c>
       <c r="AB18" s="5">
         <v>1463397</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>751148</v>
+        <v>751175</v>
       </c>
       <c r="AE18" s="5">
-        <v>1454906</v>
+        <v>1454933</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.994197746749515</v>
+        <v>0.99421619697184016</v>
       </c>
       <c r="AG18" s="5">
         <v>959088</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>469086</v>
+        <v>469108</v>
       </c>
       <c r="AJ18" s="5">
-        <v>951057</v>
+        <v>951079</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99162642009909419</v>
+        <v>0.99164935855729608</v>
       </c>
       <c r="AL18" s="5">
         <v>980581</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>470081</v>
+        <v>470105</v>
       </c>
       <c r="AO18" s="5">
-        <v>964102</v>
+        <v>964126</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98319465704515996</v>
+        <v>0.98321913233073044</v>
       </c>
       <c r="AQ18" s="5">
         <v>1490329</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>752985</v>
+        <v>753021</v>
       </c>
       <c r="AT18" s="5">
-        <v>1485968</v>
+        <v>1486004</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99707380048298055</v>
+        <v>0.99709795622308894</v>
       </c>
       <c r="AV18" s="5">
         <v>983291</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>464880</v>
+        <v>464904</v>
       </c>
       <c r="AY18" s="5">
-        <v>974178</v>
+        <v>974202</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99073214338379989</v>
+        <v>0.99075655121423867</v>
       </c>
       <c r="BA18" s="5">
         <v>1002255</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>473145</v>
+        <v>473173</v>
       </c>
       <c r="BD18" s="5">
-        <v>987658</v>
+        <v>987686</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98543584217589331</v>
+        <v>0.98546377917795369</v>
       </c>
       <c r="BF18" s="5">
         <v>1522890</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>809183</v>
+        <v>809237</v>
       </c>
       <c r="BI18" s="5">
-        <v>1512802</v>
+        <v>1512856</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99337575268075828</v>
+        <v>0.99341121157798662</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2961,14 +2961,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>327929</v>
+        <v>327931</v>
       </c>
       <c r="P19" s="5">
-        <v>470327</v>
+        <v>470329</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98170497524483813</v>
+        <v>0.98170914980838753</v>
       </c>
       <c r="R19" s="5">
         <v>279649</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>185549</v>
+        <v>185551</v>
       </c>
       <c r="U19" s="5">
-        <v>272366</v>
+        <v>272368</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97395663850040581</v>
+        <v>0.97396379032286906</v>
       </c>
       <c r="W19" s="5">
         <v>287758</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>188439</v>
+        <v>188443</v>
       </c>
       <c r="Z19" s="5">
-        <v>276669</v>
+        <v>276673</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96146414695681792</v>
+        <v>0.96147804752604615</v>
       </c>
       <c r="AB19" s="5">
         <v>485015</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>331892</v>
+        <v>331904</v>
       </c>
       <c r="AE19" s="5">
-        <v>476450</v>
+        <v>476462</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.98234075234786555</v>
+        <v>0.9823654938507056</v>
       </c>
       <c r="AG19" s="5">
         <v>283525</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>184061</v>
+        <v>184072</v>
       </c>
       <c r="AJ19" s="5">
-        <v>276453</v>
+        <v>276464</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97505687329159685</v>
+        <v>0.97509567057578694</v>
       </c>
       <c r="AL19" s="5">
         <v>295027</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>188113</v>
+        <v>188122</v>
       </c>
       <c r="AO19" s="5">
-        <v>282059</v>
+        <v>282068</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.95604470099346839</v>
+        <v>0.9560752066759991</v>
       </c>
       <c r="AQ19" s="5">
         <v>494059</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>335777</v>
+        <v>335797</v>
       </c>
       <c r="AT19" s="5">
-        <v>487916</v>
+        <v>487936</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.98756626232899314</v>
+        <v>0.98760674332417786</v>
       </c>
       <c r="AV19" s="5">
         <v>287237</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>186026</v>
+        <v>186037</v>
       </c>
       <c r="AY19" s="5">
-        <v>283016</v>
+        <v>283027</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98530481797261493</v>
+        <v>0.98534311387460527</v>
       </c>
       <c r="BA19" s="5">
         <v>298081</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>191258</v>
+        <v>191268</v>
       </c>
       <c r="BD19" s="5">
-        <v>287450</v>
+        <v>287460</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.96433519747987961</v>
+        <v>0.96436874540812734</v>
       </c>
       <c r="BF19" s="5">
         <v>503654</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>355491</v>
+        <v>355520</v>
       </c>
       <c r="BI19" s="5">
-        <v>494075</v>
+        <v>494104</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.98098099091836855</v>
+        <v>0.98103857012949369</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3275,14 +3275,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5969</v>
+        <v>5970</v>
       </c>
       <c r="AT20" s="5">
-        <v>9744</v>
+        <v>9745</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.0116279069767442</v>
+        <v>1.0117317275747508</v>
       </c>
       <c r="AV20" s="5">
         <v>6297</v>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6360</v>
+        <v>6361</v>
       </c>
       <c r="BI20" s="5">
-        <v>9897</v>
+        <v>9898</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>1.0044656449812239</v>
+        <v>1.0045671369126155</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3351,14 +3351,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>7623</v>
+        <v>7624</v>
       </c>
       <c r="F21" s="5">
-        <v>9840</v>
+        <v>9841</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.0281057360777348</v>
+        <v>1.0282102183679867</v>
       </c>
       <c r="H21" s="5">
         <v>10057</v>
@@ -3368,14 +3368,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7264</v>
+        <v>7266</v>
       </c>
       <c r="K21" s="5">
-        <v>9981</v>
+        <v>9983</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99244307447548974</v>
+        <v>0.99264194093666103</v>
       </c>
       <c r="M21" s="5">
         <v>12982</v>
@@ -3385,14 +3385,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>9813</v>
+        <v>9815</v>
       </c>
       <c r="P21" s="5">
-        <v>13257</v>
+        <v>13259</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0211831767062085</v>
+        <v>1.0213372361731627</v>
       </c>
       <c r="R21" s="5">
         <v>9811</v>
@@ -3402,14 +3402,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>7330</v>
+        <v>7332</v>
       </c>
       <c r="U21" s="5">
-        <v>10044</v>
+        <v>10046</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0237488533278973</v>
+        <v>1.0239527061461624</v>
       </c>
       <c r="W21" s="5">
         <v>10152</v>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>7387</v>
+        <v>7389</v>
       </c>
       <c r="Z21" s="5">
-        <v>10178</v>
+        <v>10180</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.002561071710008</v>
+        <v>1.0027580772261624</v>
       </c>
       <c r="AB21" s="5">
         <v>13231</v>
@@ -3436,14 +3436,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>9736</v>
+        <v>9739</v>
       </c>
       <c r="AE21" s="5">
-        <v>13580</v>
+        <v>13583</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0263774469049958</v>
+        <v>1.0266041871362708</v>
       </c>
       <c r="AG21" s="5">
         <v>10040</v>
@@ -3453,14 +3453,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>7397</v>
+        <v>7399</v>
       </c>
       <c r="AJ21" s="5">
-        <v>10251</v>
+        <v>10253</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.02101593625498</v>
+        <v>1.0212151394422311</v>
       </c>
       <c r="AL21" s="5">
         <v>10211</v>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>7524</v>
+        <v>7526</v>
       </c>
       <c r="AO21" s="5">
-        <v>10403</v>
+        <v>10405</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0188032513955538</v>
+        <v>1.0189991185975908</v>
       </c>
       <c r="AQ21" s="5">
         <v>13473</v>
@@ -3487,14 +3487,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10095</v>
+        <v>10098</v>
       </c>
       <c r="AT21" s="5">
-        <v>13909</v>
+        <v>13912</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.0323610183329621</v>
+        <v>1.032583685890299</v>
       </c>
       <c r="AV21" s="5">
         <v>10213</v>
@@ -3504,14 +3504,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>7707</v>
+        <v>7710</v>
       </c>
       <c r="AY21" s="5">
-        <v>10511</v>
+        <v>10514</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0291784979927543</v>
+        <v>1.0294722412611377</v>
       </c>
       <c r="BA21" s="5">
         <v>10449</v>
@@ -3521,14 +3521,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>7814</v>
+        <v>7818</v>
       </c>
       <c r="BD21" s="5">
-        <v>10652</v>
+        <v>10656</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0194276964302804</v>
+        <v>1.0198105081826012</v>
       </c>
       <c r="BF21" s="5">
         <v>13925</v>
@@ -3538,14 +3538,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>10904</v>
+        <v>10908</v>
       </c>
       <c r="BI21" s="5">
-        <v>14352</v>
+        <v>14356</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0306642728904847</v>
+        <v>1.0309515260323159</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4202</v>
+        <v>4203</v>
       </c>
       <c r="F22" s="5">
-        <v>6230</v>
+        <v>6231</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>1.0115278454294527</v>
+        <v>1.0116902094495859</v>
       </c>
       <c r="H22" s="5">
         <v>6265</v>
@@ -3580,14 +3580,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4373</v>
+        <v>4374</v>
       </c>
       <c r="K22" s="5">
-        <v>6316</v>
+        <v>6317</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.0081404628890662</v>
+        <v>1.0083000798084596</v>
       </c>
       <c r="M22" s="5">
         <v>7537</v>
@@ -3597,14 +3597,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5106</v>
+        <v>5109</v>
       </c>
       <c r="P22" s="5">
-        <v>7614</v>
+        <v>7617</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0102162664189995</v>
+        <v>1.0106143027729866</v>
       </c>
       <c r="R22" s="5">
         <v>6306</v>
@@ -3614,14 +3614,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4409</v>
+        <v>4411</v>
       </c>
       <c r="U22" s="5">
-        <v>6367</v>
+        <v>6369</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0096733269901681</v>
+        <v>1.0099904852521409</v>
       </c>
       <c r="W22" s="5">
         <v>6435</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4400</v>
+        <v>4401</v>
       </c>
       <c r="Z22" s="5">
-        <v>6442</v>
+        <v>6443</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>1.001087801087801</v>
+        <v>1.0012432012432013</v>
       </c>
       <c r="AB22" s="5">
         <v>7668</v>
@@ -3648,14 +3648,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5297</v>
+        <v>5300</v>
       </c>
       <c r="AE22" s="5">
-        <v>7724</v>
+        <v>7727</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0073030777256129</v>
+        <v>1.0076943140323422</v>
       </c>
       <c r="AG22" s="5">
         <v>6422</v>
@@ -3665,14 +3665,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4408</v>
+        <v>4410</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6460</v>
+        <v>6462</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0059171597633136</v>
+        <v>1.0062285892245406</v>
       </c>
       <c r="AL22" s="5">
         <v>6508</v>
@@ -3682,14 +3682,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4429</v>
+        <v>4431</v>
       </c>
       <c r="AO22" s="5">
-        <v>6509</v>
+        <v>6511</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>1.0001536570374923</v>
+        <v>1.000460971112477</v>
       </c>
       <c r="AQ22" s="5">
         <v>7781</v>
@@ -3699,14 +3699,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5400</v>
+        <v>5404</v>
       </c>
       <c r="AT22" s="5">
-        <v>7816</v>
+        <v>7820</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0044981364863128</v>
+        <v>1.0050122092276057</v>
       </c>
       <c r="AV22" s="5">
         <v>6603</v>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4479</v>
+        <v>4481</v>
       </c>
       <c r="AY22" s="5">
-        <v>6523</v>
+        <v>6525</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.98788429501741637</v>
+        <v>0.98818718764198088</v>
       </c>
       <c r="BA22" s="5">
         <v>6608</v>
@@ -3733,14 +3733,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4419</v>
+        <v>4421</v>
       </c>
       <c r="BD22" s="5">
-        <v>6564</v>
+        <v>6566</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.9933414043583535</v>
+        <v>0.99364406779661019</v>
       </c>
       <c r="BF22" s="5">
         <v>7906</v>
@@ -3750,14 +3750,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5610</v>
+        <v>5615</v>
       </c>
       <c r="BI22" s="5">
-        <v>7958</v>
+        <v>7963</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>1.0065772830761448</v>
+        <v>1.0072097141411587</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>7374</v>
+        <v>7376</v>
       </c>
       <c r="F23" s="5">
-        <v>8493</v>
+        <v>8495</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.96511363636363634</v>
+        <v>0.96534090909090908</v>
       </c>
       <c r="H23" s="5">
         <v>8763</v>
@@ -3792,14 +3792,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7008</v>
+        <v>7010</v>
       </c>
       <c r="K23" s="5">
-        <v>8526</v>
+        <v>8528</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.9729544676480657</v>
+        <v>0.97318269998858842</v>
       </c>
       <c r="M23" s="5">
         <v>10654</v>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8129</v>
+        <v>8131</v>
       </c>
       <c r="P23" s="5">
-        <v>10514</v>
+        <v>10516</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98685939553219448</v>
+        <v>0.98704711845316317</v>
       </c>
       <c r="R23" s="5">
         <v>8621</v>
@@ -3826,14 +3826,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6405</v>
+        <v>6407</v>
       </c>
       <c r="U23" s="5">
-        <v>8394</v>
+        <v>8396</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.97366894791787495</v>
+        <v>0.97390093956617563</v>
       </c>
       <c r="W23" s="5">
         <v>8774</v>
@@ -3843,14 +3843,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6295</v>
+        <v>6297</v>
       </c>
       <c r="Z23" s="5">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.96318668794164575</v>
+        <v>0.96341463414634143</v>
       </c>
       <c r="AB23" s="5">
         <v>10734</v>
@@ -3860,14 +3860,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>7677</v>
+        <v>7679</v>
       </c>
       <c r="AE23" s="5">
-        <v>10582</v>
+        <v>10584</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98583938885783495</v>
+        <v>0.98602571268865291</v>
       </c>
       <c r="AG23" s="5">
         <v>8589</v>
@@ -3877,14 +3877,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6125</v>
+        <v>6127</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8448</v>
+        <v>8450</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.98358365351030386</v>
+        <v>0.98381650948888111</v>
       </c>
       <c r="AL23" s="5">
         <v>8660</v>
@@ -3894,14 +3894,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="AO23" s="5">
-        <v>8521</v>
+        <v>8525</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.98394919168591222</v>
+        <v>0.98441108545034639</v>
       </c>
       <c r="AQ23" s="5">
         <v>10698</v>
@@ -3911,14 +3911,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>7646</v>
+        <v>7650</v>
       </c>
       <c r="AT23" s="5">
-        <v>10753</v>
+        <v>10757</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>1.005141147878108</v>
+        <v>1.0055150495419705</v>
       </c>
       <c r="AV23" s="5">
         <v>8445</v>
@@ -3928,14 +3928,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="AY23" s="5">
-        <v>8504</v>
+        <v>8507</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>1.0069863824748371</v>
+        <v>1.0073416222616933</v>
       </c>
       <c r="BA23" s="5">
         <v>8623</v>
@@ -3945,14 +3945,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="BD23" s="5">
-        <v>8551</v>
+        <v>8554</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.99165023773628669</v>
+        <v>0.99199814449727475</v>
       </c>
       <c r="BF23" s="5">
         <v>11023</v>
@@ -3962,14 +3962,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>7961</v>
+        <v>7966</v>
       </c>
       <c r="BI23" s="5">
-        <v>10939</v>
+        <v>10944</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.99237956999002086</v>
+        <v>0.99283316701442437</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4055,14 +4055,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4402</v>
+        <v>4403</v>
       </c>
       <c r="Z24" s="5">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.98042194092827006</v>
+        <v>0.98059071729957803</v>
       </c>
       <c r="AB24" s="5">
         <v>6940</v>
@@ -4072,14 +4072,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="AE24" s="5">
-        <v>6817</v>
+        <v>6818</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.9822766570605187</v>
+        <v>0.98242074927953893</v>
       </c>
       <c r="AG24" s="5">
         <v>6076</v>
@@ -4089,14 +4089,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4622</v>
+        <v>4623</v>
       </c>
       <c r="AJ24" s="5">
-        <v>5954</v>
+        <v>5955</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.97992100065832788</v>
+        <v>0.98008558262014478</v>
       </c>
       <c r="AL24" s="5">
         <v>6181</v>
@@ -4106,14 +4106,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4438</v>
+        <v>4441</v>
       </c>
       <c r="AO24" s="5">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.97346707652483422</v>
+        <v>0.97395243488108718</v>
       </c>
       <c r="AQ24" s="5">
         <v>6974</v>
@@ -4123,14 +4123,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5468</v>
+        <v>5471</v>
       </c>
       <c r="AT24" s="5">
-        <v>6908</v>
+        <v>6911</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.99053627760252361</v>
+        <v>0.99096644680240897</v>
       </c>
       <c r="AV24" s="5">
         <v>6124</v>
@@ -4140,14 +4140,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>4698</v>
+        <v>4700</v>
       </c>
       <c r="AY24" s="5">
-        <v>6045</v>
+        <v>6047</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.98709993468321355</v>
+        <v>0.98742651861528408</v>
       </c>
       <c r="BA24" s="5">
         <v>6202</v>
@@ -4157,14 +4157,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>4728</v>
+        <v>4730</v>
       </c>
       <c r="BD24" s="5">
-        <v>6137</v>
+        <v>6139</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.98951950983553694</v>
+        <v>0.98984198645598198</v>
       </c>
       <c r="BF24" s="5">
         <v>7084</v>
@@ -4174,14 +4174,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>5553</v>
+        <v>5556</v>
       </c>
       <c r="BI24" s="5">
-        <v>7039</v>
+        <v>7042</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.99364765669113497</v>
+        <v>0.99407114624505932</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4199,14 +4199,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>10072</v>
+        <v>10073</v>
       </c>
       <c r="F25" s="5">
-        <v>18494</v>
+        <v>18495</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>1.0114854517611025</v>
+        <v>1.0115401443885363</v>
       </c>
       <c r="H25" s="5">
         <v>18682</v>
@@ -4216,14 +4216,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>10337</v>
+        <v>10338</v>
       </c>
       <c r="K25" s="5">
-        <v>18848</v>
+        <v>18849</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>1.0088855582914036</v>
+        <v>1.0089390857509903</v>
       </c>
       <c r="M25" s="5">
         <v>25970</v>
@@ -4233,14 +4233,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>14496</v>
+        <v>14497</v>
       </c>
       <c r="P25" s="5">
-        <v>26280</v>
+        <v>26281</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>1.0119368502117829</v>
+        <v>1.0119753561802078</v>
       </c>
       <c r="R25" s="5">
         <v>18895</v>
@@ -4250,14 +4250,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>10405</v>
+        <v>10407</v>
       </c>
       <c r="U25" s="5">
-        <v>19047</v>
+        <v>19049</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>1.0080444562053454</v>
+        <v>1.0081503043133104</v>
       </c>
       <c r="W25" s="5">
         <v>19436</v>
@@ -4267,14 +4267,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>10767</v>
+        <v>10769</v>
       </c>
       <c r="Z25" s="5">
-        <v>19337</v>
+        <v>19339</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.99490635933319616</v>
+        <v>0.99500926116484878</v>
       </c>
       <c r="AB25" s="5">
         <v>26661</v>
@@ -4284,14 +4284,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>14623</v>
+        <v>14626</v>
       </c>
       <c r="AE25" s="5">
-        <v>26880</v>
+        <v>26883</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>1.0082142455271745</v>
+        <v>1.0083267694385056</v>
       </c>
       <c r="AG25" s="5">
         <v>19440</v>
@@ -4301,14 +4301,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>10484</v>
+        <v>10487</v>
       </c>
       <c r="AJ25" s="5">
-        <v>19514</v>
+        <v>19517</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>1.00380658436214</v>
+        <v>1.0039609053497942</v>
       </c>
       <c r="AL25" s="5">
         <v>19709</v>
@@ -4318,14 +4318,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>10531</v>
+        <v>10534</v>
       </c>
       <c r="AO25" s="5">
-        <v>19690</v>
+        <v>19693</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99903597341316153</v>
+        <v>0.99918818813739918</v>
       </c>
       <c r="AQ25" s="5">
         <v>27081</v>
@@ -4335,14 +4335,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>15499</v>
+        <v>15504</v>
       </c>
       <c r="AT25" s="5">
-        <v>27313</v>
+        <v>27318</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>1.008566891916842</v>
+        <v>1.0087515232081534</v>
       </c>
       <c r="AV25" s="5">
         <v>19795</v>
@@ -4352,14 +4352,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>10837</v>
+        <v>10841</v>
       </c>
       <c r="AY25" s="5">
-        <v>19922</v>
+        <v>19926</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>1.0064157615559484</v>
+        <v>1.0066178327860571</v>
       </c>
       <c r="BA25" s="5">
         <v>20139</v>
@@ -4369,14 +4369,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>11096</v>
+        <v>11100</v>
       </c>
       <c r="BD25" s="5">
-        <v>20147</v>
+        <v>20151</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>1.0003972391876459</v>
+        <v>1.0005958587814687</v>
       </c>
       <c r="BF25" s="5">
         <v>27639</v>
@@ -4386,14 +4386,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>16937</v>
+        <v>16942</v>
       </c>
       <c r="BI25" s="5">
-        <v>27807</v>
+        <v>27812</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>1.0060783675241507</v>
+        <v>1.0062592713195122</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4411,14 +4411,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>8944</v>
+        <v>8946</v>
       </c>
       <c r="F26" s="5">
-        <v>13322</v>
+        <v>13324</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.98426302179534542</v>
+        <v>0.98441078684891026</v>
       </c>
       <c r="H26" s="5">
         <v>13884</v>
@@ -4428,14 +4428,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9411</v>
+        <v>9413</v>
       </c>
       <c r="K26" s="5">
-        <v>13917</v>
+        <v>13919</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>1.0023768366464996</v>
+        <v>1.0025208873523481</v>
       </c>
       <c r="M26" s="5">
         <v>25920</v>
@@ -4445,14 +4445,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>17768</v>
+        <v>17770</v>
       </c>
       <c r="P26" s="5">
-        <v>26347</v>
+        <v>26349</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>1.0164737654320988</v>
+        <v>1.016550925925926</v>
       </c>
       <c r="R26" s="5">
         <v>13869</v>
@@ -4462,14 +4462,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9531</v>
+        <v>9534</v>
       </c>
       <c r="U26" s="5">
-        <v>14121</v>
+        <v>14124</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>1.018170019467878</v>
+        <v>1.0183863292234481</v>
       </c>
       <c r="W26" s="5">
         <v>14474</v>
@@ -4479,14 +4479,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9571</v>
+        <v>9577</v>
       </c>
       <c r="Z26" s="5">
-        <v>14429</v>
+        <v>14435</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.99689097692413986</v>
+        <v>0.99730551333425455</v>
       </c>
       <c r="AB26" s="5">
         <v>27035</v>
@@ -4496,14 +4496,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>18156</v>
+        <v>18161</v>
       </c>
       <c r="AE26" s="5">
-        <v>27024</v>
+        <v>27029</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.99959312002959122</v>
+        <v>0.99977806547068615</v>
       </c>
       <c r="AG26" s="5">
         <v>14053</v>
@@ -4513,14 +4513,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9393</v>
+        <v>9397</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14061</v>
+        <v>14065</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>1.0005692734647407</v>
+        <v>1.000853910197111</v>
       </c>
       <c r="AL26" s="5">
         <v>14372</v>
@@ -4530,14 +4530,14 @@
       </c>
       <c r="AN26" s="3">
         <f>AO26-AM26</f>
-        <v>9114</v>
+        <v>9122</v>
       </c>
       <c r="AO26" s="5">
-        <v>14222</v>
+        <v>14230</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.9895630392429724</v>
+        <v>0.99011967715001392</v>
       </c>
       <c r="AQ26" s="5">
         <v>27267</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="AS26" s="3">
         <f>AT26-AR26</f>
-        <v>19131</v>
+        <v>19139</v>
       </c>
       <c r="AT26" s="5">
-        <v>27130</v>
+        <v>27138</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99497561154509118</v>
+        <v>0.99526900649136318</v>
       </c>
       <c r="AV26" s="5">
         <v>14007</v>
@@ -4564,14 +4564,14 @@
       </c>
       <c r="AX26" s="3">
         <f>AY26-AW26</f>
-        <v>9383</v>
+        <v>9390</v>
       </c>
       <c r="AY26" s="5">
-        <v>13989</v>
+        <v>13996</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99871492825016062</v>
+        <v>0.99921467837509814</v>
       </c>
       <c r="BA26" s="5">
         <v>14398</v>
@@ -4581,14 +4581,14 @@
       </c>
       <c r="BC26" s="3">
         <f>BD26-BB26</f>
-        <v>9290</v>
+        <v>9301</v>
       </c>
       <c r="BD26" s="5">
-        <v>14084</v>
+        <v>14095</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.9781914154743715</v>
+        <v>0.97895541047367685</v>
       </c>
       <c r="BF26" s="5">
         <v>27339</v>
@@ -4598,14 +4598,14 @@
       </c>
       <c r="BH26" s="3">
         <f>BI26-BG26</f>
-        <v>19196</v>
+        <v>19210</v>
       </c>
       <c r="BI26" s="5">
-        <v>27149</v>
+        <v>27163</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99305022129558507</v>
+        <v>0.99356231025275243</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>74120</v>
+        <v>74125</v>
       </c>
       <c r="F27" s="5">
-        <v>120711</v>
+        <v>120716</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>1.0019006988595807</v>
+        <v>1.0019421988346806</v>
       </c>
       <c r="H27" s="5">
         <v>123649</v>
@@ -4640,14 +4640,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>75153</v>
+        <v>75158</v>
       </c>
       <c r="K27" s="5">
-        <v>122575</v>
+        <v>122580</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.99131412304183619</v>
+        <v>0.99135456008540301</v>
       </c>
       <c r="M27" s="5">
         <v>182121</v>
@@ -4657,14 +4657,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>115211</v>
+        <v>115220</v>
       </c>
       <c r="P27" s="5">
-        <v>181421</v>
+        <v>181430</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99615640151327967</v>
+        <v>0.99620581920810891</v>
       </c>
       <c r="R27" s="5">
         <v>122848</v>
@@ -4674,14 +4674,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>73656</v>
+        <v>73663</v>
       </c>
       <c r="U27" s="5">
-        <v>121981</v>
+        <v>121988</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99294249804636625</v>
+        <v>0.99299947903099761</v>
       </c>
       <c r="W27" s="5">
         <v>125846</v>
@@ -4691,14 +4691,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>74956</v>
+        <v>74965</v>
       </c>
       <c r="Z27" s="5">
-        <v>123339</v>
+        <v>123348</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.98007882650223288</v>
+        <v>0.98015034248208133</v>
       </c>
       <c r="AB27" s="5">
         <v>184102</v>
@@ -4708,14 +4708,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>113363</v>
+        <v>113382</v>
       </c>
       <c r="AE27" s="5">
-        <v>183173</v>
+        <v>183192</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99495388425981246</v>
+        <v>0.99505708791865377</v>
       </c>
       <c r="AG27" s="5">
         <v>124176</v>
@@ -4725,14 +4725,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>72900</v>
+        <v>72911</v>
       </c>
       <c r="AJ27" s="5">
-        <v>123163</v>
+        <v>123174</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99184222394021393</v>
+        <v>0.99193080788558174</v>
       </c>
       <c r="AL27" s="5">
         <v>126536</v>
@@ -4742,14 +4742,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" ref="AN27:AN33" si="24">AO27-AM27</f>
-        <v>74037</v>
+        <v>74049</v>
       </c>
       <c r="AO27" s="5">
-        <v>124101</v>
+        <v>124113</v>
       </c>
       <c r="AP27" s="4">
         <f>AO27/AL27</f>
-        <v>0.98075646456344434</v>
+        <v>0.98085129923500036</v>
       </c>
       <c r="AQ27" s="5">
         <v>184835</v>
@@ -4759,14 +4759,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" ref="AS27:AS33" si="25">AT27-AR27</f>
-        <v>115246</v>
+        <v>115269</v>
       </c>
       <c r="AT27" s="5">
-        <v>184699</v>
+        <v>184722</v>
       </c>
       <c r="AU27" s="4">
         <f>AT27/AQ27</f>
-        <v>0.99926420861849763</v>
+        <v>0.9993886439256634</v>
       </c>
       <c r="AV27" s="5">
         <v>124975</v>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" ref="AX27:AX33" si="26">AY27-AW27</f>
-        <v>73633</v>
+        <v>73651</v>
       </c>
       <c r="AY27" s="5">
-        <v>124218</v>
+        <v>124236</v>
       </c>
       <c r="AZ27" s="4">
         <f>AY27/AV27</f>
-        <v>0.99394278855771157</v>
+        <v>0.99408681736347271</v>
       </c>
       <c r="BA27" s="5">
         <v>127493</v>
@@ -4793,14 +4793,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" ref="BC27:BC33" si="27">BD27-BB27</f>
-        <v>74257</v>
+        <v>74278</v>
       </c>
       <c r="BD27" s="5">
-        <v>125351</v>
+        <v>125372</v>
       </c>
       <c r="BE27" s="4">
         <f>BD27/BA27</f>
-        <v>0.983199077596417</v>
+        <v>0.98336379252194239</v>
       </c>
       <c r="BF27" s="5">
         <v>187636</v>
@@ -4810,14 +4810,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>121604</v>
+        <v>121636</v>
       </c>
       <c r="BI27" s="5">
-        <v>186152</v>
+        <v>186184</v>
       </c>
       <c r="BJ27" s="4">
         <f>BI27/BF27</f>
-        <v>0.99209106994393403</v>
+        <v>0.99226161291010251</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4835,14 +4835,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>164961</v>
+        <v>164963</v>
       </c>
       <c r="F28" s="5">
-        <v>379834</v>
+        <v>379836</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99378872237106497</v>
+        <v>0.99379395512391155</v>
       </c>
       <c r="H28" s="5">
         <v>389922</v>
@@ -4852,14 +4852,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>167362</v>
+        <v>167364</v>
       </c>
       <c r="K28" s="5">
-        <v>384971</v>
+        <v>384973</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.9873025887228728</v>
+        <v>0.9873077179538472</v>
       </c>
       <c r="M28" s="5">
         <v>650891</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>302138</v>
+        <v>302142</v>
       </c>
       <c r="P28" s="5">
-        <v>646842</v>
+        <v>646846</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99377929637988538</v>
+        <v>0.99378544180208361</v>
       </c>
       <c r="R28" s="5">
         <v>389073</v>
@@ -4886,14 +4886,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>169121</v>
+        <v>169127</v>
       </c>
       <c r="U28" s="5">
-        <v>386334</v>
+        <v>386340</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99296018999005331</v>
+        <v>0.99297561126061173</v>
       </c>
       <c r="W28" s="5">
         <v>397763</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>171208</v>
+        <v>171213</v>
       </c>
       <c r="Z28" s="5">
-        <v>391708</v>
+        <v>391713</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.98477736742733735</v>
+        <v>0.98478993772673673</v>
       </c>
       <c r="AB28" s="5">
         <v>660941</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>292824</v>
+        <v>292837</v>
       </c>
       <c r="AE28" s="5">
-        <v>657462</v>
+        <v>657475</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99473629264941954</v>
+        <v>0.99475596157599544</v>
       </c>
       <c r="AG28" s="5">
         <v>397417</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>163426</v>
+        <v>163432</v>
       </c>
       <c r="AJ28" s="5">
-        <v>394439</v>
+        <v>394445</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.99250661144339569</v>
+        <v>0.99252170893545066</v>
       </c>
       <c r="AL28" s="5">
         <v>405895</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="24"/>
-        <v>168525</v>
+        <v>168534</v>
       </c>
       <c r="AO28" s="5">
-        <v>398840</v>
+        <v>398849</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" ref="AP28:AP33" si="28">AO28/AL28</f>
-        <v>0.98261865753458411</v>
+        <v>0.98264083075672282</v>
       </c>
       <c r="AQ28" s="5">
         <v>670091</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="25"/>
-        <v>295986</v>
+        <v>296002</v>
       </c>
       <c r="AT28" s="5">
-        <v>667114</v>
+        <v>667130</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" ref="AU28:AU33" si="29">AT28/AQ28</f>
-        <v>0.99555731982671014</v>
+        <v>0.99558119718068139</v>
       </c>
       <c r="AV28" s="5">
         <v>405395</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="26"/>
-        <v>166507</v>
+        <v>166515</v>
       </c>
       <c r="AY28" s="5">
-        <v>402210</v>
+        <v>402218</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" ref="AZ28:AZ33" si="30">AY28/AV28</f>
-        <v>0.99214346501560202</v>
+        <v>0.99216319885543724</v>
       </c>
       <c r="BA28" s="5">
         <v>412255</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="27"/>
-        <v>167744</v>
+        <v>167754</v>
       </c>
       <c r="BD28" s="5">
-        <v>406750</v>
+        <v>406760</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" ref="BE28:BE33" si="31">BD28/BA28</f>
-        <v>0.98664661435276713</v>
+        <v>0.98667087118409724</v>
       </c>
       <c r="BF28" s="5">
         <v>680839</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>320773</v>
+        <v>320795</v>
       </c>
       <c r="BI28" s="5">
-        <v>677461</v>
+        <v>677483</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99503847458797157</v>
+        <v>0.99507078766051882</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>65990</v>
+        <v>65994</v>
       </c>
       <c r="F29" s="5">
-        <v>126984</v>
+        <v>126988</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99550789059008915</v>
+        <v>0.99553924912000125</v>
       </c>
       <c r="H29" s="5">
         <v>129829</v>
@@ -5064,14 +5064,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>67259</v>
+        <v>67263</v>
       </c>
       <c r="K29" s="5">
-        <v>128367</v>
+        <v>128371</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98873903365195759</v>
+        <v>0.98876984340940777</v>
       </c>
       <c r="M29" s="5">
         <v>176637</v>
@@ -5081,14 +5081,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>93977</v>
+        <v>93981</v>
       </c>
       <c r="P29" s="5">
-        <v>174570</v>
+        <v>174574</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98829803495303925</v>
+        <v>0.98832068026517661</v>
       </c>
       <c r="R29" s="5">
         <v>129740</v>
@@ -5098,14 +5098,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>67084</v>
+        <v>67089</v>
       </c>
       <c r="U29" s="5">
-        <v>128524</v>
+        <v>128529</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.99062740866348076</v>
+        <v>0.99066594727917379</v>
       </c>
       <c r="W29" s="5">
         <v>131766</v>
@@ -5115,14 +5115,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>67104</v>
+        <v>67110</v>
       </c>
       <c r="Z29" s="5">
-        <v>129610</v>
+        <v>129616</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98363766070154668</v>
+        <v>0.98368319596861098</v>
       </c>
       <c r="AB29" s="5">
         <v>178083</v>
@@ -5132,14 +5132,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>93892</v>
+        <v>93897</v>
       </c>
       <c r="AE29" s="5">
-        <v>176673</v>
+        <v>176678</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.99208234362628667</v>
+        <v>0.99211042042193809</v>
       </c>
       <c r="AG29" s="5">
         <v>131984</v>
@@ -5149,14 +5149,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>68242</v>
+        <v>68247</v>
       </c>
       <c r="AJ29" s="5">
-        <v>130627</v>
+        <v>130632</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.9897184507212996</v>
+        <v>0.9897563341011032</v>
       </c>
       <c r="AL29" s="5">
         <v>133676</v>
@@ -5166,14 +5166,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="24"/>
-        <v>68586</v>
+        <v>68591</v>
       </c>
       <c r="AO29" s="5">
-        <v>131856</v>
+        <v>131861</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="28"/>
-        <v>0.98638499057422424</v>
+        <v>0.98642239444627311</v>
       </c>
       <c r="AQ29" s="5">
         <v>179800</v>
@@ -5183,14 +5183,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="25"/>
-        <v>93905</v>
+        <v>93910</v>
       </c>
       <c r="AT29" s="5">
-        <v>179270</v>
+        <v>179275</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="29"/>
-        <v>0.99705228031145721</v>
+        <v>0.99708008898776423</v>
       </c>
       <c r="AV29" s="5">
         <v>134089</v>
@@ -5200,14 +5200,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="26"/>
-        <v>66907</v>
+        <v>66911</v>
       </c>
       <c r="AY29" s="5">
-        <v>133039</v>
+        <v>133043</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="30"/>
-        <v>0.99216938003863109</v>
+        <v>0.99219921097181718</v>
       </c>
       <c r="BA29" s="5">
         <v>136058</v>
@@ -5217,14 +5217,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="27"/>
-        <v>68607</v>
+        <v>68612</v>
       </c>
       <c r="BD29" s="5">
-        <v>134434</v>
+        <v>134439</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="31"/>
-        <v>0.9880639139190639</v>
+        <v>0.98810066295256438</v>
       </c>
       <c r="BF29" s="5">
         <v>182623</v>
@@ -5234,14 +5234,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>100484</v>
+        <v>100492</v>
       </c>
       <c r="BI29" s="5">
-        <v>181759</v>
+        <v>181767</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.99526894202811256</v>
+        <v>0.9953127481204449</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5259,14 +5259,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>95640</v>
+        <v>95641</v>
       </c>
       <c r="F30" s="5">
-        <v>166224</v>
+        <v>166225</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99598547581099384</v>
+        <v>0.99599146763814161</v>
       </c>
       <c r="H30" s="5">
         <v>172134</v>
@@ -5276,14 +5276,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="K30" s="5">
-        <v>169430</v>
+        <v>169431</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98429130793451614</v>
+        <v>0.98429711736205516</v>
       </c>
       <c r="M30" s="5">
         <v>289249</v>
@@ -5293,14 +5293,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>172719</v>
+        <v>172722</v>
       </c>
       <c r="P30" s="5">
-        <v>286750</v>
+        <v>286753</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.99136038499700951</v>
+        <v>0.99137075668368779</v>
       </c>
       <c r="R30" s="5">
         <v>169142</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>95693</v>
+        <v>95694</v>
       </c>
       <c r="U30" s="5">
-        <v>167651</v>
+        <v>167652</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99118492154521054</v>
+        <v>0.99119083373733308</v>
       </c>
       <c r="W30" s="5">
         <v>174259</v>
@@ -5327,14 +5327,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>95215</v>
+        <v>95217</v>
       </c>
       <c r="Z30" s="5">
-        <v>170791</v>
+        <v>170793</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.98009858888206636</v>
+        <v>0.98011006605110784</v>
       </c>
       <c r="AB30" s="5">
         <v>293307</v>
@@ -5344,14 +5344,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>173233</v>
+        <v>173241</v>
       </c>
       <c r="AE30" s="5">
-        <v>291158</v>
+        <v>291166</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99267320589007424</v>
+        <v>0.99270048106591391</v>
       </c>
       <c r="AG30" s="5">
         <v>172053</v>
@@ -5361,14 +5361,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>94761</v>
+        <v>94767</v>
       </c>
       <c r="AJ30" s="5">
-        <v>170789</v>
+        <v>170795</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.99265342656042033</v>
+        <v>0.99268829953560822</v>
       </c>
       <c r="AL30" s="5">
         <v>176835</v>
@@ -5378,14 +5378,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="24"/>
-        <v>96569</v>
+        <v>96575</v>
       </c>
       <c r="AO30" s="5">
-        <v>173517</v>
+        <v>173523</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="28"/>
-        <v>0.9812367461192637</v>
+        <v>0.98127067605394858</v>
       </c>
       <c r="AQ30" s="5">
         <v>297651</v>
@@ -5395,14 +5395,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="25"/>
-        <v>175608</v>
+        <v>175622</v>
       </c>
       <c r="AT30" s="5">
-        <v>296824</v>
+        <v>296838</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="29"/>
-        <v>0.9972215782913546</v>
+        <v>0.99726861324168237</v>
       </c>
       <c r="AV30" s="5">
         <v>175428</v>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="26"/>
-        <v>96847</v>
+        <v>96853</v>
       </c>
       <c r="AY30" s="5">
-        <v>174082</v>
+        <v>174088</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="30"/>
-        <v>0.99232733657112893</v>
+        <v>0.99236153863693366</v>
       </c>
       <c r="BA30" s="5">
         <v>179593</v>
@@ -5429,14 +5429,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="27"/>
-        <v>98799</v>
+        <v>98807</v>
       </c>
       <c r="BD30" s="5">
-        <v>176061</v>
+        <v>176069</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="31"/>
-        <v>0.98033330920470174</v>
+        <v>0.98037785437071601</v>
       </c>
       <c r="BF30" s="5">
         <v>302258</v>
@@ -5446,14 +5446,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>185084</v>
+        <v>185101</v>
       </c>
       <c r="BI30" s="5">
-        <v>300117</v>
+        <v>300134</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99291664736748075</v>
+        <v>0.99297289070926165</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5505,14 +5505,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>70017</v>
+        <v>70019</v>
       </c>
       <c r="P31" s="5">
-        <v>133851</v>
+        <v>133853</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0007925529926351</v>
+        <v>1.0008075068226849</v>
       </c>
       <c r="R31" s="5">
         <v>74974</v>
@@ -5522,14 +5522,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34162</v>
+        <v>34163</v>
       </c>
       <c r="U31" s="5">
-        <v>74781</v>
+        <v>74782</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>0.99742577426841306</v>
+        <v>0.99743911222557158</v>
       </c>
       <c r="W31" s="5">
         <v>77586</v>
@@ -5556,14 +5556,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>70315</v>
+        <v>70316</v>
       </c>
       <c r="AE31" s="5">
-        <v>135428</v>
+        <v>135429</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0023091269723794</v>
+        <v>1.0023165280203676</v>
       </c>
       <c r="AG31" s="5">
         <v>76230</v>
@@ -5573,14 +5573,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>33311</v>
+        <v>33312</v>
       </c>
       <c r="AJ31" s="5">
-        <v>75676</v>
+        <v>75677</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>0.99273252000524725</v>
+        <v>0.99274563820018369</v>
       </c>
       <c r="AL31" s="5">
         <v>77611</v>
@@ -5590,14 +5590,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="24"/>
-        <v>33394</v>
+        <v>33395</v>
       </c>
       <c r="AO31" s="5">
-        <v>76716</v>
+        <v>76717</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="28"/>
-        <v>0.988468129517723</v>
+        <v>0.98848101428921153</v>
       </c>
       <c r="AQ31" s="5">
         <v>136879</v>
@@ -5607,14 +5607,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="25"/>
-        <v>69318</v>
+        <v>69319</v>
       </c>
       <c r="AT31" s="5">
-        <v>137680</v>
+        <v>137681</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="29"/>
-        <v>1.0058518837805652</v>
+        <v>1.0058591895031379</v>
       </c>
       <c r="AV31" s="5">
         <v>76719</v>
@@ -5624,14 +5624,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="26"/>
-        <v>33135</v>
+        <v>33136</v>
       </c>
       <c r="AY31" s="5">
-        <v>76698</v>
+        <v>76699</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="30"/>
-        <v>0.99972627380440304</v>
+        <v>0.9997393083851458</v>
       </c>
       <c r="BA31" s="5">
         <v>78720</v>
@@ -5641,14 +5641,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="27"/>
-        <v>33795</v>
+        <v>33796</v>
       </c>
       <c r="BD31" s="5">
-        <v>78208</v>
+        <v>78209</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="31"/>
-        <v>0.99349593495934962</v>
+        <v>0.99350863821138213</v>
       </c>
       <c r="BF31" s="5">
         <v>140181</v>
@@ -5658,14 +5658,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>76259</v>
+        <v>76266</v>
       </c>
       <c r="BI31" s="5">
-        <v>140492</v>
+        <v>140499</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.002218560289911</v>
+        <v>1.0022684957305199</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5683,14 +5683,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>93780</v>
+        <v>93783</v>
       </c>
       <c r="F32" s="5">
-        <v>202832</v>
+        <v>202835</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99565085068575188</v>
+        <v>0.99566557692496493</v>
       </c>
       <c r="H32" s="5">
         <v>210874</v>
@@ -5700,14 +5700,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>94714</v>
+        <v>94717</v>
       </c>
       <c r="K32" s="5">
-        <v>207283</v>
+        <v>207286</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98297087360224589</v>
+        <v>0.98298510010717299</v>
       </c>
       <c r="M32" s="5">
         <v>441035</v>
@@ -5717,14 +5717,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>233991</v>
+        <v>233999</v>
       </c>
       <c r="P32" s="5">
-        <v>439425</v>
+        <v>439433</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99634949607174039</v>
+        <v>0.99636763522169447</v>
       </c>
       <c r="R32" s="5">
         <v>206418</v>
@@ -5734,14 +5734,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>92300</v>
+        <v>92303</v>
       </c>
       <c r="U32" s="5">
-        <v>204376</v>
+        <v>204379</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99010745186950755</v>
+        <v>0.99012198548576191</v>
       </c>
       <c r="W32" s="5">
         <v>212709</v>
@@ -5751,14 +5751,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>95924</v>
+        <v>95927</v>
       </c>
       <c r="Z32" s="5">
-        <v>208793</v>
+        <v>208796</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.98158987160862965</v>
+        <v>0.9816039753842104</v>
       </c>
       <c r="AB32" s="5">
         <v>446806</v>
@@ -5768,14 +5768,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>237846</v>
+        <v>237852</v>
       </c>
       <c r="AE32" s="5">
-        <v>445874</v>
+        <v>445880</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99791408351723121</v>
+        <v>0.99792751216411602</v>
       </c>
       <c r="AG32" s="5">
         <v>210129</v>
@@ -5785,14 +5785,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>92553</v>
+        <v>92556</v>
       </c>
       <c r="AJ32" s="5">
-        <v>208779</v>
+        <v>208782</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.9935753751267079</v>
+        <v>0.9935896520708708</v>
       </c>
       <c r="AL32" s="5">
         <v>217332</v>
@@ -5802,14 +5802,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="24"/>
-        <v>93052</v>
+        <v>93057</v>
       </c>
       <c r="AO32" s="5">
-        <v>212387</v>
+        <v>212392</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="28"/>
-        <v>0.97724679292510996</v>
+        <v>0.97726979920122214</v>
       </c>
       <c r="AQ32" s="5">
         <v>453805</v>
@@ -5819,14 +5819,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="25"/>
-        <v>229535</v>
+        <v>229544</v>
       </c>
       <c r="AT32" s="5">
-        <v>453649</v>
+        <v>453658</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="29"/>
-        <v>0.99965624001498443</v>
+        <v>0.99967607232181221</v>
       </c>
       <c r="AV32" s="5">
         <v>213428</v>
@@ -5836,14 +5836,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="26"/>
-        <v>91566</v>
+        <v>91571</v>
       </c>
       <c r="AY32" s="5">
-        <v>212593</v>
+        <v>212598</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="30"/>
-        <v>0.99608767359484229</v>
+        <v>0.99611110069906483</v>
       </c>
       <c r="BA32" s="5">
         <v>220509</v>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="27"/>
-        <v>94377</v>
+        <v>94380</v>
       </c>
       <c r="BD32" s="5">
-        <v>217107</v>
+        <v>217110</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="31"/>
-        <v>0.98457205828333538</v>
+        <v>0.98458566317021079</v>
       </c>
       <c r="BF32" s="5">
         <v>463937</v>
@@ -5870,14 +5870,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>253946</v>
+        <v>253955</v>
       </c>
       <c r="BI32" s="5">
-        <v>461920</v>
+        <v>461929</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99565242694589995</v>
+        <v>0.99567182613156524</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5895,14 +5895,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>96268</v>
+        <v>96269</v>
       </c>
       <c r="F33" s="5">
-        <v>620527</v>
+        <v>620528</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.9992463707437258</v>
+        <v>0.99924798106264945</v>
       </c>
       <c r="H33" s="5">
         <v>630476</v>
@@ -5912,14 +5912,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>98479</v>
+        <v>98480</v>
       </c>
       <c r="K33" s="5">
-        <v>628336</v>
+        <v>628337</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99660573915581241</v>
+        <v>0.99660732525901063</v>
       </c>
       <c r="M33" s="5">
         <v>1032030</v>
@@ -5929,14 +5929,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>184051</v>
+        <v>184054</v>
       </c>
       <c r="P33" s="5">
-        <v>1033751</v>
+        <v>1033754</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0016675871825431</v>
+        <v>1.0016704940747847</v>
       </c>
       <c r="R33" s="5">
         <v>629419</v>
@@ -5946,14 +5946,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>97173</v>
+        <v>97175</v>
       </c>
       <c r="U33" s="5">
-        <v>627899</v>
+        <v>627901</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>0.99758507448933065</v>
+        <v>0.99758825202289736</v>
       </c>
       <c r="W33" s="5">
         <v>637378</v>
@@ -5963,14 +5963,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>101397</v>
+        <v>101398</v>
       </c>
       <c r="Z33" s="5">
-        <v>634257</v>
+        <v>634258</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99510337664619741</v>
+        <v>0.99510494557389806</v>
       </c>
       <c r="AB33" s="5">
         <v>1041984</v>
@@ -5980,14 +5980,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>184408</v>
+        <v>184414</v>
       </c>
       <c r="AE33" s="5">
-        <v>1043587</v>
+        <v>1043593</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0015384113383698</v>
+        <v>1.0015441695841778</v>
       </c>
       <c r="AG33" s="5">
         <v>638215</v>
@@ -5997,14 +5997,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>78015</v>
+        <v>78016</v>
       </c>
       <c r="AJ33" s="5">
-        <v>637054</v>
+        <v>637055</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>0.99818086381548543</v>
+        <v>0.99818243068558399</v>
       </c>
       <c r="AL33" s="5">
         <v>645318</v>
@@ -6014,14 +6014,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="24"/>
-        <v>94794</v>
+        <v>94795</v>
       </c>
       <c r="AO33" s="5">
-        <v>641699</v>
+        <v>641700</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="28"/>
-        <v>0.9943919122045255</v>
+        <v>0.99439346182812194</v>
       </c>
       <c r="AQ33" s="5">
         <v>1053133</v>
@@ -6031,14 +6031,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="25"/>
-        <v>167724</v>
+        <v>167729</v>
       </c>
       <c r="AT33" s="5">
-        <v>1055180</v>
+        <v>1055185</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="29"/>
-        <v>1.0019437241070217</v>
+        <v>1.0019484718454363</v>
       </c>
       <c r="AV33" s="5">
         <v>647979</v>
@@ -6048,14 +6048,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="26"/>
-        <v>89182</v>
+        <v>89183</v>
       </c>
       <c r="AY33" s="5">
-        <v>647885</v>
+        <v>647886</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="30"/>
-        <v>0.99985493357037802</v>
+        <v>0.99985647683026768</v>
       </c>
       <c r="BA33" s="5">
         <v>657743</v>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="27"/>
-        <v>89584</v>
+        <v>89586</v>
       </c>
       <c r="BD33" s="5">
-        <v>657189</v>
+        <v>657191</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="31"/>
-        <v>0.99915772573786421</v>
+        <v>0.99916076643917151</v>
       </c>
       <c r="BF33" s="5">
         <v>1071541</v>
@@ -6082,14 +6082,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>189775</v>
+        <v>189781</v>
       </c>
       <c r="BI33" s="5">
-        <v>1072571</v>
+        <v>1072577</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0009612324680064</v>
+        <v>1.0009668318804414</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6431,14 +6431,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="46">AT35-AR35</f>
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="AT35" s="5">
-        <v>14613</v>
+        <v>14614</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU47" si="47">AT35/AQ35</f>
-        <v>0.99822392239907098</v>
+        <v>0.99829223307602977</v>
       </c>
       <c r="AV35" s="5">
         <v>11843</v>
@@ -6448,14 +6448,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="48">AY35-AW35</f>
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="AY35" s="5">
-        <v>11822</v>
+        <v>11823</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ47" si="49">AY35/AV35</f>
-        <v>0.99822680064172931</v>
+        <v>0.99831123870640881</v>
       </c>
       <c r="BA35" s="5">
         <v>11921</v>
@@ -6465,14 +6465,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="50">BD35-BB35</f>
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="BD35" s="5">
-        <v>11865</v>
+        <v>11866</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE47" si="51">BD35/BA35</f>
-        <v>0.99530240751614796</v>
+        <v>0.99538629309621673</v>
       </c>
       <c r="BF35" s="5">
         <v>14735</v>
@@ -6482,14 +6482,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="52">BI35-BG35</f>
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="BI35" s="5">
-        <v>14722</v>
+        <v>14723</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ47" si="53">BI35/BF35</f>
-        <v>0.99911774686121479</v>
+        <v>0.99918561248727522</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6507,14 +6507,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>253990</v>
+        <v>253998</v>
       </c>
       <c r="F36" s="5">
-        <v>833189</v>
+        <v>833197</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.99659345220367046</v>
+        <v>0.99660302115815447</v>
       </c>
       <c r="H36" s="5">
         <v>854298</v>
@@ -6524,14 +6524,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="32"/>
-        <v>261263</v>
+        <v>261271</v>
       </c>
       <c r="K36" s="5">
-        <v>843353</v>
+        <v>843361</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98718831133866636</v>
+        <v>0.98719767575248918</v>
       </c>
       <c r="M36" s="5">
         <v>1510524</v>
@@ -6541,14 +6541,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="34"/>
-        <v>489849</v>
+        <v>489861</v>
       </c>
       <c r="P36" s="5">
-        <v>1504240</v>
+        <v>1504252</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99583985424925392</v>
+        <v>0.99584779851230432</v>
       </c>
       <c r="R36" s="5">
         <v>845008</v>
@@ -6558,14 +6558,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="36"/>
-        <v>248831</v>
+        <v>248838</v>
       </c>
       <c r="U36" s="5">
-        <v>839797</v>
+        <v>839804</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99383319447863216</v>
+        <v>0.99384147842387294</v>
       </c>
       <c r="W36" s="5">
         <v>865288</v>
@@ -6575,14 +6575,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="38"/>
-        <v>251384</v>
+        <v>251391</v>
       </c>
       <c r="Z36" s="5">
-        <v>849469</v>
+        <v>849476</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98171822560812128</v>
+        <v>0.98172631540019051</v>
       </c>
       <c r="AB36" s="5">
         <v>1522408</v>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="40"/>
-        <v>485987</v>
+        <v>486006</v>
       </c>
       <c r="AE36" s="5">
-        <v>1517957</v>
+        <v>1517976</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="41"/>
-        <v>0.99707634221575292</v>
+        <v>0.9970888224444433</v>
       </c>
       <c r="AG36" s="5">
         <v>860909</v>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="42"/>
-        <v>232924</v>
+        <v>232935</v>
       </c>
       <c r="AJ36" s="5">
-        <v>855817</v>
+        <v>855828</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="43"/>
-        <v>0.99408532144512374</v>
+        <v>0.99409809863760279</v>
       </c>
       <c r="AL36" s="5">
         <v>879793</v>
@@ -6626,14 +6626,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="44"/>
-        <v>238568</v>
+        <v>238578</v>
       </c>
       <c r="AO36" s="5">
-        <v>866308</v>
+        <v>866318</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="45"/>
-        <v>0.98467253092488805</v>
+        <v>0.98468389723491778</v>
       </c>
       <c r="AQ36" s="5">
         <v>1539776</v>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="46"/>
-        <v>458700</v>
+        <v>458721</v>
       </c>
       <c r="AT36" s="5">
-        <v>1539476</v>
+        <v>1539497</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="47"/>
-        <v>0.99980516646577167</v>
+        <v>0.99981880481316765</v>
       </c>
       <c r="AV36" s="5">
         <v>875330</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="48"/>
-        <v>234334</v>
+        <v>234345</v>
       </c>
       <c r="AY36" s="5">
-        <v>872485</v>
+        <v>872496</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="49"/>
-        <v>0.99674979721933443</v>
+        <v>0.99676236390846884</v>
       </c>
       <c r="BA36" s="5">
         <v>893595</v>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="50"/>
-        <v>235994</v>
+        <v>236004</v>
       </c>
       <c r="BD36" s="5">
-        <v>883724</v>
+        <v>883734</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="51"/>
-        <v>0.98895360873773919</v>
+        <v>0.98896479948970173</v>
       </c>
       <c r="BF36" s="5">
         <v>1566403</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="52"/>
-        <v>507335</v>
+        <v>507359</v>
       </c>
       <c r="BI36" s="5">
-        <v>1560406</v>
+        <v>1560430</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="53"/>
-        <v>0.99617148332836436</v>
+        <v>0.99618680505591473</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>283681</v>
+        <v>283686</v>
       </c>
       <c r="F37" s="5">
-        <v>667690</v>
+        <v>667695</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.98836649895122342</v>
+        <v>0.98837390033883554</v>
       </c>
       <c r="H37" s="5">
         <v>681828</v>
@@ -6736,14 +6736,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="32"/>
-        <v>274159</v>
+        <v>274164</v>
       </c>
       <c r="K37" s="5">
-        <v>670560</v>
+        <v>670565</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98347383797673316</v>
+        <v>0.98348117120446799</v>
       </c>
       <c r="M37" s="5">
         <v>856106</v>
@@ -6753,14 +6753,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="34"/>
-        <v>347695</v>
+        <v>347702</v>
       </c>
       <c r="P37" s="5">
-        <v>846331</v>
+        <v>846338</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98858202138520235</v>
+        <v>0.98859019794277814</v>
       </c>
       <c r="R37" s="5">
         <v>679636</v>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="36"/>
-        <v>268949</v>
+        <v>268955</v>
       </c>
       <c r="U37" s="5">
-        <v>671498</v>
+        <v>671504</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98802594329906013</v>
+        <v>0.98803477155418484</v>
       </c>
       <c r="W37" s="5">
         <v>687189</v>
@@ -6787,14 +6787,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="38"/>
-        <v>273282</v>
+        <v>273295</v>
       </c>
       <c r="Z37" s="5">
-        <v>676597</v>
+        <v>676610</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98458648203041665</v>
+        <v>0.98460539967898209</v>
       </c>
       <c r="AB37" s="5">
         <v>863912</v>
@@ -6804,14 +6804,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="40"/>
-        <v>349272</v>
+        <v>349285</v>
       </c>
       <c r="AE37" s="5">
-        <v>855443</v>
+        <v>855456</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99019691820463196</v>
+        <v>0.99021196603357753</v>
       </c>
       <c r="AG37" s="5">
         <v>690763</v>
@@ -6821,14 +6821,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="42"/>
-        <v>260645</v>
+        <v>260657</v>
       </c>
       <c r="AJ37" s="5">
-        <v>682625</v>
+        <v>682637</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="43"/>
-        <v>0.98821882469095768</v>
+        <v>0.98823619678529395</v>
       </c>
       <c r="AL37" s="5">
         <v>697437</v>
@@ -6838,14 +6838,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="44"/>
-        <v>264998</v>
+        <v>265012</v>
       </c>
       <c r="AO37" s="5">
-        <v>688614</v>
+        <v>688628</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98734939499911822</v>
+        <v>0.98736946849679608</v>
       </c>
       <c r="AQ37" s="5">
         <v>873380</v>
@@ -6855,14 +6855,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="46"/>
-        <v>338552</v>
+        <v>338570</v>
       </c>
       <c r="AT37" s="5">
-        <v>868962</v>
+        <v>868980</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99494149167601731</v>
+        <v>0.99496210126176465</v>
       </c>
       <c r="AV37" s="5">
         <v>700086</v>
@@ -6872,14 +6872,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="48"/>
-        <v>266958</v>
+        <v>266975</v>
       </c>
       <c r="AY37" s="5">
-        <v>694471</v>
+        <v>694488</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="49"/>
-        <v>0.99197955679730776</v>
+        <v>0.99200383952828652</v>
       </c>
       <c r="BA37" s="5">
         <v>708485</v>
@@ -6889,14 +6889,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="50"/>
-        <v>268853</v>
+        <v>268870</v>
       </c>
       <c r="BD37" s="5">
-        <v>699453</v>
+        <v>699470</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="51"/>
-        <v>0.98725167081871879</v>
+        <v>0.98727566568099534</v>
       </c>
       <c r="BF37" s="5">
         <v>887779</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="52"/>
-        <v>384164</v>
+        <v>384188</v>
       </c>
       <c r="BI37" s="5">
-        <v>878225</v>
+        <v>878249</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="53"/>
-        <v>0.9892383126881803</v>
+        <v>0.98926534644320263</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6982,14 +6982,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="36"/>
-        <v>9353</v>
+        <v>9354</v>
       </c>
       <c r="U38" s="5">
-        <v>23142</v>
+        <v>23143</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="37"/>
-        <v>1.010082493125573</v>
+        <v>1.0101261402819606</v>
       </c>
       <c r="W38" s="5">
         <v>23450</v>
@@ -7016,14 +7016,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="40"/>
-        <v>14260</v>
+        <v>14261</v>
       </c>
       <c r="AE38" s="5">
-        <v>36327</v>
+        <v>36328</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0114715300013921</v>
+        <v>1.0114993735208131</v>
       </c>
       <c r="AG38" s="5">
         <v>23414</v>
@@ -7101,14 +7101,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="50"/>
-        <v>8902</v>
+        <v>8903</v>
       </c>
       <c r="BD38" s="5">
-        <v>24406</v>
+        <v>24407</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="51"/>
-        <v>1.0046929030133378</v>
+        <v>1.0047340688292441</v>
       </c>
       <c r="BF38" s="5">
         <v>37393</v>
@@ -7118,14 +7118,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="52"/>
-        <v>15244</v>
+        <v>15246</v>
       </c>
       <c r="BI38" s="5">
-        <v>37599</v>
+        <v>37601</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="53"/>
-        <v>1.0055090524964565</v>
+        <v>1.005562538443024</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>104864</v>
+        <v>104871</v>
       </c>
       <c r="F40" s="5">
-        <v>275848</v>
+        <v>275855</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.99325224505080623</v>
+        <v>0.99327745011198254</v>
       </c>
       <c r="H40" s="5">
         <v>279588</v>
@@ -7372,14 +7372,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="32"/>
-        <v>108063</v>
+        <v>108071</v>
       </c>
       <c r="K40" s="5">
-        <v>277552</v>
+        <v>277560</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99271785627423204</v>
+        <v>0.99274646980557102</v>
       </c>
       <c r="M40" s="5">
         <v>339205</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="34"/>
-        <v>135130</v>
+        <v>135137</v>
       </c>
       <c r="P40" s="5">
-        <v>337532</v>
+        <v>337539</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99506787930602436</v>
+        <v>0.9950885157942837</v>
       </c>
       <c r="R40" s="5">
         <v>280405</v>
@@ -7406,14 +7406,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="36"/>
-        <v>104710</v>
+        <v>104715</v>
       </c>
       <c r="U40" s="5">
-        <v>278866</v>
+        <v>278871</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99451151013712313</v>
+        <v>0.9945293414882046</v>
       </c>
       <c r="W40" s="5">
         <v>283529</v>
@@ -7423,14 +7423,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="38"/>
-        <v>110246</v>
+        <v>110251</v>
       </c>
       <c r="Z40" s="5">
-        <v>280810</v>
+        <v>280815</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="39"/>
-        <v>0.9904101520479387</v>
+        <v>0.99042778692832123</v>
       </c>
       <c r="AB40" s="5">
         <v>342699</v>
@@ -7440,14 +7440,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="40"/>
-        <v>136248</v>
+        <v>136256</v>
       </c>
       <c r="AE40" s="5">
-        <v>341675</v>
+        <v>341683</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99701195509762208</v>
+        <v>0.99703529919842193</v>
       </c>
       <c r="AG40" s="5">
         <v>284836</v>
@@ -7457,14 +7457,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="42"/>
-        <v>104284</v>
+        <v>104293</v>
       </c>
       <c r="AJ40" s="5">
-        <v>283415</v>
+        <v>283424</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="43"/>
-        <v>0.99501116431911696</v>
+        <v>0.9950427614486933</v>
       </c>
       <c r="AL40" s="5">
         <v>287465</v>
@@ -7474,14 +7474,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="44"/>
-        <v>109802</v>
+        <v>109811</v>
       </c>
       <c r="AO40" s="5">
-        <v>285645</v>
+        <v>285654</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="45"/>
-        <v>0.99366879446193446</v>
+        <v>0.99370010262118869</v>
       </c>
       <c r="AQ40" s="5">
         <v>346543</v>
@@ -7491,14 +7491,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="46"/>
-        <v>133819</v>
+        <v>133833</v>
       </c>
       <c r="AT40" s="5">
-        <v>346479</v>
+        <v>346493</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99981531873389451</v>
+        <v>0.99985571776085502</v>
       </c>
       <c r="AV40" s="5">
         <v>288959</v>
@@ -7508,14 +7508,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="48"/>
-        <v>110667</v>
+        <v>110681</v>
       </c>
       <c r="AY40" s="5">
-        <v>287763</v>
+        <v>287777</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="49"/>
-        <v>0.99586100450236881</v>
+        <v>0.99590945428244149</v>
       </c>
       <c r="BA40" s="5">
         <v>291465</v>
@@ -7525,14 +7525,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="50"/>
-        <v>109542</v>
+        <v>109557</v>
       </c>
       <c r="BD40" s="5">
-        <v>288942</v>
+        <v>288957</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="51"/>
-        <v>0.99134372909268698</v>
+        <v>0.99139519324790282</v>
       </c>
       <c r="BF40" s="5">
         <v>351557</v>
@@ -7542,14 +7542,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="52"/>
-        <v>149293</v>
+        <v>149318</v>
       </c>
       <c r="BI40" s="5">
-        <v>349442</v>
+        <v>349467</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="53"/>
-        <v>0.99398390588154983</v>
+        <v>0.99405501810517216</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>345435</v>
+        <v>345446</v>
       </c>
       <c r="F41" s="5">
-        <v>905561</v>
+        <v>905572</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.99281559103357697</v>
+        <v>0.99282765092959868</v>
       </c>
       <c r="H41" s="5">
         <v>920596</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="32"/>
-        <v>358267</v>
+        <v>358278</v>
       </c>
       <c r="K41" s="5">
-        <v>910574</v>
+        <v>910585</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98911357424972512</v>
+        <v>0.98912552303073231</v>
       </c>
       <c r="M41" s="5">
         <v>1028922</v>
@@ -7601,14 +7601,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="34"/>
-        <v>396213</v>
+        <v>396227</v>
       </c>
       <c r="P41" s="5">
-        <v>1018320</v>
+        <v>1018334</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="35"/>
-        <v>0.98969601194259627</v>
+        <v>0.98970961841616756</v>
       </c>
       <c r="R41" s="5">
         <v>924082</v>
@@ -7618,14 +7618,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="36"/>
-        <v>360527</v>
+        <v>360542</v>
       </c>
       <c r="U41" s="5">
-        <v>915047</v>
+        <v>915062</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99022272915174192</v>
+        <v>0.99023896147744461</v>
       </c>
       <c r="W41" s="5">
         <v>929406</v>
@@ -7635,14 +7635,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="38"/>
-        <v>356197</v>
+        <v>356214</v>
       </c>
       <c r="Z41" s="5">
-        <v>919001</v>
+        <v>919018</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="39"/>
-        <v>0.98880467739610034</v>
+        <v>0.98882296864879293</v>
       </c>
       <c r="AB41" s="5">
         <v>1036539</v>
@@ -7652,14 +7652,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="40"/>
-        <v>396619</v>
+        <v>396641</v>
       </c>
       <c r="AE41" s="5">
-        <v>1027435</v>
+        <v>1027457</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99121692478527101</v>
+        <v>0.99123814926404119</v>
       </c>
       <c r="AG41" s="5">
         <v>935526</v>
@@ -7669,14 +7669,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="42"/>
-        <v>348943</v>
+        <v>348966</v>
       </c>
       <c r="AJ41" s="5">
-        <v>925575</v>
+        <v>925598</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="43"/>
-        <v>0.98936320316057491</v>
+        <v>0.98938778826029417</v>
       </c>
       <c r="AL41" s="5">
         <v>940174</v>
@@ -7686,14 +7686,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="44"/>
-        <v>363738</v>
+        <v>363762</v>
       </c>
       <c r="AO41" s="5">
-        <v>930140</v>
+        <v>930164</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="45"/>
-        <v>0.98932750746138476</v>
+        <v>0.98935303465103264</v>
       </c>
       <c r="AQ41" s="5">
         <v>1046219</v>
@@ -7703,14 +7703,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="46"/>
-        <v>386048</v>
+        <v>386077</v>
       </c>
       <c r="AT41" s="5">
-        <v>1038935</v>
+        <v>1038964</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99303778654373509</v>
+        <v>0.99306550540565597</v>
       </c>
       <c r="AV41" s="5">
         <v>945246</v>
@@ -7720,14 +7720,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="48"/>
-        <v>357491</v>
+        <v>357518</v>
       </c>
       <c r="AY41" s="5">
-        <v>936930</v>
+        <v>936957</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="49"/>
-        <v>0.99120229019747241</v>
+        <v>0.99123085419033774</v>
       </c>
       <c r="BA41" s="5">
         <v>950318</v>
@@ -7737,14 +7737,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="50"/>
-        <v>355001</v>
+        <v>355025</v>
       </c>
       <c r="BD41" s="5">
-        <v>940876</v>
+        <v>940900</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="51"/>
-        <v>0.99006437845016093</v>
+        <v>0.9900896331543757</v>
       </c>
       <c r="BF41" s="5">
         <v>1056723</v>
@@ -7754,14 +7754,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="52"/>
-        <v>421991</v>
+        <v>422026</v>
       </c>
       <c r="BI41" s="5">
-        <v>1049231</v>
+        <v>1049266</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="53"/>
-        <v>0.99291015715565956</v>
+        <v>0.9929432784182799</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7779,14 +7779,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="0"/>
-        <v>8186</v>
+        <v>8187</v>
       </c>
       <c r="F42" s="5">
-        <v>18237</v>
+        <v>18238</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="1"/>
-        <v>0.98872323122797501</v>
+        <v>0.98877744646245591</v>
       </c>
       <c r="H42" s="5">
         <v>18615</v>
@@ -7796,14 +7796,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="32"/>
-        <v>8628</v>
+        <v>8629</v>
       </c>
       <c r="K42" s="5">
-        <v>18359</v>
+        <v>18360</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="33"/>
-        <v>0.98624764974482948</v>
+        <v>0.98630136986301364</v>
       </c>
       <c r="M42" s="5">
         <v>20702</v>
@@ -7813,14 +7813,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="34"/>
-        <v>9321</v>
+        <v>9322</v>
       </c>
       <c r="P42" s="5">
-        <v>20398</v>
+        <v>20399</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="35"/>
-        <v>0.98531542846101827</v>
+        <v>0.98536373297265967</v>
       </c>
       <c r="R42" s="5">
         <v>18543</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="36"/>
-        <v>8478</v>
+        <v>8479</v>
       </c>
       <c r="U42" s="5">
-        <v>18337</v>
+        <v>18338</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="37"/>
-        <v>0.98889068651243062</v>
+        <v>0.98894461521868093</v>
       </c>
       <c r="W42" s="5">
         <v>18720</v>
@@ -8178,14 +8178,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="52"/>
-        <v>2776</v>
+        <v>2777</v>
       </c>
       <c r="BI43" s="5">
-        <v>4550</v>
+        <v>4551</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="53"/>
-        <v>1.0013204225352113</v>
+        <v>1.0015404929577465</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8203,14 +8203,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>164126</v>
+        <v>164131</v>
       </c>
       <c r="F44" s="5">
-        <v>333694</v>
+        <v>333699</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.9924634474225823</v>
+        <v>0.99247831828402155</v>
       </c>
       <c r="H44" s="5">
         <v>340996</v>
@@ -8220,14 +8220,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="32"/>
-        <v>169336</v>
+        <v>169341</v>
       </c>
       <c r="K44" s="5">
-        <v>337617</v>
+        <v>337622</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="33"/>
-        <v>0.99009079285387513</v>
+        <v>0.99010545578247255</v>
       </c>
       <c r="M44" s="5">
         <v>408512</v>
@@ -8237,14 +8237,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="34"/>
-        <v>200397</v>
+        <v>200402</v>
       </c>
       <c r="P44" s="5">
-        <v>404893</v>
+        <v>404898</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="35"/>
-        <v>0.99114101911326957</v>
+        <v>0.9911532586558045</v>
       </c>
       <c r="R44" s="5">
         <v>342556</v>
@@ -8254,14 +8254,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="36"/>
-        <v>167623</v>
+        <v>167628</v>
       </c>
       <c r="U44" s="5">
-        <v>339654</v>
+        <v>339659</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="37"/>
-        <v>0.99152839243802471</v>
+        <v>0.99154298859164636</v>
       </c>
       <c r="W44" s="5">
         <v>347597</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="38"/>
-        <v>168811</v>
+        <v>168816</v>
       </c>
       <c r="Z44" s="5">
-        <v>343535</v>
+        <v>343540</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98831405334338329</v>
+        <v>0.98832843781735746</v>
       </c>
       <c r="AB44" s="5">
         <v>416340</v>
@@ -8288,14 +8288,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="40"/>
-        <v>203189</v>
+        <v>203196</v>
       </c>
       <c r="AE44" s="5">
-        <v>413214</v>
+        <v>413221</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="41"/>
-        <v>0.99249171350338661</v>
+        <v>0.99250852668492096</v>
       </c>
       <c r="AG44" s="5">
         <v>350469</v>
@@ -8305,14 +8305,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="42"/>
-        <v>166204</v>
+        <v>166211</v>
       </c>
       <c r="AJ44" s="5">
-        <v>347629</v>
+        <v>347636</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="43"/>
-        <v>0.99189657287805766</v>
+        <v>0.99191654611392166</v>
       </c>
       <c r="AL44" s="5">
         <v>355186</v>
@@ -8322,14 +8322,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="44"/>
-        <v>169376</v>
+        <v>169382</v>
       </c>
       <c r="AO44" s="5">
-        <v>351109</v>
+        <v>351115</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98852150704138109</v>
+        <v>0.9885383995990833</v>
       </c>
       <c r="AQ44" s="5">
         <v>424208</v>
@@ -8339,14 +8339,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="46"/>
-        <v>198287</v>
+        <v>198297</v>
       </c>
       <c r="AT44" s="5">
-        <v>421874</v>
+        <v>421884</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="47"/>
-        <v>0.99449798212197793</v>
+        <v>0.99452155546335763</v>
       </c>
       <c r="AV44" s="5">
         <v>358114</v>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="48"/>
-        <v>167147</v>
+        <v>167159</v>
       </c>
       <c r="AY44" s="5">
-        <v>354708</v>
+        <v>354720</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="49"/>
-        <v>0.99048906214222288</v>
+        <v>0.99052257102486918</v>
       </c>
       <c r="BA44" s="5">
         <v>361984</v>
@@ -8373,14 +8373,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="50"/>
-        <v>170858</v>
+        <v>170870</v>
       </c>
       <c r="BD44" s="5">
-        <v>357809</v>
+        <v>357821</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="51"/>
-        <v>0.9884663410537482</v>
+        <v>0.98849949169024043</v>
       </c>
       <c r="BF44" s="5">
         <v>432310</v>
@@ -8390,14 +8390,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="52"/>
-        <v>225462</v>
+        <v>225482</v>
       </c>
       <c r="BI44" s="5">
-        <v>428058</v>
+        <v>428078</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="53"/>
-        <v>0.99016446531424207</v>
+        <v>0.99021072841248181</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8449,14 +8449,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="34"/>
-        <v>144179</v>
+        <v>144182</v>
       </c>
       <c r="P45" s="5">
-        <v>305413</v>
+        <v>305416</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98404142206298373</v>
+        <v>0.98405108807021391</v>
       </c>
       <c r="R45" s="5">
         <v>257356</v>
@@ -8466,14 +8466,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="36"/>
-        <v>118788</v>
+        <v>118791</v>
       </c>
       <c r="U45" s="5">
-        <v>253930</v>
+        <v>253933</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98668770108332426</v>
+        <v>0.98669935808762954</v>
       </c>
       <c r="W45" s="5">
         <v>260553</v>
@@ -8483,14 +8483,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="38"/>
-        <v>120991</v>
+        <v>120995</v>
       </c>
       <c r="Z45" s="5">
-        <v>255892</v>
+        <v>255896</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98211112518374377</v>
+        <v>0.98212647714668422</v>
       </c>
       <c r="AB45" s="5">
         <v>313911</v>
@@ -8500,14 +8500,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="40"/>
-        <v>148037</v>
+        <v>148043</v>
       </c>
       <c r="AE45" s="5">
-        <v>309031</v>
+        <v>309037</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="41"/>
-        <v>0.98445419243033849</v>
+        <v>0.98447330612817008</v>
       </c>
       <c r="AG45" s="5">
         <v>261210</v>
@@ -8517,14 +8517,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="42"/>
-        <v>116293</v>
+        <v>116300</v>
       </c>
       <c r="AJ45" s="5">
-        <v>257217</v>
+        <v>257224</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="43"/>
-        <v>0.98471344894912138</v>
+        <v>0.98474024731059306</v>
       </c>
       <c r="AL45" s="5">
         <v>264020</v>
@@ -8534,14 +8534,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="44"/>
-        <v>120914</v>
+        <v>120924</v>
       </c>
       <c r="AO45" s="5">
-        <v>259608</v>
+        <v>259618</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98328914476176044</v>
+        <v>0.98332702068025146</v>
       </c>
       <c r="AQ45" s="5">
         <v>317407</v>
@@ -8551,14 +8551,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="46"/>
-        <v>143499</v>
+        <v>143510</v>
       </c>
       <c r="AT45" s="5">
-        <v>312037</v>
+        <v>312048</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="47"/>
-        <v>0.98308165856455587</v>
+        <v>0.98311631438500091</v>
       </c>
       <c r="AV45" s="5">
         <v>263886</v>
@@ -8568,14 +8568,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="48"/>
-        <v>118311</v>
+        <v>118320</v>
       </c>
       <c r="AY45" s="5">
-        <v>259613</v>
+        <v>259622</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="49"/>
-        <v>0.98380740168102898</v>
+        <v>0.98384150731755382</v>
       </c>
       <c r="BA45" s="5">
         <v>265781</v>
@@ -8585,14 +8585,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="50"/>
-        <v>120895</v>
+        <v>120905</v>
       </c>
       <c r="BD45" s="5">
-        <v>261441</v>
+        <v>261451</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="51"/>
-        <v>0.98367076653334884</v>
+        <v>0.98370839149525358</v>
       </c>
       <c r="BF45" s="5">
         <v>319799</v>
@@ -8602,14 +8602,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="52"/>
-        <v>165104</v>
+        <v>165114</v>
       </c>
       <c r="BI45" s="5">
-        <v>315169</v>
+        <v>315179</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="53"/>
-        <v>0.98552215610430305</v>
+        <v>0.98555342574554639</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8746,14 +8746,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="44"/>
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AO46" s="5">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="45"/>
-        <v>1.0057471264367817</v>
+        <v>1.0061576354679802</v>
       </c>
       <c r="AQ46" s="5">
         <v>7143</v>
@@ -8763,14 +8763,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="46"/>
-        <v>4295</v>
+        <v>4297</v>
       </c>
       <c r="AT46" s="5">
-        <v>7365</v>
+        <v>7367</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="47"/>
-        <v>1.0310793784124317</v>
+        <v>1.0313593728125436</v>
       </c>
       <c r="AV46" s="5">
         <v>2225</v>
@@ -8780,14 +8780,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="48"/>
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="AY46" s="5">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="49"/>
-        <v>1.0593258426966292</v>
+        <v>1.0597752808988765</v>
       </c>
       <c r="BA46" s="5">
         <v>2388</v>
@@ -8797,14 +8797,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="50"/>
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="BD46" s="5">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="51"/>
-        <v>1.0134003350083751</v>
+        <v>1.0138190954773869</v>
       </c>
       <c r="BF46" s="5">
         <v>7407</v>
@@ -8814,14 +8814,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="52"/>
-        <v>4646</v>
+        <v>4647</v>
       </c>
       <c r="BI46" s="5">
-        <v>7566</v>
+        <v>7567</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="53"/>
-        <v>1.0214661806399352</v>
+        <v>1.0216011880653435</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9051,15 +9051,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3007712</v>
+        <v>3007798</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>7666641</v>
+        <v>7666727</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.99406476517864184</v>
+        <v>0.9940759160294258</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9071,15 +9071,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3058356</v>
+        <v>3058445</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7765211</v>
+        <v>7765300</v>
       </c>
       <c r="L48" s="6">
         <f>K48/H48</f>
-        <v>0.9870181092882172</v>
+        <v>0.98702942187350651</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9091,15 +9091,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>4954568</v>
+        <v>4954715</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12077232</v>
+        <v>12077379</v>
       </c>
       <c r="Q48" s="6">
         <f>P48/M48</f>
-        <v>0.99382665863084474</v>
+        <v>0.99383875515418874</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9111,15 +9111,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3023267</v>
+        <v>3023388</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7734631</v>
+        <v>7734752</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.99087074342423087</v>
+        <v>0.99088624453345697</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3062656</v>
+        <v>3062791</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7826361</v>
+        <v>7826496</v>
       </c>
       <c r="AA48" s="6">
         <f>Z48/W48</f>
-        <v>0.98471658493996661</v>
+        <v>0.98473357070627199</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>4962592</v>
+        <v>4962849</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12221046</v>
+        <v>12221303</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.99486062519929086</v>
+        <v>0.99488154641836468</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2974330</v>
+        <v>2974522</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7866510</v>
+        <v>7866702</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.99144533679102576</v>
+        <v>0.99146953526082549</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3044387</v>
+        <v>3044602</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7955517</v>
+        <v>7955732</v>
       </c>
       <c r="AP48" s="6">
         <f>AO48/AL48</f>
-        <v>0.9847793092683188</v>
+        <v>0.98480592319567162</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4873964</v>
+        <v>4874311</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12411282</v>
+        <v>12411629</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.9972709257816198</v>
+        <v>0.99729880791428305</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>2995320</v>
+        <v>2995556</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8002233</v>
+        <v>8002469</v>
       </c>
       <c r="AZ48" s="6">
         <f>AY48/AV48</f>
-        <v>0.99266833686128453</v>
+        <v>0.99269761240568566</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3029073</v>
+        <v>3029331</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8095472</v>
+        <v>8095730</v>
       </c>
       <c r="BE48" s="6">
         <f>BD48/BA48</f>
-        <v>0.98695719757072731</v>
+        <v>0.98698865156834148</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9271,15 +9271,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5326259</v>
+        <v>5326723</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12582854</v>
+        <v>12583318</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99421573538684238</v>
+        <v>0.99425239766562423</v>
       </c>
     </row>
   </sheetData>
